--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY139"/>
+  <dimension ref="A1:AY138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8346,10 +8346,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>16065826</v>
+        <v>16065665</v>
       </c>
       <c r="B63" t="n">
-        <v>103226</v>
+        <v>96312</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8358,40 +8358,32 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>340</v>
+        <v>219798</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -8401,10 +8393,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>601230.7653263864</v>
+        <v>601222.0309980026</v>
       </c>
       <c r="R63" t="n">
-        <v>6276614.151326371</v>
+        <v>6276656.315908728</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -8460,7 +8452,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>SANDTAG</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8478,10 +8470,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>16065665</v>
+        <v>16065671</v>
       </c>
       <c r="B64" t="n">
-        <v>96312</v>
+        <v>101692</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8490,34 +8482,26 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219798</v>
+        <v>224416</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8525,10 +8509,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>601222.0309980026</v>
+        <v>601211.9961727971</v>
       </c>
       <c r="R64" t="n">
-        <v>6276656.315908728</v>
+        <v>6276637.914061293</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8602,10 +8586,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>16065671</v>
+        <v>16065773</v>
       </c>
       <c r="B65" t="n">
-        <v>101692</v>
+        <v>103265</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8614,23 +8598,27 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>224416</v>
+        <v>221144</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -8641,10 +8629,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>601211.9961727971</v>
+        <v>601303.340485534</v>
       </c>
       <c r="R65" t="n">
-        <v>6276637.914061293</v>
+        <v>6276691.841509511</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8700,7 +8688,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>SANDTAG</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8718,10 +8706,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>16065773</v>
+        <v>16071703</v>
       </c>
       <c r="B66" t="n">
-        <v>103265</v>
+        <v>103226</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8730,29 +8718,37 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221144</v>
+        <v>340</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
@@ -8761,10 +8757,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>601303.340485534</v>
+        <v>601291.732164192</v>
       </c>
       <c r="R66" t="n">
-        <v>6276691.841509511</v>
+        <v>6276670.099830886</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8838,7 +8834,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>16071703</v>
+        <v>16071704</v>
       </c>
       <c r="B67" t="n">
         <v>103226</v>
@@ -8873,7 +8869,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8889,10 +8885,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>601291.732164192</v>
+        <v>601279.8939441737</v>
       </c>
       <c r="R67" t="n">
-        <v>6276670.099830886</v>
+        <v>6276680.821239713</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8966,10 +8962,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>16071704</v>
+        <v>16071746</v>
       </c>
       <c r="B68" t="n">
-        <v>103226</v>
+        <v>103252</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8978,37 +8974,29 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>340</v>
+        <v>224098</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -9017,10 +9005,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>601279.8939441737</v>
+        <v>601277.8615302774</v>
       </c>
       <c r="R68" t="n">
-        <v>6276680.821239713</v>
+        <v>6276673.618233426</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -9094,10 +9082,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>16071746</v>
+        <v>16071702</v>
       </c>
       <c r="B69" t="n">
-        <v>103252</v>
+        <v>103226</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9106,29 +9094,37 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>224098</v>
+        <v>340</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Wallr.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -9137,10 +9133,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>601277.8615302774</v>
+        <v>601300.1759324172</v>
       </c>
       <c r="R69" t="n">
-        <v>6276673.618233426</v>
+        <v>6276640.03555864</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -9214,10 +9210,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>16071702</v>
+        <v>16071705</v>
       </c>
       <c r="B70" t="n">
-        <v>103226</v>
+        <v>106707</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9226,37 +9222,29 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>340</v>
+        <v>220204</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -9265,10 +9253,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>601300.1759324172</v>
+        <v>601271.7992213219</v>
       </c>
       <c r="R70" t="n">
-        <v>6276640.03555864</v>
+        <v>6276673.472352961</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -9342,10 +9330,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>16071705</v>
+        <v>17012454</v>
       </c>
       <c r="B71" t="n">
-        <v>106707</v>
+        <v>40753</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9358,37 +9346,55 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220204</v>
+        <v>215683</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Mellanmätare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Phibalapteryx virgata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Hufnagel, 1767)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Gårdby sandhed, Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>601271.7992213219</v>
+        <v>601193.3068938741</v>
       </c>
       <c r="R71" t="n">
-        <v>6276673.472352961</v>
+        <v>6276727.165816098</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -9415,7 +9421,7 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-08-06</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
@@ -9425,7 +9431,7 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-08-06</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
@@ -9441,31 +9447,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>David Hammarberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>17012454</v>
+        <v>17012458</v>
       </c>
       <c r="B72" t="n">
-        <v>40753</v>
+        <v>9359</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9478,21 +9479,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>215683</v>
+        <v>102176</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mellanmätare</t>
+          <t>Heddyngbagge</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phibalapteryx virgata</t>
+          <t>Bodilopsis sordida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
+          <t>(Fabricius, 1775)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -9553,7 +9554,7 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2014-08-06</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
@@ -9563,7 +9564,7 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2014-08-06</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
@@ -9595,10 +9596,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>17012458</v>
+        <v>17021016</v>
       </c>
       <c r="B73" t="n">
-        <v>9359</v>
+        <v>39815</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9611,21 +9612,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>102176</v>
+        <v>214498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Heddyngbagge</t>
+          <t>Sikelsäckmal</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bodilopsis sordida</t>
+          <t>Coleophora lixella</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fabricius, 1775)</t>
+          <t>Zeller, 1849</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -9728,10 +9729,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>17021016</v>
+        <v>17204730</v>
       </c>
       <c r="B74" t="n">
-        <v>39815</v>
+        <v>103265</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9740,59 +9741,45 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>214498</v>
+        <v>221144</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sikelsäckmal</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Coleophora lixella</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Zeller, 1849</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Gårdby, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>601193.3068938741</v>
+        <v>601399.8208384699</v>
       </c>
       <c r="R74" t="n">
-        <v>6276727.165816098</v>
+        <v>6276601.160870589</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -9819,7 +9806,7 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2015-03-17</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
@@ -9829,7 +9816,7 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2015-03-17</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
@@ -9845,26 +9832,31 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>tallskog på sand</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>David Hammarberg</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>17204730</v>
+        <v>17204727</v>
       </c>
       <c r="B75" t="n">
-        <v>103265</v>
+        <v>103226</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9873,34 +9865,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221144</v>
+        <v>340</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9908,10 +9904,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>601399.8208384699</v>
+        <v>601394.6673125625</v>
       </c>
       <c r="R75" t="n">
-        <v>6276601.160870589</v>
+        <v>6276586.177884741</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9985,7 +9981,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>17204727</v>
+        <v>17204731</v>
       </c>
       <c r="B76" t="n">
         <v>103226</v>
@@ -10020,7 +10016,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10036,10 +10032,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>601394.6673125625</v>
+        <v>601399.8208384699</v>
       </c>
       <c r="R76" t="n">
-        <v>6276586.177884741</v>
+        <v>6276601.160870589</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -10113,7 +10109,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>17204731</v>
+        <v>54444150</v>
       </c>
       <c r="B77" t="n">
         <v>103226</v>
@@ -10148,7 +10144,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10160,14 +10156,14 @@
       <c r="L77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>601399.8208384699</v>
+        <v>601233.494501177</v>
       </c>
       <c r="R77" t="n">
-        <v>6276601.160870589</v>
+        <v>6276615.317616789</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -10194,7 +10190,7 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2015-03-17</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
@@ -10204,7 +10200,7 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2015-03-17</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
@@ -10223,7 +10219,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10241,10 +10237,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>54444150</v>
+        <v>54444175</v>
       </c>
       <c r="B78" t="n">
-        <v>103226</v>
+        <v>103265</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10253,37 +10249,29 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>340</v>
+        <v>221144</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -10292,10 +10280,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>601233.494501177</v>
+        <v>601350.6114488394</v>
       </c>
       <c r="R78" t="n">
-        <v>6276615.317616789</v>
+        <v>6276606.579479626</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -10369,7 +10357,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>54444175</v>
+        <v>54444133</v>
       </c>
       <c r="B79" t="n">
         <v>103265</v>
@@ -10412,10 +10400,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>601350.6114488394</v>
+        <v>601309.323332068</v>
       </c>
       <c r="R79" t="n">
-        <v>6276606.579479626</v>
+        <v>6276695.287403132</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -10489,10 +10477,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>54444133</v>
+        <v>54444064</v>
       </c>
       <c r="B80" t="n">
-        <v>103265</v>
+        <v>103226</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10501,29 +10489,37 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221144</v>
+        <v>340</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
@@ -10532,10 +10528,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>601309.323332068</v>
+        <v>601248.1586250714</v>
       </c>
       <c r="R80" t="n">
-        <v>6276695.287403132</v>
+        <v>6276647.588971923</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -10609,7 +10605,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>54444064</v>
+        <v>54444032</v>
       </c>
       <c r="B81" t="n">
         <v>103226</v>
@@ -10644,7 +10640,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10652,7 +10648,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10660,10 +10660,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>601248.1586250714</v>
+        <v>601310.0250217792</v>
       </c>
       <c r="R81" t="n">
-        <v>6276647.588971923</v>
+        <v>6276666.13760154</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -10737,7 +10737,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>54444032</v>
+        <v>54444116</v>
       </c>
       <c r="B82" t="n">
         <v>103226</v>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>139</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10780,11 +10780,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10792,10 +10788,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>601310.0250217792</v>
+        <v>601271.1469509092</v>
       </c>
       <c r="R82" t="n">
-        <v>6276666.13760154</v>
+        <v>6276654.745885707</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -10869,7 +10865,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>54444116</v>
+        <v>54444046</v>
       </c>
       <c r="B83" t="n">
         <v>103226</v>
@@ -10904,7 +10900,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10920,10 +10916,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>601271.1469509092</v>
+        <v>601281.4943553162</v>
       </c>
       <c r="R83" t="n">
-        <v>6276654.745885707</v>
+        <v>6276683.06101186</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10997,10 +10993,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>54444046</v>
+        <v>54444054</v>
       </c>
       <c r="B84" t="n">
-        <v>103226</v>
+        <v>103265</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11009,37 +11005,29 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>340</v>
+        <v>221144</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
@@ -11048,10 +11036,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>601281.4943553162</v>
+        <v>601271.1469509092</v>
       </c>
       <c r="R84" t="n">
-        <v>6276683.06101186</v>
+        <v>6276654.745885707</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -11125,10 +11113,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>54444054</v>
+        <v>54511725</v>
       </c>
       <c r="B85" t="n">
-        <v>103265</v>
+        <v>96312</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11141,26 +11129,30 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11168,10 +11160,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>601271.1469509092</v>
+        <v>601305.2105685344</v>
       </c>
       <c r="R85" t="n">
-        <v>6276654.745885707</v>
+        <v>6276659.968222207</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -11198,7 +11190,7 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
@@ -11208,7 +11200,7 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
@@ -11227,28 +11219,28 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>54511725</v>
+        <v>54511702</v>
       </c>
       <c r="B86" t="n">
-        <v>96312</v>
+        <v>95521</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11261,30 +11253,22 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219798</v>
+        <v>224363</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11292,10 +11276,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>601305.2105685344</v>
+        <v>601304.1411444313</v>
       </c>
       <c r="R86" t="n">
-        <v>6276659.968222207</v>
+        <v>6276566.937782379</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -11369,10 +11353,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>54511702</v>
+        <v>54524712</v>
       </c>
       <c r="B87" t="n">
-        <v>95521</v>
+        <v>103265</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11385,36 +11369,40 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>224363</v>
+        <v>221144</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>NO Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>601304.1411444313</v>
+        <v>601271.4910445306</v>
       </c>
       <c r="R87" t="n">
-        <v>6276566.937782379</v>
+        <v>6276640.445872318</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11438,7 +11426,7 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2015-07-21</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
@@ -11448,7 +11436,7 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2015-07-21</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
@@ -11464,31 +11452,26 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>54524712</v>
+        <v>54524711</v>
       </c>
       <c r="B88" t="n">
-        <v>103265</v>
+        <v>103226</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11497,25 +11480,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221144</v>
+        <v>340</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -11600,7 +11583,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>54524711</v>
+        <v>54592439</v>
       </c>
       <c r="B89" t="n">
         <v>103226</v>
@@ -11633,23 +11616,31 @@
           <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>NO Gårdby sandhed, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>601271.4910445306</v>
+        <v>601399.7280807921</v>
       </c>
       <c r="R89" t="n">
-        <v>6276640.445872318</v>
+        <v>6276605.010915966</v>
       </c>
       <c r="S89" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11673,7 +11664,7 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2015-07-21</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
@@ -11683,7 +11674,7 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2015-07-21</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
@@ -11699,23 +11690,28 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>tallskog, vid hygge</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>54592439</v>
+        <v>56867190</v>
       </c>
       <c r="B90" t="n">
         <v>103226</v>
@@ -11748,16 +11744,8 @@
           <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
@@ -11766,10 +11754,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>601399.7280807921</v>
+        <v>601209.5447587589</v>
       </c>
       <c r="R90" t="n">
-        <v>6276605.010915966</v>
+        <v>6276625.197736246</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -11796,7 +11784,7 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2016-02-07</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
@@ -11806,7 +11794,7 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2016-02-07</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
@@ -11822,28 +11810,23 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>tallskog, vid hygge</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Jan-Olof Petersson, Birgitta Andersson, Bernt Andersson, Monica Lidberg</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>56867190</v>
+        <v>58885087</v>
       </c>
       <c r="B91" t="n">
         <v>103226</v>
@@ -11886,13 +11869,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>601209.5447587589</v>
+        <v>601245.8569339331</v>
       </c>
       <c r="R91" t="n">
-        <v>6276625.197736246</v>
+        <v>6276674.499135178</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11916,7 +11899,7 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2016-02-07</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
@@ -11926,7 +11909,7 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2016-02-07</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
@@ -11946,22 +11929,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson, Birgitta Andersson, Bernt Andersson, Monica Lidberg</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>58885087</v>
+        <v>58884981</v>
       </c>
       <c r="B92" t="n">
-        <v>103226</v>
+        <v>56411</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11970,31 +11953,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>340</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
@@ -12073,10 +12060,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>58884981</v>
+        <v>58885018</v>
       </c>
       <c r="B93" t="n">
-        <v>56411</v>
+        <v>103265</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12085,35 +12072,31 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
@@ -12192,10 +12175,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>58885018</v>
+        <v>60656204</v>
       </c>
       <c r="B94" t="n">
-        <v>103265</v>
+        <v>103252</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12208,21 +12191,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221144</v>
+        <v>224098</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12235,13 +12218,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>601245.8569339331</v>
+        <v>601309.094892863</v>
       </c>
       <c r="R94" t="n">
-        <v>6276674.499135178</v>
+        <v>6276658.961086687</v>
       </c>
       <c r="S94" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12265,7 +12248,7 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
@@ -12275,7 +12258,7 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
@@ -12291,26 +12274,31 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>skogsväg</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>60656204</v>
+        <v>60656163</v>
       </c>
       <c r="B95" t="n">
-        <v>103252</v>
+        <v>97457</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12319,25 +12307,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>224098</v>
+        <v>222223</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Apera spica-venti</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) P. Beauv.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12350,10 +12338,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>601309.094892863</v>
+        <v>601222.0309980026</v>
       </c>
       <c r="R95" t="n">
-        <v>6276658.961086687</v>
+        <v>6276656.315908728</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -12409,7 +12397,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>skogsväg</t>
+          <t>igenlagt sandtag</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12427,10 +12415,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>60656163</v>
+        <v>60656115</v>
       </c>
       <c r="B96" t="n">
-        <v>97457</v>
+        <v>104188</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12443,26 +12431,38 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222223</v>
+        <v>221647</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Apera spica-venti</t>
+          <t>Galeopsis ladanum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) P. Beauv.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -12470,10 +12470,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>601222.0309980026</v>
+        <v>601211.9961727971</v>
       </c>
       <c r="R96" t="n">
-        <v>6276656.315908728</v>
+        <v>6276637.914061293</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -12547,10 +12547,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>60656115</v>
+        <v>60656187</v>
       </c>
       <c r="B97" t="n">
-        <v>104188</v>
+        <v>96312</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12559,37 +12559,29 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221647</v>
+        <v>219798</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Galeopsis ladanum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -12602,10 +12594,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>601211.9961727971</v>
+        <v>601309.094892863</v>
       </c>
       <c r="R97" t="n">
-        <v>6276637.914061293</v>
+        <v>6276658.961086687</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -12661,7 +12653,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>igenlagt sandtag</t>
+          <t>skogsväg</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12679,10 +12671,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>60656187</v>
+        <v>60675948</v>
       </c>
       <c r="B98" t="n">
-        <v>96312</v>
+        <v>103226</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12691,25 +12683,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219798</v>
+        <v>340</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12722,14 +12714,14 @@
       <c r="L98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby Tallskog, Gårdby sandhed väst, Öl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>601309.094892863</v>
+        <v>601299.5453806611</v>
       </c>
       <c r="R98" t="n">
-        <v>6276658.961086687</v>
+        <v>6276643.322301487</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -12756,7 +12748,7 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2016-07-21</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
@@ -12766,7 +12758,7 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2016-07-21</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
@@ -12782,31 +12774,26 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>skogsväg</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Birgitta Davidsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Birgitta Davidsson, Gunnar Siljestrand</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>60675948</v>
+        <v>66113422</v>
       </c>
       <c r="B99" t="n">
-        <v>103226</v>
+        <v>103265</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12815,48 +12802,48 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>340</v>
+        <v>221144</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Dörby Tallskog, Gårdby sandhed väst, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>601299.5453806611</v>
+        <v>601321.0838900616</v>
       </c>
       <c r="R99" t="n">
-        <v>6276643.322301487</v>
+        <v>6276619.076304981</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12880,7 +12867,7 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2016-07-21</t>
+          <t>2017-06-04</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
@@ -12890,7 +12877,7 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2016-07-21</t>
+          <t>2017-06-04</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
@@ -12910,19 +12897,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Birgitta Davidsson</t>
+          <t>Hans Lindfors</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Birgitta Davidsson, Gunnar Siljestrand</t>
+          <t>Hans Lindfors</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>66113422</v>
+        <v>66676941</v>
       </c>
       <c r="B100" t="n">
         <v>103265</v>
@@ -12957,25 +12944,21 @@
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, N2, Öl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>601321.0838900616</v>
+        <v>601275.9567076238</v>
       </c>
       <c r="R100" t="n">
-        <v>6276619.076304981</v>
+        <v>6276684.028379709</v>
       </c>
       <c r="S100" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12999,7 +12982,7 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
@@ -13009,7 +12992,7 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
@@ -13029,22 +13012,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Hans Lindfors</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Hans Lindfors</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>66676941</v>
+        <v>66677098</v>
       </c>
       <c r="B101" t="n">
-        <v>103265</v>
+        <v>104035</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13053,44 +13036,44 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221144</v>
+        <v>224354</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vanlig axveronika</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
+          <t>Veronica spicata subsp. spicata</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Dörby tallskog, N2, Öl</t>
+          <t>Dörby tallskog, infart, Öl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>601275.9567076238</v>
+        <v>601217.1502711129</v>
       </c>
       <c r="R101" t="n">
-        <v>6276684.028379709</v>
+        <v>6276652.896620128</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -13156,10 +13139,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>66677098</v>
+        <v>66674736</v>
       </c>
       <c r="B102" t="n">
-        <v>104035</v>
+        <v>103252</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13168,23 +13151,27 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>224354</v>
+        <v>224098</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vanlig axveronika</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Veronica spicata subsp. spicata</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
@@ -13195,17 +13182,17 @@
       <c r="L102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Dörby tallskog, infart, Öl</t>
+          <t>Dörby tallskog, N1, Öl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>601217.1502711129</v>
+        <v>601316.1849915995</v>
       </c>
       <c r="R102" t="n">
-        <v>6276652.896620128</v>
+        <v>6276639.320274717</v>
       </c>
       <c r="S102" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13271,10 +13258,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>66674736</v>
+        <v>67231376</v>
       </c>
       <c r="B103" t="n">
-        <v>103252</v>
+        <v>103226</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13283,48 +13270,48 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>224098</v>
+        <v>340</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Dörby tallskog, N1, Öl</t>
+          <t>Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>601316.1849915995</v>
+        <v>601287.8526688792</v>
       </c>
       <c r="R103" t="n">
-        <v>6276639.320274717</v>
+        <v>6276647.993758504</v>
       </c>
       <c r="S103" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13348,7 +13335,7 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2017-08-21</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
@@ -13358,7 +13345,7 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2017-08-21</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
@@ -13378,26 +13365,26 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Bert Östholm</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Bert Östholm</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>67231376</v>
+        <v>66676943</v>
       </c>
       <c r="B104" t="n">
         <v>103226</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13427,23 +13414,23 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Gårdby, Öl</t>
+          <t>Dörby tallskog, N2, Öl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>601287.8526688792</v>
+        <v>601275.9567076238</v>
       </c>
       <c r="R104" t="n">
-        <v>6276647.993758504</v>
+        <v>6276684.028379709</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13467,7 +13454,7 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2017-08-21</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
@@ -13477,7 +13464,7 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2017-08-21</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
@@ -13497,22 +13484,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Bert Östholm</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Bert Östholm</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>66676943</v>
+        <v>17012459</v>
       </c>
       <c r="B105" t="n">
-        <v>103226</v>
+        <v>41060</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13521,45 +13508,59 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>340</v>
+        <v>215656</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Rödlätt lövmätare</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Scopula rubiginata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(Hufnagel, 1767)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Dörby tallskog, N2, Öl</t>
+          <t>Gårdby sandhed, Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>601275.9567076238</v>
+        <v>601193.3068938741</v>
       </c>
       <c r="R105" t="n">
-        <v>6276684.028379709</v>
+        <v>6276727.165816098</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -13586,7 +13587,7 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
@@ -13596,7 +13597,7 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
@@ -13616,83 +13617,66 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>David Hammarberg</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>17012459</v>
+        <v>72346273</v>
       </c>
       <c r="B106" t="n">
-        <v>41060</v>
+        <v>96312</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>215656</v>
+        <v>219798</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rödlätt lövmätare</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Scopula rubiginata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Gårdby, Öl</t>
+          <t>Dörby tallskog, norr sandheden, Öl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>601193.3068938741</v>
+        <v>601268.9471723713</v>
       </c>
       <c r="R106" t="n">
-        <v>6276727.165816098</v>
+        <v>6276631.579533952</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -13719,7 +13703,7 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
@@ -13729,7 +13713,7 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
@@ -13743,25 +13727,26 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>David Hammarberg</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>72346273</v>
+        <v>60675953</v>
       </c>
       <c r="B107" t="n">
         <v>96312</v>
@@ -13796,19 +13781,22 @@
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Dörby tallskog, norr sandheden, Öl</t>
+          <t>Dörby Tallskog, Gårdby sandhed väst, Öl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>601268.9471723713</v>
+        <v>601299.5453806611</v>
       </c>
       <c r="R107" t="n">
-        <v>6276631.579533952</v>
+        <v>6276643.322301487</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -13835,7 +13823,7 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2016-07-21</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
@@ -13845,7 +13833,7 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2016-07-21</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
@@ -13859,79 +13847,75 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Birgitta Davidsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Birgitta Davidsson, Gunnar Siljestrand</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>60675953</v>
+        <v>78025941</v>
       </c>
       <c r="B108" t="n">
-        <v>96312</v>
+        <v>56632</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219798</v>
+        <v>103012</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Dörby Tallskog, Gårdby sandhed väst, Öl</t>
+          <t>N Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>601299.5453806611</v>
+        <v>601389.7593287153</v>
       </c>
       <c r="R108" t="n">
-        <v>6276643.322301487</v>
+        <v>6276812.788659053</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13955,22 +13939,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2016-07-21</t>
+          <t>2019-05-18</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2016-07-21</t>
+          <t>2019-05-18</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13985,69 +13969,77 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Birgitta Davidsson</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Birgitta Davidsson, Gunnar Siljestrand</t>
+          <t>Linda Johannesson, Guillaume Mercier, Alexandra Johansson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>78025941</v>
+        <v>78964858</v>
       </c>
       <c r="B109" t="n">
-        <v>56632</v>
+        <v>96370</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103012</v>
+        <v>219875</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>N Gårdby, Öl</t>
+          <t>Dörrby, Tallskog, Öl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>601389.7593287153</v>
+        <v>601273.5754416483</v>
       </c>
       <c r="R109" t="n">
-        <v>6276812.788659053</v>
+        <v>6276714.238253681</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -14071,22 +14063,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2019-05-18</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2019-05-18</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14095,83 +14087,80 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>joakim johansson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Guillaume Mercier, Alexandra Johansson</t>
+          <t>joakim johansson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>78964858</v>
+        <v>79087782</v>
       </c>
       <c r="B110" t="n">
-        <v>96370</v>
+        <v>103226</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219875</v>
+        <v>340</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Dörrby, Tallskog, Öl</t>
+          <t>Radarmasten, Öl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>601273.5754416483</v>
+        <v>601269.2336148486</v>
       </c>
       <c r="R110" t="n">
-        <v>6276714.238253681</v>
+        <v>6276642.592832611</v>
       </c>
       <c r="S110" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -14195,7 +14184,7 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr">
@@ -14205,7 +14194,7 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
@@ -14226,22 +14215,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>joakim johansson</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>joakim johansson</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>79087782</v>
+        <v>79945652</v>
       </c>
       <c r="B111" t="n">
-        <v>103226</v>
+        <v>96334</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -14250,49 +14239,49 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>340</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Radarmasten, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>601269.2336148486</v>
+        <v>601266.95441455</v>
       </c>
       <c r="R111" t="n">
-        <v>6276642.592832611</v>
+        <v>6276622.72643963</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -14316,7 +14305,7 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
+          <t>2010-08-07</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
@@ -14326,7 +14315,7 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
+          <t>2010-08-07</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
@@ -14347,22 +14336,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>79945652</v>
+        <v>81819854</v>
       </c>
       <c r="B112" t="n">
-        <v>96334</v>
+        <v>103226</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14371,30 +14360,34 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>340</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
@@ -14403,14 +14396,14 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Gårdby Telemast N, Öl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>601266.95441455</v>
+        <v>601271.7150834949</v>
       </c>
       <c r="R112" t="n">
-        <v>6276622.72643963</v>
+        <v>6276699.885395006</v>
       </c>
       <c r="S112" t="n">
         <v>50</v>
@@ -14437,7 +14430,7 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2010-08-07</t>
+          <t>2020-01-19</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr">
@@ -14447,7 +14440,7 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2010-08-07</t>
+          <t>2020-01-19</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
@@ -14468,22 +14461,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>Birgitta Andersson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t xml:space="preserve">Birgitta Andersson, Gun Jonasson </t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>81819854</v>
+        <v>86801212</v>
       </c>
       <c r="B113" t="n">
-        <v>103226</v>
+        <v>103265</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14492,53 +14485,49 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>340</v>
+        <v>221144</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Gårdby Telemast N, Öl</t>
+          <t>Dörbytallskog, Öl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>601271.7150834949</v>
+        <v>601246.0335219763</v>
       </c>
       <c r="R113" t="n">
-        <v>6276699.885395006</v>
+        <v>6276644.235934953</v>
       </c>
       <c r="S113" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14562,7 +14551,7 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2020-01-19</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="Z113" t="inlineStr">
@@ -14572,7 +14561,7 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2020-01-19</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
@@ -14590,25 +14579,30 @@
       <c r="AG113" t="b">
         <v>0</v>
       </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>gles tallskog</t>
+        </is>
+      </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Birgitta Andersson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birgitta Andersson, Gun Jonasson </t>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>86801212</v>
+        <v>86801227</v>
       </c>
       <c r="B114" t="n">
-        <v>103265</v>
+        <v>96313</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14621,30 +14615,22 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221144</v>
+        <v>223609</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
@@ -14653,10 +14639,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>601246.0335219763</v>
+        <v>601308.0588468611</v>
       </c>
       <c r="R114" t="n">
-        <v>6276644.235934953</v>
+        <v>6276656.184557838</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14731,10 +14717,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>86801227</v>
+        <v>86801215</v>
       </c>
       <c r="B115" t="n">
-        <v>96313</v>
+        <v>103226</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14743,26 +14729,34 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>223609</v>
+        <v>340</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+          <t>Chimaphila umbellata</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
@@ -14771,10 +14765,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>601308.0588468611</v>
+        <v>601246.0335219763</v>
       </c>
       <c r="R115" t="n">
-        <v>6276656.184557838</v>
+        <v>6276644.235934953</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -14849,10 +14843,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>86801215</v>
+        <v>86918873</v>
       </c>
       <c r="B116" t="n">
-        <v>103226</v>
+        <v>41690</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14861,49 +14855,58 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>340</v>
+        <v>215920</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Kalkfly</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Tyta luctuosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>ljusfälla</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Dörbytallskog, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>601246.0335219763</v>
+        <v>601266.95441455</v>
       </c>
       <c r="R116" t="n">
-        <v>6276644.235934953</v>
+        <v>6276622.72643963</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14927,7 +14930,7 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="Z116" t="inlineStr">
@@ -14937,7 +14940,7 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
@@ -14955,30 +14958,25 @@
       <c r="AG116" t="b">
         <v>0</v>
       </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
-      </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>86918873</v>
+        <v>88752757</v>
       </c>
       <c r="B117" t="n">
-        <v>41690</v>
+        <v>103226</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14987,58 +14985,53 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>215920</v>
+        <v>340</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kalkfly</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tyta luctuosa</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>ljusfälla</t>
-        </is>
-      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>601266.95441455</v>
+        <v>601266.0715903379</v>
       </c>
       <c r="R117" t="n">
-        <v>6276622.72643963</v>
+        <v>6276705.252717341</v>
       </c>
       <c r="S117" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -15062,7 +15055,7 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2020-07-19</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
@@ -15072,7 +15065,7 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2020-07-19</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
@@ -15093,22 +15086,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>Margareta Ohné</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>Margareta Ohné</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>88752757</v>
+        <v>94471286</v>
       </c>
       <c r="B118" t="n">
-        <v>103226</v>
+        <v>96370</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15117,33 +15110,28 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>340</v>
+        <v>219875</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -15153,17 +15141,17 @@
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Vägkant norr om Gårdby sanshed, Öl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>601266.0715903379</v>
+        <v>601202.9357894144</v>
       </c>
       <c r="R118" t="n">
-        <v>6276705.252717341</v>
+        <v>6276670.715239353</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -15187,22 +15175,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2020-07-19</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2020-07-19</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15218,22 +15206,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Margareta Ohné</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Margareta Ohné</t>
+          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>94471286</v>
+        <v>94467631</v>
       </c>
       <c r="B119" t="n">
-        <v>96370</v>
+        <v>103226</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15242,25 +15230,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219875</v>
+        <v>340</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15273,14 +15261,14 @@
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Vägkant norr om Gårdby sanshed, Öl</t>
+          <t>Dörby tallskog, norr sandheden, Öl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>601202.9357894144</v>
+        <v>601268.9471723713</v>
       </c>
       <c r="R119" t="n">
-        <v>6276670.715239353</v>
+        <v>6276631.579533952</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -15312,7 +15300,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15322,7 +15310,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15350,10 +15338,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>94467631</v>
+        <v>94467626</v>
       </c>
       <c r="B120" t="n">
-        <v>103226</v>
+        <v>103265</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15362,33 +15350,29 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>340</v>
+        <v>221144</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
@@ -15470,10 +15454,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>94467626</v>
+        <v>94467618</v>
       </c>
       <c r="B121" t="n">
-        <v>103265</v>
+        <v>96312</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15486,21 +15470,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15509,14 +15493,14 @@
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Dörby tallskog, norr sandheden, Öl</t>
+          <t>Dörby tallskog, N1, Öl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>601268.9471723713</v>
+        <v>601316.1849915995</v>
       </c>
       <c r="R121" t="n">
-        <v>6276631.579533952</v>
+        <v>6276639.320274717</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15586,10 +15570,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>94467618</v>
+        <v>95770410</v>
       </c>
       <c r="B122" t="n">
-        <v>96312</v>
+        <v>103226</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15598,44 +15582,53 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219798</v>
+        <v>340</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Dörby tallskog, N1, Öl</t>
+          <t>Dörby söderut, Öl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>601316.1849915995</v>
+        <v>601433.1557138723</v>
       </c>
       <c r="R122" t="n">
-        <v>6276639.320274717</v>
+        <v>6276636.634531654</v>
       </c>
       <c r="S122" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15659,7 +15652,7 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr">
@@ -15669,7 +15662,7 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
@@ -15687,25 +15680,30 @@
       <c r="AG122" t="b">
         <v>0</v>
       </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>gallrad tallskog</t>
+        </is>
+      </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>95770410</v>
+        <v>99255660</v>
       </c>
       <c r="B123" t="n">
-        <v>103226</v>
+        <v>103265</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15714,35 +15712,35 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>340</v>
+        <v>221144</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -15750,17 +15748,17 @@
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Dörby söderut, Öl</t>
+          <t>Gårdby-Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>601433.1557138723</v>
+        <v>601321.2692618417</v>
       </c>
       <c r="R123" t="n">
-        <v>6276636.634531654</v>
+        <v>6276611.37623784</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15784,7 +15782,7 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr">
@@ -15794,7 +15792,7 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
@@ -15814,7 +15812,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>gallrad tallskog</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -15825,14 +15823,14 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>99255660</v>
+        <v>99255628</v>
       </c>
       <c r="B124" t="n">
         <v>103265</v>
@@ -15867,7 +15865,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -15884,10 +15882,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>601321.2692618417</v>
+        <v>601239.1951351715</v>
       </c>
       <c r="R124" t="n">
-        <v>6276611.37623784</v>
+        <v>6276653.426849021</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -15962,10 +15960,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>99255628</v>
+        <v>99257266</v>
       </c>
       <c r="B125" t="n">
-        <v>103265</v>
+        <v>103226</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15974,53 +15972,45 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221144</v>
+        <v>340</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Gårdby-Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>601239.1951351715</v>
+        <v>601239.7991777682</v>
       </c>
       <c r="R125" t="n">
-        <v>6276653.426849021</v>
+        <v>6276651.240106804</v>
       </c>
       <c r="S125" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -16044,22 +16034,22 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
+          <t>2022-03-19</t>
         </is>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
+          <t>2022-03-19</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -16072,30 +16062,25 @@
       <c r="AG125" t="b">
         <v>0</v>
       </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Erik F Nordberg</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Erik F Nordberg, Karin Andersson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>99257266</v>
+        <v>101612360</v>
       </c>
       <c r="B126" t="n">
-        <v>103226</v>
+        <v>103265</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -16104,30 +16089,34 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>340</v>
+        <v>221144</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
@@ -16166,22 +16155,22 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2022-03-19</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2022-03-19</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -16209,10 +16198,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>101612360</v>
+        <v>102470725</v>
       </c>
       <c r="B127" t="n">
-        <v>103265</v>
+        <v>40957</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -16221,49 +16210,58 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221144</v>
+        <v>215768</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svartbrun klaffmätare</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Philereme transversata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Hufnagel, 1767)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>601239.7991777682</v>
+        <v>601266.95441455</v>
       </c>
       <c r="R127" t="n">
-        <v>6276651.240106804</v>
+        <v>6276622.72643963</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -16287,7 +16285,7 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
@@ -16297,7 +16295,7 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
@@ -16318,22 +16316,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Erik F Nordberg</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Erik F Nordberg, Karin Andersson</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>102470725</v>
+        <v>102469855</v>
       </c>
       <c r="B128" t="n">
-        <v>40957</v>
+        <v>41685</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -16342,25 +16340,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>215768</v>
+        <v>100892</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svartbrun klaffmätare</t>
+          <t>Åkervindefly</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Philereme transversata</t>
+          <t>Acontia trabealis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -16460,10 +16458,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>102469855</v>
+        <v>102470713</v>
       </c>
       <c r="B129" t="n">
-        <v>41685</v>
+        <v>43085</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -16472,25 +16470,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100892</v>
+        <v>215481</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Åkervindefly</t>
+          <t>Dubbelbandat ljusmott</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Acontia trabealis</t>
+          <t>Pyrausta ostrinalis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Hübner, 1796)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -16590,10 +16588,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>102470713</v>
+        <v>102470721</v>
       </c>
       <c r="B130" t="n">
-        <v>43085</v>
+        <v>40969</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -16606,28 +16604,24 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>215481</v>
+        <v>215766</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dubbelbandat ljusmott</t>
+          <t>Vägtornsmätare</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pyrausta ostrinalis</t>
+          <t>Triphosa dubitata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hübner, 1796)</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
@@ -16720,10 +16714,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>102470721</v>
+        <v>102470028</v>
       </c>
       <c r="B131" t="n">
-        <v>40969</v>
+        <v>40753</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -16736,24 +16730,28 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>215766</v>
+        <v>215683</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vägtornsmätare</t>
+          <t>Mellanmätare</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Triphosa dubitata</t>
+          <t>Phibalapteryx virgata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Hufnagel, 1767)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
@@ -16846,70 +16844,55 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>102470028</v>
+        <v>101733531</v>
       </c>
       <c r="B132" t="n">
-        <v>40753</v>
+        <v>103226</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>215683</v>
+        <v>340</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mellanmätare</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phibalapteryx virgata</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Mörbylånga, Öl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>601266.95441455</v>
+        <v>601387.200422315</v>
       </c>
       <c r="R132" t="n">
-        <v>6276622.72643963</v>
+        <v>6276644.332355867</v>
       </c>
       <c r="S132" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16933,7 +16916,7 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2022-06-18</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
@@ -16943,7 +16926,7 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2022-06-18</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
@@ -16957,26 +16940,25 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>Marie Glahn</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>Marie Glahn</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>101733531</v>
+        <v>102189039</v>
       </c>
       <c r="B133" t="n">
         <v>103226</v>
@@ -17010,7 +16992,11 @@
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -17018,10 +17004,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>601387.200422315</v>
+        <v>601249.0756290605</v>
       </c>
       <c r="R133" t="n">
-        <v>6276644.332355867</v>
+        <v>6276655.315488469</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -17048,22 +17034,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2022-06-18</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2022-06-18</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -17078,71 +17064,77 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Marie Glahn</t>
+          <t>Kjell Stålberg</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Marie Glahn</t>
+          <t>Kjell Stålberg, Carolina Stålberg</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>102189039</v>
+        <v>110458149</v>
       </c>
       <c r="B134" t="n">
-        <v>103226</v>
+        <v>96312</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>340</v>
+        <v>219798</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Mörbylånga, Öl</t>
+          <t>Dörby tallskog, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>601249.0756290605</v>
+        <v>601270.4285005968</v>
       </c>
       <c r="R134" t="n">
-        <v>6276655.315488469</v>
+        <v>6276638.76934504</v>
       </c>
       <c r="S134" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -17166,22 +17158,22 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -17190,28 +17182,29 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Kjell Stålberg</t>
+          <t>Hasse Andersson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Kjell Stålberg, Carolina Stålberg</t>
+          <t>Hasse Andersson, Birgit Svensson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>110458149</v>
+        <v>110458137</v>
       </c>
       <c r="B135" t="n">
-        <v>96312</v>
+        <v>103249</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -17220,32 +17213,28 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219798</v>
+        <v>340</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
@@ -17333,14 +17322,14 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>110458137</v>
+        <v>117212950</v>
       </c>
       <c r="B136" t="n">
-        <v>103249</v>
+        <v>104890</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17377,14 +17366,14 @@
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Radiomasten, Dörby, Öl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>601270.4285005968</v>
+        <v>601342</v>
       </c>
       <c r="R136" t="n">
-        <v>6276638.76934504</v>
+        <v>6276629</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -17411,22 +17400,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -17442,70 +17421,65 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Liselotte Andersson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Hasse Andersson, Birgit Svensson</t>
+          <t>Liselotte Andersson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>117212950</v>
+        <v>121707046</v>
       </c>
       <c r="B137" t="n">
-        <v>104890</v>
+        <v>91372</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>340</v>
+        <v>6031</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Radiomasten, Dörby, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>601342</v>
+        <v>601443</v>
       </c>
       <c r="R137" t="n">
-        <v>6276629</v>
+        <v>6276610</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -17532,12 +17506,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -17550,25 +17524,30 @@
       <c r="AG137" t="b">
         <v>0</v>
       </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>vid basen av tall, sandigt</t>
+        </is>
+      </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Liselotte Andersson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Liselotte Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121707046</v>
+        <v>121707142</v>
       </c>
       <c r="B138" t="n">
-        <v>91372</v>
+        <v>105215</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -17577,41 +17556,50 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6031</v>
+        <v>340</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Gårdby-Dörby tallskog (21), Öl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>601443</v>
+        <v>601430</v>
       </c>
       <c r="R138" t="n">
-        <v>6276610</v>
+        <v>6276628</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -17636,6 +17624,11 @@
           <t>Norra Möckleby</t>
         </is>
       </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>Hö-Mör-3071</t>
+        </is>
+      </c>
       <c r="Y138" t="inlineStr">
         <is>
           <t>2024-12-21</t>
@@ -17644,6 +17637,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2024-12-21</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>alldeles väster om stig</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -17658,7 +17656,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>vid basen av tall, sandigt</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -17673,136 +17671,6 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>121707142</v>
-      </c>
-      <c r="B139" t="n">
-        <v>105215</v>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E139" t="n">
-        <v>340</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Ryl</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Chimaphila umbellata</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="P139" t="inlineStr">
-        <is>
-          <t>Gårdby-Dörby tallskog (21), Öl</t>
-        </is>
-      </c>
-      <c r="Q139" t="n">
-        <v>601430</v>
-      </c>
-      <c r="R139" t="n">
-        <v>6276628</v>
-      </c>
-      <c r="S139" t="n">
-        <v>10</v>
-      </c>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t>Mörbylånga</t>
-        </is>
-      </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W139" t="inlineStr">
-        <is>
-          <t>Norra Möckleby</t>
-        </is>
-      </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>Hö-Mör-3071</t>
-        </is>
-      </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>2024-12-21</t>
-        </is>
-      </c>
-      <c r="AA139" t="inlineStr">
-        <is>
-          <t>2024-12-21</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>alldeles väster om stig</t>
-        </is>
-      </c>
-      <c r="AD139" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE139" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF139" t="inlineStr"/>
-      <c r="AG139" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
-      </c>
-      <c r="AT139" t="inlineStr"/>
-      <c r="AW139" t="inlineStr">
-        <is>
-          <t>Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AX139" t="inlineStr">
-        <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -3680,7 +3680,7 @@
         <v>134260</v>
       </c>
       <c r="B26" t="n">
-        <v>105357</v>
+        <v>105432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>126780833</v>
       </c>
       <c r="B139" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>127081837</v>
       </c>
       <c r="B140" t="n">
-        <v>98340</v>
+        <v>98415</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -3680,7 +3680,7 @@
         <v>134260</v>
       </c>
       <c r="B26" t="n">
-        <v>105432</v>
+        <v>105438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>126780833</v>
       </c>
       <c r="B139" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>127081837</v>
       </c>
       <c r="B140" t="n">
-        <v>98415</v>
+        <v>98421</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -3680,7 +3680,7 @@
         <v>134260</v>
       </c>
       <c r="B26" t="n">
-        <v>105438</v>
+        <v>105439</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>126780833</v>
       </c>
       <c r="B139" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>127081837</v>
       </c>
       <c r="B140" t="n">
-        <v>98421</v>
+        <v>98422</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -3680,7 +3680,7 @@
         <v>134260</v>
       </c>
       <c r="B26" t="n">
-        <v>105439</v>
+        <v>105445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>126780833</v>
       </c>
       <c r="B139" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>127081837</v>
       </c>
       <c r="B140" t="n">
-        <v>98422</v>
+        <v>98426</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -17765,7 +17765,7 @@
         <v>127081837</v>
       </c>
       <c r="B140" t="n">
-        <v>98426</v>
+        <v>98427</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -17765,7 +17765,7 @@
         <v>127081837</v>
       </c>
       <c r="B140" t="n">
-        <v>98427</v>
+        <v>98429</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -17765,7 +17765,7 @@
         <v>127081837</v>
       </c>
       <c r="B140" t="n">
-        <v>98429</v>
+        <v>98435</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -17765,7 +17765,7 @@
         <v>127081837</v>
       </c>
       <c r="B140" t="n">
-        <v>98435</v>
+        <v>98438</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY140"/>
+  <dimension ref="A1:AY141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17876,6 +17876,121 @@
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>129903845</v>
+      </c>
+      <c r="B141" t="n">
+        <v>105812</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>340</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Ryl</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Chimaphila umbellata</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Galgrör, Öl</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>601248</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6276636</v>
+      </c>
+      <c r="S141" t="n">
+        <v>25</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Ieva Mardega, Håkan Örtman</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -17881,7 +17881,7 @@
         <v>129903845</v>
       </c>
       <c r="B141" t="n">
-        <v>105812</v>
+        <v>105817</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -17881,7 +17881,7 @@
         <v>129903845</v>
       </c>
       <c r="B141" t="n">
-        <v>105817</v>
+        <v>105821</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -17881,7 +17881,7 @@
         <v>129903845</v>
       </c>
       <c r="B141" t="n">
-        <v>105821</v>
+        <v>105824</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -17881,7 +17881,7 @@
         <v>129903845</v>
       </c>
       <c r="B141" t="n">
-        <v>105824</v>
+        <v>105825</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -17881,7 +17881,7 @@
         <v>129903845</v>
       </c>
       <c r="B141" t="n">
-        <v>105825</v>
+        <v>105842</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -17881,7 +17881,7 @@
         <v>129903845</v>
       </c>
       <c r="B141" t="n">
-        <v>105858</v>
+        <v>105861</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -3680,7 +3680,7 @@
         <v>134260</v>
       </c>
       <c r="B26" t="n">
-        <v>105445</v>
+        <v>105432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>126780833</v>
       </c>
       <c r="B139" t="n">
-        <v>105484</v>
+        <v>105471</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>127081837</v>
       </c>
       <c r="B140" t="n">
-        <v>98438</v>
+        <v>98415</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>129903845</v>
       </c>
       <c r="B141" t="n">
-        <v>105861</v>
+        <v>105948</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -3680,7 +3680,7 @@
         <v>134260</v>
       </c>
       <c r="B26" t="n">
-        <v>105432</v>
+        <v>105445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>126780833</v>
       </c>
       <c r="B139" t="n">
-        <v>105471</v>
+        <v>105484</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>127081837</v>
       </c>
       <c r="B140" t="n">
-        <v>98415</v>
+        <v>98438</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>129903845</v>
       </c>
       <c r="B141" t="n">
-        <v>105948</v>
+        <v>105861</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -15466,7 +15466,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Kjell Stålberg, Carolina Stålberg</t>
+          <t>Carolina Stålberg, Kjell Stålberg</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -15466,7 +15466,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Carolina Stålberg, Kjell Stålberg</t>
+          <t>Kjell Stålberg, Carolina Stålberg</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY183"/>
+  <dimension ref="A1:AY185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13392,50 +13392,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>3025627</v>
+        <v>135288243</v>
       </c>
       <c r="B114" t="n">
-        <v>99118</v>
+        <v>109896</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>220204</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Gårdby N., Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>601256</v>
+        <v>601301</v>
       </c>
       <c r="R114" t="n">
-        <v>6276584</v>
+        <v>6276866</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13462,17 +13457,17 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2007-08-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2007-08-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Delvis överblommad</t>
+          <t>3 plantor i blom på släntkrön 2m från beläggningen(+6plantor utanför vägområdet)</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13483,32 +13478,27 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>3026664</v>
+        <v>3025627</v>
       </c>
       <c r="B115" t="n">
         <v>99118</v>
@@ -13537,19 +13527,24 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Övre Ålebäck N, Öl</t>
+          <t>Gårdby N., Öl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>601247</v>
+        <v>601256</v>
       </c>
       <c r="R115" t="n">
-        <v>6276600</v>
+        <v>6276584</v>
       </c>
       <c r="S115" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13573,12 +13568,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2007-08-10</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2007-08-10</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Delvis överblommad</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13598,12 +13598,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -13614,7 +13614,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>3029119</v>
+        <v>3026664</v>
       </c>
       <c r="B116" t="n">
         <v>99118</v>
@@ -13645,14 +13645,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Dörby S, Öl</t>
+          <t>Övre Ålebäck N, Öl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>601245</v>
+        <v>601247</v>
       </c>
       <c r="R116" t="n">
-        <v>6276602</v>
+        <v>6276600</v>
       </c>
       <c r="S116" t="n">
         <v>50</v>
@@ -13679,12 +13679,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2009-05-05</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2009-05-05</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13720,7 +13720,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>3029132</v>
+        <v>3029119</v>
       </c>
       <c r="B117" t="n">
         <v>99118</v>
@@ -13749,24 +13749,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby S, Öl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>601226</v>
+        <v>601245</v>
       </c>
       <c r="R117" t="n">
-        <v>6276599</v>
+        <v>6276602</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13790,12 +13785,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2009-05-05</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2009-05-05</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13809,18 +13804,18 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>gles tallskog med enstaka lövträd</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -13831,7 +13826,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>3029133</v>
+        <v>3029132</v>
       </c>
       <c r="B118" t="n">
         <v>99118</v>
@@ -13860,16 +13855,21 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>601222</v>
+        <v>601226</v>
       </c>
       <c r="R118" t="n">
-        <v>6276594</v>
+        <v>6276599</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13902,11 +13902,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2009-06-03</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>stort bestånd</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13942,7 +13937,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>3029134</v>
+        <v>3029133</v>
       </c>
       <c r="B119" t="n">
         <v>99118</v>
@@ -13977,10 +13972,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>601306</v>
+        <v>601222</v>
       </c>
       <c r="R119" t="n">
-        <v>6276718</v>
+        <v>6276594</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -14013,6 +14008,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2009-06-03</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>stort bestånd</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14048,7 +14048,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>3029135</v>
+        <v>3029134</v>
       </c>
       <c r="B120" t="n">
         <v>99118</v>
@@ -14083,10 +14083,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>601299</v>
+        <v>601306</v>
       </c>
       <c r="R120" t="n">
-        <v>6276716</v>
+        <v>6276718</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -14154,7 +14154,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>3035150</v>
+        <v>3029135</v>
       </c>
       <c r="B121" t="n">
         <v>99118</v>
@@ -14182,31 +14182,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>tallskog syd Dörby, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>601317</v>
+        <v>601299</v>
       </c>
       <c r="R121" t="n">
-        <v>6276750</v>
+        <v>6276716</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -14233,17 +14219,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>hotas av avverkning</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14257,7 +14238,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>gles tallskog med enstaka lövträd</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14279,7 +14260,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>3035151</v>
+        <v>3035150</v>
       </c>
       <c r="B122" t="n">
         <v>99118</v>
@@ -14307,10 +14288,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -14319,10 +14309,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>601326</v>
+        <v>601317</v>
       </c>
       <c r="R122" t="n">
-        <v>6276771</v>
+        <v>6276750</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14395,7 +14385,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>3035398</v>
+        <v>3035151</v>
       </c>
       <c r="B123" t="n">
         <v>99118</v>
@@ -14431,14 +14421,14 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>tallskog mellan Dörby-Gårdby, Öl</t>
+          <t>tallskog syd Dörby, Öl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>601300</v>
+        <v>601326</v>
       </c>
       <c r="R123" t="n">
-        <v>6276710</v>
+        <v>6276771</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14465,17 +14455,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>ej blommande</t>
+          <t>hotas av avverkning</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14489,7 +14479,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -14511,7 +14501,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>3035399</v>
+        <v>3035398</v>
       </c>
       <c r="B124" t="n">
         <v>99118</v>
@@ -14551,10 +14541,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>601211</v>
+        <v>601300</v>
       </c>
       <c r="R124" t="n">
-        <v>6276590</v>
+        <v>6276710</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -14591,7 +14581,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>täckt av ris för avverkning</t>
+          <t>ej blommande</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14627,7 +14617,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>3042763</v>
+        <v>3035399</v>
       </c>
       <c r="B125" t="n">
         <v>99118</v>
@@ -14655,31 +14645,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Öl</t>
+          <t>tallskog mellan Dörby-Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>601285</v>
+        <v>601211</v>
       </c>
       <c r="R125" t="n">
-        <v>6276690</v>
+        <v>6276590</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14706,17 +14687,17 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>5 blommande, 50 bladrosetter</t>
+          <t>täckt av ris för avverkning</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14752,7 +14733,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>3042764</v>
+        <v>3042763</v>
       </c>
       <c r="B126" t="n">
         <v>99118</v>
@@ -14782,7 +14763,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14801,10 +14782,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>601259</v>
+        <v>601285</v>
       </c>
       <c r="R126" t="n">
-        <v>6276711</v>
+        <v>6276690</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14841,7 +14822,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>1 blommande, 2 bestånd, 14 bladrosetter</t>
+          <t>5 blommande, 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14877,7 +14858,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>3042765</v>
+        <v>3042764</v>
       </c>
       <c r="B127" t="n">
         <v>99118</v>
@@ -14907,7 +14888,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14926,10 +14907,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>601330</v>
+        <v>601259</v>
       </c>
       <c r="R127" t="n">
-        <v>6276690</v>
+        <v>6276711</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14966,7 +14947,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>4blommande, 55 bladrosetter, 2 bestånd</t>
+          <t>1 blommande, 2 bestånd, 14 bladrosetter</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15002,7 +14983,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>3042766</v>
+        <v>3042765</v>
       </c>
       <c r="B128" t="n">
         <v>99118</v>
@@ -15032,12 +15013,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -15051,10 +15032,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>601317</v>
+        <v>601330</v>
       </c>
       <c r="R128" t="n">
-        <v>6276649</v>
+        <v>6276690</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -15091,7 +15072,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>9 blommande, 50 bladrosetter</t>
+          <t>4blommande, 55 bladrosetter, 2 bestånd</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15127,7 +15108,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>3052277</v>
+        <v>3042766</v>
       </c>
       <c r="B129" t="n">
         <v>99118</v>
@@ -15157,29 +15138,29 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Dörby, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>601279</v>
+        <v>601317</v>
       </c>
       <c r="R129" t="n">
-        <v>6276712</v>
+        <v>6276649</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -15206,12 +15187,17 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2011-08-31</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2011-08-31</t>
+          <t>2011-07-17</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>9 blommande, 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15225,18 +15211,18 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Sandtallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Veronika Johansson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Veronika Johansson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -15247,7 +15233,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>79945652</v>
+        <v>3052277</v>
       </c>
       <c r="B130" t="n">
         <v>99118</v>
@@ -15275,28 +15261,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Dörby, Öl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>601267</v>
+        <v>601279</v>
       </c>
       <c r="R130" t="n">
-        <v>6276623</v>
+        <v>6276712</v>
       </c>
       <c r="S130" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15320,12 +15312,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2010-08-07</t>
+          <t>2011-08-31</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2010-08-07</t>
+          <t>2011-08-31</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15334,19 +15326,23 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>Veronika Johansson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>Veronika Johansson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -15357,10 +15353,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>134863685</v>
+        <v>79945652</v>
       </c>
       <c r="B131" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15385,29 +15381,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Mörbylånga, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>601249</v>
+        <v>601267</v>
       </c>
       <c r="R131" t="n">
-        <v>6276655</v>
+        <v>6276623</v>
       </c>
       <c r="S131" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15431,22 +15426,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>07:53</t>
+          <t>2010-08-07</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>07:53</t>
+          <t>2010-08-07</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15455,71 +15440,80 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Kjell Stålberg</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Carolina Stålberg, Kjell Stålberg</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr"/>
+          <t>Christer Klingstedt</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>3421658</v>
+        <v>134863685</v>
       </c>
       <c r="B132" t="n">
-        <v>106243</v>
+        <v>99195</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Övre Ålebäck N, Öl</t>
+          <t>Mörbylånga, Öl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>601247</v>
+        <v>601249</v>
       </c>
       <c r="R132" t="n">
-        <v>6276600</v>
+        <v>6276655</v>
       </c>
       <c r="S132" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15543,12 +15537,22 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15559,32 +15563,23 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Kjell Stålberg</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Kjell Stålberg, Carolina Stålberg</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>3424445</v>
+        <v>3421658</v>
       </c>
       <c r="B133" t="n">
         <v>106243</v>
@@ -15615,22 +15610,22 @@
       <c r="I133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>tallskog syd Dörby, Öl</t>
+          <t>Övre Ålebäck N, Öl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>601286</v>
+        <v>601247</v>
       </c>
       <c r="R133" t="n">
-        <v>6276626</v>
+        <v>6276600</v>
       </c>
       <c r="S133" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15654,12 +15649,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15673,18 +15668,18 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -15695,7 +15690,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>3424446</v>
+        <v>3424445</v>
       </c>
       <c r="B134" t="n">
         <v>106243</v>
@@ -15735,10 +15730,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>601257</v>
+        <v>601286</v>
       </c>
       <c r="R134" t="n">
-        <v>6276610</v>
+        <v>6276626</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -15806,7 +15801,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>3424453</v>
+        <v>3424446</v>
       </c>
       <c r="B135" t="n">
         <v>106243</v>
@@ -15837,19 +15832,19 @@
       <c r="I135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>tallskog mellan Dörby-Gårdby, Öl</t>
+          <t>tallskog syd Dörby, Öl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>601243</v>
+        <v>601257</v>
       </c>
       <c r="R135" t="n">
-        <v>6276628</v>
+        <v>6276610</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -15876,12 +15871,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15895,7 +15890,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15917,7 +15912,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>3425394</v>
+        <v>3424453</v>
       </c>
       <c r="B136" t="n">
         <v>106243</v>
@@ -15953,14 +15948,14 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Öl</t>
+          <t>tallskog mellan Dörby-Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>601237</v>
+        <v>601243</v>
       </c>
       <c r="R136" t="n">
-        <v>6276677</v>
+        <v>6276628</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15987,12 +15982,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16028,7 +16023,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>7176385</v>
+        <v>3425394</v>
       </c>
       <c r="B137" t="n">
         <v>106243</v>
@@ -16057,19 +16052,21 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>601266</v>
+        <v>601237</v>
       </c>
       <c r="R137" t="n">
-        <v>6276652</v>
+        <v>6276677</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -16096,12 +16093,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16112,16 +16109,21 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>tallskog på sand</t>
+        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -16132,7 +16134,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>16038157</v>
+        <v>7176385</v>
       </c>
       <c r="B138" t="n">
         <v>106243</v>
@@ -16166,14 +16168,14 @@
       <c r="L138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>601227</v>
+        <v>601266</v>
       </c>
       <c r="R138" t="n">
-        <v>6276593</v>
+        <v>6276652</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -16200,12 +16202,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16216,11 +16218,6 @@
       </c>
       <c r="AG138" t="b">
         <v>0</v>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
@@ -16230,7 +16227,7 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -16241,7 +16238,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>16038171</v>
+        <v>16038157</v>
       </c>
       <c r="B139" t="n">
         <v>106243</v>
@@ -16271,11 +16268,7 @@
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -16283,10 +16276,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>601245</v>
+        <v>601227</v>
       </c>
       <c r="R139" t="n">
-        <v>6276638</v>
+        <v>6276593</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -16354,7 +16347,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>16038187</v>
+        <v>16038171</v>
       </c>
       <c r="B140" t="n">
         <v>106243</v>
@@ -16384,7 +16377,11 @@
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -16392,10 +16389,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>601269</v>
+        <v>601245</v>
       </c>
       <c r="R140" t="n">
-        <v>6276641</v>
+        <v>6276638</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -16463,7 +16460,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>16038207</v>
+        <v>16038187</v>
       </c>
       <c r="B141" t="n">
         <v>106243</v>
@@ -16501,10 +16498,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>601489</v>
+        <v>601269</v>
       </c>
       <c r="R141" t="n">
-        <v>6276715</v>
+        <v>6276641</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -16572,7 +16569,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>16038421</v>
+        <v>16038207</v>
       </c>
       <c r="B142" t="n">
         <v>106243</v>
@@ -16610,10 +16607,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>601286</v>
+        <v>601489</v>
       </c>
       <c r="R142" t="n">
-        <v>6276666</v>
+        <v>6276715</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -16681,7 +16678,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>16065773</v>
+        <v>16038421</v>
       </c>
       <c r="B143" t="n">
         <v>106243</v>
@@ -16719,10 +16716,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>601303</v>
+        <v>601286</v>
       </c>
       <c r="R143" t="n">
-        <v>6276692</v>
+        <v>6276666</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -16749,12 +16746,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16768,7 +16765,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>
@@ -16779,7 +16776,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -16790,7 +16787,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>17204730</v>
+        <v>16065773</v>
       </c>
       <c r="B144" t="n">
         <v>106243</v>
@@ -16820,22 +16817,18 @@
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>601400</v>
+        <v>601303</v>
       </c>
       <c r="R144" t="n">
-        <v>6276601</v>
+        <v>6276692</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -16862,12 +16855,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2015-03-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2015-03-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16881,7 +16874,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -16903,7 +16896,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>54444054</v>
+        <v>17204730</v>
       </c>
       <c r="B145" t="n">
         <v>106243</v>
@@ -16933,18 +16926,22 @@
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>601271</v>
+        <v>601400</v>
       </c>
       <c r="R145" t="n">
-        <v>6276655</v>
+        <v>6276601</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -16971,12 +16968,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16990,7 +16987,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -17012,7 +17009,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>54444133</v>
+        <v>54444054</v>
       </c>
       <c r="B146" t="n">
         <v>106243</v>
@@ -17050,10 +17047,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>601309</v>
+        <v>601271</v>
       </c>
       <c r="R146" t="n">
-        <v>6276695</v>
+        <v>6276655</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -17121,7 +17118,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>54444175</v>
+        <v>54444133</v>
       </c>
       <c r="B147" t="n">
         <v>106243</v>
@@ -17159,10 +17156,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>601351</v>
+        <v>601309</v>
       </c>
       <c r="R147" t="n">
-        <v>6276607</v>
+        <v>6276695</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -17230,7 +17227,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>54511650</v>
+        <v>54444175</v>
       </c>
       <c r="B148" t="n">
         <v>106243</v>
@@ -17268,10 +17265,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>601215</v>
+        <v>601351</v>
       </c>
       <c r="R148" t="n">
-        <v>6276591</v>
+        <v>6276607</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -17298,12 +17295,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17317,18 +17314,18 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -17339,7 +17336,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>54524712</v>
+        <v>54511650</v>
       </c>
       <c r="B149" t="n">
         <v>106243</v>
@@ -17373,17 +17370,17 @@
       <c r="L149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>NO Gårdby sandhed, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>601271</v>
+        <v>601215</v>
       </c>
       <c r="R149" t="n">
-        <v>6276640</v>
+        <v>6276591</v>
       </c>
       <c r="S149" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17407,12 +17404,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2015-07-21</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2015-07-21</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17423,16 +17420,21 @@
       </c>
       <c r="AG149" t="b">
         <v>0</v>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>tallskog på sand</t>
+        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -17443,7 +17445,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>58885018</v>
+        <v>54524712</v>
       </c>
       <c r="B150" t="n">
         <v>106243</v>
@@ -17477,14 +17479,14 @@
       <c r="L150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>NO Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>601246</v>
+        <v>601271</v>
       </c>
       <c r="R150" t="n">
-        <v>6276674</v>
+        <v>6276640</v>
       </c>
       <c r="S150" t="n">
         <v>50</v>
@@ -17511,12 +17513,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2015-07-21</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2015-07-21</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17531,12 +17533,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -17547,7 +17549,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>66113422</v>
+        <v>58885018</v>
       </c>
       <c r="B151" t="n">
         <v>106243</v>
@@ -17577,11 +17579,7 @@
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -17589,10 +17587,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>601321</v>
+        <v>601246</v>
       </c>
       <c r="R151" t="n">
-        <v>6276619</v>
+        <v>6276674</v>
       </c>
       <c r="S151" t="n">
         <v>50</v>
@@ -17619,12 +17617,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17639,12 +17637,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Hans Lindfors</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Hans Lindfors</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -17655,7 +17653,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>66676941</v>
+        <v>66113422</v>
       </c>
       <c r="B152" t="n">
         <v>106243</v>
@@ -17685,21 +17683,25 @@
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Dörby tallskog, N2, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>601276</v>
+        <v>601321</v>
       </c>
       <c r="R152" t="n">
-        <v>6276684</v>
+        <v>6276619</v>
       </c>
       <c r="S152" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17723,12 +17725,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2017-06-04</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2017-06-04</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17743,12 +17745,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Hans Lindfors</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Hans Lindfors</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -17759,7 +17761,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>72346187</v>
+        <v>66676941</v>
       </c>
       <c r="B153" t="n">
         <v>106243</v>
@@ -17789,23 +17791,18 @@
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, N2, Öl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>601215</v>
+        <v>601276</v>
       </c>
       <c r="R153" t="n">
-        <v>6276612</v>
+        <v>6276684</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -17832,12 +17829,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17846,7 +17843,6 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -17869,7 +17865,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>86801212</v>
+        <v>72346187</v>
       </c>
       <c r="B154" t="n">
         <v>106243</v>
@@ -17901,21 +17897,21 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Dörbytallskog, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>601246</v>
+        <v>601215</v>
       </c>
       <c r="R154" t="n">
-        <v>6276644</v>
+        <v>6276612</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -17942,12 +17938,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17960,20 +17956,15 @@
       <c r="AG154" t="b">
         <v>0</v>
       </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
-      </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -17984,10 +17975,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>94467626</v>
+        <v>86801212</v>
       </c>
       <c r="B155" t="n">
-        <v>106244</v>
+        <v>106243</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18013,19 +18004,24 @@
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Dörby tallskog, norr sandheden, Öl</t>
+          <t>Dörbytallskog, Öl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>601269</v>
+        <v>601246</v>
       </c>
       <c r="R155" t="n">
-        <v>6276632</v>
+        <v>6276644</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -18052,12 +18048,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18070,22 +18066,31 @@
       <c r="AG155" t="b">
         <v>0</v>
       </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>gles tallskog</t>
+        </is>
+      </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>99255605</v>
+        <v>94467626</v>
       </c>
       <c r="B156" t="n">
         <v>106244</v>
@@ -18113,29 +18118,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Gårdby-Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, norr sandheden, Öl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>601203</v>
+        <v>601269</v>
       </c>
       <c r="R156" t="n">
-        <v>6276606</v>
+        <v>6276632</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -18162,12 +18158,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18180,27 +18176,22 @@
       <c r="AG156" t="b">
         <v>0</v>
       </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>99255615</v>
+        <v>99255605</v>
       </c>
       <c r="B157" t="n">
         <v>106244</v>
@@ -18228,8 +18219,16 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
@@ -18239,10 +18238,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>601209</v>
+        <v>601203</v>
       </c>
       <c r="R157" t="n">
-        <v>6276612</v>
+        <v>6276606</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -18307,7 +18306,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>99255628</v>
+        <v>99255615</v>
       </c>
       <c r="B158" t="n">
         <v>106244</v>
@@ -18335,16 +18334,8 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
@@ -18354,10 +18345,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>601239</v>
+        <v>601209</v>
       </c>
       <c r="R158" t="n">
-        <v>6276653</v>
+        <v>6276612</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -18422,7 +18413,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>99255660</v>
+        <v>99255628</v>
       </c>
       <c r="B159" t="n">
         <v>106244</v>
@@ -18452,7 +18443,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -18469,10 +18460,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>601321</v>
+        <v>601239</v>
       </c>
       <c r="R159" t="n">
-        <v>6276611</v>
+        <v>6276653</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -18537,7 +18528,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>101612360</v>
+        <v>99255660</v>
       </c>
       <c r="B160" t="n">
         <v>106244</v>
@@ -18565,28 +18556,32 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Gårdby-Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>601240</v>
+        <v>601321</v>
       </c>
       <c r="R160" t="n">
-        <v>6276652</v>
+        <v>6276611</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18610,12 +18605,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18628,22 +18623,27 @@
       <c r="AG160" t="b">
         <v>0</v>
       </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
+      </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Erik F Nordberg</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Erik F Nordberg, Karin Andersson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126780833</v>
+        <v>101612360</v>
       </c>
       <c r="B161" t="n">
         <v>106244</v>
@@ -18673,22 +18673,26 @@
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>601288</v>
+        <v>601240</v>
       </c>
       <c r="R161" t="n">
-        <v>6276671</v>
+        <v>6276652</v>
       </c>
       <c r="S161" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18712,12 +18716,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18730,80 +18734,64 @@
       <c r="AG161" t="b">
         <v>0</v>
       </c>
-      <c r="AI161" t="inlineStr">
-        <is>
-          <t>gallrad tallskog</t>
-        </is>
-      </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Erik F Nordberg</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Erik F Nordberg, Karin Andersson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>60656115</v>
+        <v>126780833</v>
       </c>
       <c r="B162" t="n">
-        <v>107294</v>
+        <v>106244</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>221647</v>
+        <v>221144</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Galeopsis ladanum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>601212</v>
+        <v>601288</v>
       </c>
       <c r="R162" t="n">
-        <v>6276638</v>
+        <v>6276671</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -18830,12 +18818,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18844,12 +18832,13 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>igenlagt sandtag</t>
+          <t>gallrad tallskog</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr"/>
@@ -18863,18 +18852,14 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY162" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+      <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>16065673</v>
+        <v>60656115</v>
       </c>
       <c r="B163" t="n">
-        <v>107516</v>
+        <v>107294</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18882,16 +18867,16 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>221849</v>
+        <v>221647</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Galeopsis ladanum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -18899,9 +18884,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
@@ -18939,12 +18936,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18958,7 +18955,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>SANDTAG</t>
+          <t>igenlagt sandtag</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -18980,7 +18977,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>54591844</v>
+        <v>16065673</v>
       </c>
       <c r="B164" t="n">
         <v>107516</v>
@@ -19018,10 +19015,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>601143</v>
+        <v>601212</v>
       </c>
       <c r="R164" t="n">
-        <v>6276662</v>
+        <v>6276638</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -19048,12 +19045,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19067,18 +19064,18 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>fd banvall, sandig</t>
+          <t>SANDTAG</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -19089,7 +19086,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>72696139</v>
+        <v>54591844</v>
       </c>
       <c r="B165" t="n">
         <v>107516</v>
@@ -19121,17 +19118,16 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>601166</v>
+        <v>601143</v>
       </c>
       <c r="R165" t="n">
-        <v>6276823</v>
+        <v>6276662</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -19158,12 +19154,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19172,24 +19168,23 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>sandig gammal banvall</t>
+          <t>fd banvall, sandig</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -19200,27 +19195,27 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>4220789</v>
+        <v>72696139</v>
       </c>
       <c r="B166" t="n">
-        <v>97983</v>
+        <v>107516</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>221945</v>
+        <v>221849</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -19229,16 +19224,20 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Dörby tallskog, öster vägen, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>601369</v>
+        <v>601166</v>
       </c>
       <c r="R166" t="n">
-        <v>6276502</v>
+        <v>6276823</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -19265,12 +19264,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2008-01-27</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2008-01-27</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19279,23 +19278,24 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>sandig tallskog med enstaka hassel/ek</t>
+          <t>sandig gammal banvall</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -19306,7 +19306,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>4220790</v>
+        <v>4220789</v>
       </c>
       <c r="B167" t="n">
         <v>97983</v>
@@ -19341,10 +19341,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>601392</v>
+        <v>601369</v>
       </c>
       <c r="R167" t="n">
-        <v>6276503</v>
+        <v>6276502</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -19412,7 +19412,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>7176403</v>
+        <v>4220790</v>
       </c>
       <c r="B168" t="n">
         <v>97983</v>
@@ -19441,19 +19441,16 @@
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, öster vägen, Öl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>601303</v>
+        <v>601392</v>
       </c>
       <c r="R168" t="n">
-        <v>6276564</v>
+        <v>6276503</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -19480,12 +19477,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2008-01-27</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2008-01-27</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19496,16 +19493,21 @@
       </c>
       <c r="AG168" t="b">
         <v>0</v>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>sandig tallskog med enstaka hassel/ek</t>
+        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -19516,7 +19518,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>16065769</v>
+        <v>7176403</v>
       </c>
       <c r="B169" t="n">
         <v>97983</v>
@@ -19550,14 +19552,14 @@
       <c r="L169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>601312</v>
+        <v>601303</v>
       </c>
       <c r="R169" t="n">
-        <v>6276555</v>
+        <v>6276564</v>
       </c>
       <c r="S169" t="n">
         <v>25</v>
@@ -19584,12 +19586,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19600,11 +19602,6 @@
       </c>
       <c r="AG169" t="b">
         <v>0</v>
-      </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
@@ -19625,32 +19622,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>60656163</v>
+        <v>16065769</v>
       </c>
       <c r="B170" t="n">
-        <v>100292</v>
+        <v>97983</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>222223</v>
+        <v>221945</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Apera spica-venti</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) P. Beauv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19663,10 +19660,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>601222</v>
+        <v>601312</v>
       </c>
       <c r="R170" t="n">
-        <v>6276656</v>
+        <v>6276555</v>
       </c>
       <c r="S170" t="n">
         <v>25</v>
@@ -19693,12 +19690,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19712,7 +19709,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>igenlagt sandtag</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -19734,10 +19731,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>5144080</v>
+        <v>60656163</v>
       </c>
       <c r="B171" t="n">
-        <v>100797</v>
+        <v>100292</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19745,34 +19742,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>222617</v>
+        <v>222223</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Apera spica-venti</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>(L.) P. Beauv.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>601216</v>
+        <v>601222</v>
       </c>
       <c r="R171" t="n">
-        <v>6276667</v>
+        <v>6276656</v>
       </c>
       <c r="S171" t="n">
         <v>25</v>
@@ -19799,12 +19799,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19818,18 +19818,18 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>sandtag</t>
+          <t>igenlagt sandtag</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -19840,7 +19840,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>72345748</v>
+        <v>5144080</v>
       </c>
       <c r="B172" t="n">
         <v>100797</v>
@@ -19869,20 +19869,16 @@
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>601132</v>
+        <v>601216</v>
       </c>
       <c r="R172" t="n">
-        <v>6276668</v>
+        <v>6276667</v>
       </c>
       <c r="S172" t="n">
         <v>25</v>
@@ -19909,12 +19905,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19923,19 +19919,23 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>sandtag</t>
+        </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -19946,30 +19946,34 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>86801227</v>
+        <v>72345748</v>
       </c>
       <c r="B173" t="n">
-        <v>99097</v>
+        <v>100797</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>223609</v>
+        <v>222617</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr"/>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
@@ -19977,14 +19981,14 @@
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Dörbytallskog, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>601308</v>
+        <v>601132</v>
       </c>
       <c r="R173" t="n">
-        <v>6276656</v>
+        <v>6276668</v>
       </c>
       <c r="S173" t="n">
         <v>25</v>
@@ -20011,12 +20015,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20029,20 +20033,15 @@
       <c r="AG173" t="b">
         <v>0</v>
       </c>
-      <c r="AI173" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
-      </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -20053,53 +20052,45 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127081837</v>
+        <v>135288104</v>
       </c>
       <c r="B174" t="n">
-        <v>99097</v>
+        <v>100875</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>223609</v>
+        <v>222617</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Gårdby tallskog tornet, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>601308</v>
+        <v>601301</v>
       </c>
       <c r="R174" t="n">
-        <v>6276635</v>
+        <v>6276866</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20126,22 +20117,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20150,29 +20131,32 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Rolf Kläppe</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Rolf Kläppe</t>
-        </is>
-      </c>
-      <c r="AY174" t="inlineStr"/>
+          <t>Edvin Åhman, Christine Sandberg</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>16071746</v>
+        <v>86801227</v>
       </c>
       <c r="B175" t="n">
-        <v>106230</v>
+        <v>99097</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20180,37 +20164,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>224098</v>
+        <v>223609</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Wallr.</t>
-        </is>
-      </c>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbytallskog, Öl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>601278</v>
+        <v>601308</v>
       </c>
       <c r="R175" t="n">
-        <v>6276674</v>
+        <v>6276656</v>
       </c>
       <c r="S175" t="n">
         <v>25</v>
@@ -20237,12 +20218,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20251,12 +20232,13 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
+      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>gles tallskog</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr"/>
@@ -20267,7 +20249,7 @@
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -20278,10 +20260,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>60656204</v>
+        <v>127081837</v>
       </c>
       <c r="B176" t="n">
-        <v>106230</v>
+        <v>99097</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20289,40 +20271,45 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>224098</v>
+        <v>223609</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Wallr.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Gårdby tallskog tornet, Öl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>601309</v>
+        <v>601308</v>
       </c>
       <c r="R176" t="n">
-        <v>6276659</v>
+        <v>6276635</v>
       </c>
       <c r="S176" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -20346,12 +20333,22 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20360,34 +20357,26 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>skogsväg</t>
-        </is>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Rolf Kläppe</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY176" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Rolf Kläppe</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>66674736</v>
+        <v>16071746</v>
       </c>
       <c r="B177" t="n">
         <v>106230</v>
@@ -20417,22 +20406,18 @@
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Dörby tallskog, N1, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>601316</v>
+        <v>601278</v>
       </c>
       <c r="R177" t="n">
-        <v>6276639</v>
+        <v>6276674</v>
       </c>
       <c r="S177" t="n">
         <v>25</v>
@@ -20459,12 +20444,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20475,16 +20460,21 @@
       </c>
       <c r="AG177" t="b">
         <v>0</v>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Ingela Carlström</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -20495,46 +20485,48 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>6187223</v>
+        <v>60656204</v>
       </c>
       <c r="B178" t="n">
-        <v>107062</v>
+        <v>106230</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>224354</v>
+        <v>224098</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vanlig axveronika</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Veronica spicata subsp. spicata</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr"/>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
       <c r="I178" t="inlineStr"/>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>601335</v>
+        <v>601309</v>
       </c>
       <c r="R178" t="n">
-        <v>6276698</v>
+        <v>6276659</v>
       </c>
       <c r="S178" t="n">
         <v>25</v>
@@ -20561,12 +20553,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20580,18 +20572,18 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>skogsväg</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -20602,30 +20594,34 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>66677098</v>
+        <v>66674736</v>
       </c>
       <c r="B179" t="n">
-        <v>107062</v>
+        <v>106230</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>224354</v>
+        <v>224098</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vanlig axveronika</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Veronica spicata subsp. spicata</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr"/>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
@@ -20636,17 +20632,17 @@
       <c r="L179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Dörby tallskog, infart, Öl</t>
+          <t>Dörby tallskog, N1, Öl</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>601217</v>
+        <v>601316</v>
       </c>
       <c r="R179" t="n">
-        <v>6276653</v>
+        <v>6276639</v>
       </c>
       <c r="S179" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20695,7 +20691,7 @@
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Tommy Carlström, Ingela Carlström</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -20706,44 +20702,46 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>54511699</v>
+        <v>6187223</v>
       </c>
       <c r="B180" t="n">
-        <v>97985</v>
+        <v>107062</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>224363</v>
+        <v>224354</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig axveronika</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Veronica spicata subsp. spicata</t>
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>601285</v>
+        <v>601335</v>
       </c>
       <c r="R180" t="n">
-        <v>6276569</v>
+        <v>6276698</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>
@@ -20770,12 +20768,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20811,47 +20809,51 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>54511702</v>
+        <v>66677098</v>
       </c>
       <c r="B181" t="n">
-        <v>97985</v>
+        <v>107062</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>224363</v>
+        <v>224354</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig axveronika</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Veronica spicata subsp. spicata</t>
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, infart, Öl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>601304</v>
+        <v>601217</v>
       </c>
       <c r="R181" t="n">
-        <v>6276567</v>
+        <v>6276653</v>
       </c>
       <c r="S181" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -20875,12 +20877,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20891,21 +20893,16 @@
       </c>
       <c r="AG181" t="b">
         <v>0</v>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
@@ -20916,41 +20913,44 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>6247724</v>
+        <v>54511699</v>
       </c>
       <c r="B182" t="n">
-        <v>104640</v>
+        <v>97985</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>224416</v>
+        <v>224363</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>601216</v>
+        <v>601285</v>
       </c>
       <c r="R182" t="n">
-        <v>6276667</v>
+        <v>6276569</v>
       </c>
       <c r="S182" t="n">
         <v>25</v>
@@ -20977,12 +20977,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20996,7 +20996,7 @@
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>sandtag</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -21018,27 +21018,27 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>16065671</v>
+        <v>54511702</v>
       </c>
       <c r="B183" t="n">
-        <v>104640</v>
+        <v>97985</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>224416</v>
+        <v>224363</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
@@ -21052,10 +21052,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>601212</v>
+        <v>601304</v>
       </c>
       <c r="R183" t="n">
-        <v>6276638</v>
+        <v>6276567</v>
       </c>
       <c r="S183" t="n">
         <v>25</v>
@@ -21082,12 +21082,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21101,21 +21101,228 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>SANDTAG</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>6247724</v>
+      </c>
+      <c r="B184" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Dörby tallskog, Öl</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>601216</v>
+      </c>
+      <c r="R184" t="n">
+        <v>6276667</v>
+      </c>
+      <c r="S184" t="n">
+        <v>25</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2009-06-03</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2009-06-03</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>sandtag</t>
+        </is>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>16065671</v>
+      </c>
+      <c r="B185" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Dörby tallskog, Öl</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>601212</v>
+      </c>
+      <c r="R185" t="n">
+        <v>6276638</v>
+      </c>
+      <c r="S185" t="n">
+        <v>25</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2014-07-07</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2014-07-07</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>SANDTAG</t>
+        </is>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
           <t>Ulla-Britt Andersson</t>
         </is>
       </c>
-      <c r="AX183" t="inlineStr">
+      <c r="AX185" t="inlineStr">
         <is>
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY183" t="inlineStr">
+      <c r="AY185" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY185"/>
+  <dimension ref="A1:AY186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8827,57 +8827,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>636681</v>
+        <v>135447260</v>
       </c>
       <c r="B73" t="n">
-        <v>100693</v>
+        <v>104760</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1888</v>
+        <v>1852</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tofsäxing</t>
+          <t>Grådådra</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Koeleria glauca</t>
+          <t>Alyssum alyssoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) DC.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Gårdby-Dörby tallskog (23), Öl</t>
+          <t>Väg 925, fyndplats 020, Öl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>601286</v>
+        <v>601307</v>
       </c>
       <c r="R73" t="n">
-        <v>6276636</v>
+        <v>6276876</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8899,19 +8890,20 @@
           <t>Norra Möckleby</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>Hö-Mör-3051</t>
-        </is>
-      </c>
+      <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2007-07-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2007-07-21</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt i blom just här i vägskäl till skogsbilväg</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8926,23 +8918,23 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Öland- Floraväktarna</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>636940</v>
+        <v>636681</v>
       </c>
       <c r="B74" t="n">
         <v>100693</v>
@@ -8972,7 +8964,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8982,17 +8974,17 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Gårdby-Dörby tallskog (23), Öl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>601222</v>
+        <v>601286</v>
       </c>
       <c r="R74" t="n">
-        <v>6276683</v>
+        <v>6276636</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9014,14 +9006,19 @@
           <t>Norra Möckleby</t>
         </is>
       </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Hö-Mör-3051</t>
+        </is>
+      </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2007-07-21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2007-07-21</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9032,32 +9029,27 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>sandtag</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Öland- Floraväktarna</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>637468</v>
+        <v>636940</v>
       </c>
       <c r="B75" t="n">
         <v>100693</v>
@@ -9087,7 +9079,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9097,14 +9089,14 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>talldunge mellan Gårdby-Dörby, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>601174</v>
+        <v>601222</v>
       </c>
       <c r="R75" t="n">
-        <v>6276841</v>
+        <v>6276683</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9131,12 +9123,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9150,7 +9142,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>f.d. banvall, kalkrik sand</t>
+          <t>sandtag</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9172,7 +9164,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>54591847</v>
+        <v>637468</v>
       </c>
       <c r="B76" t="n">
         <v>100693</v>
@@ -9200,20 +9192,26 @@
           <t>(Spreng.) DC.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>talldunge mellan Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>601143</v>
+        <v>601174</v>
       </c>
       <c r="R76" t="n">
-        <v>6276662</v>
+        <v>6276841</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9240,12 +9238,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9259,7 +9257,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>fd banvall, sandig</t>
+          <t>f.d. banvall, kalkrik sand</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9281,7 +9279,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>72696154</v>
+        <v>54591847</v>
       </c>
       <c r="B77" t="n">
         <v>100693</v>
@@ -9313,17 +9311,16 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>601173</v>
+        <v>601143</v>
       </c>
       <c r="R77" t="n">
-        <v>6276842</v>
+        <v>6276662</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9350,17 +9347,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>ganska gott om</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9369,24 +9361,23 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>sandig gammal banvall</t>
+          <t>fd banvall, sandig</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9397,37 +9388,38 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121707046</v>
+        <v>72696154</v>
       </c>
       <c r="B78" t="n">
-        <v>92567</v>
+        <v>100693</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6031</v>
+        <v>1888</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tofsäxing</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Koeleria glauca</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Spreng.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9435,13 +9427,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>601443</v>
+        <v>601173</v>
       </c>
       <c r="R78" t="n">
-        <v>6276610</v>
+        <v>6276842</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9465,12 +9457,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2018-08-13</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>ganska gott om</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9485,7 +9482,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>vid basen av tall, sandigt</t>
+          <t>sandig gammal banvall</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9499,14 +9496,18 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY78" t="inlineStr"/>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>58884981</v>
+        <v>121707046</v>
       </c>
       <c r="B79" t="n">
-        <v>57950</v>
+        <v>92567</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9514,44 +9515,40 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>601246</v>
+        <v>601443</v>
       </c>
       <c r="R79" t="n">
-        <v>6276674</v>
+        <v>6276610</v>
       </c>
       <c r="S79" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9575,12 +9572,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9589,50 +9586,56 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>vid basen av tall, sandigt</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>13438719</v>
+        <v>58884981</v>
       </c>
       <c r="B80" t="n">
-        <v>45049</v>
+        <v>57950</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>102021</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9640,21 +9643,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Gårdby sandhed/talle, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>601163</v>
+        <v>601246</v>
       </c>
       <c r="R80" t="n">
-        <v>6276740</v>
+        <v>6276674</v>
       </c>
       <c r="S80" t="n">
         <v>50</v>
@@ -9681,12 +9682,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9701,44 +9702,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Stefan Lithner</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Stefan Lithner</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>17012458</v>
+        <v>13438719</v>
       </c>
       <c r="B81" t="n">
-        <v>9463</v>
+        <v>45049</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>102176</v>
+        <v>102021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Heddyngbagge</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bodilopsis sordida</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fabricius, 1775)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9746,36 +9747,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Gårdby, Öl</t>
+          <t>Gårdby sandhed/talle, Öl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>601193</v>
+        <v>601163</v>
       </c>
       <c r="R81" t="n">
-        <v>6276727</v>
+        <v>6276740</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9799,12 +9788,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2006-08-01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2006-08-01</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9819,44 +9808,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>David Hammarberg</t>
+          <t>Stefan Lithner</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
+          <t>Stefan Lithner</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>78025936</v>
+        <v>17012458</v>
       </c>
       <c r="B82" t="n">
-        <v>57947</v>
+        <v>9463</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102977</v>
+        <v>102176</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Heddyngbagge</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Bodilopsis sordida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fabricius, 1775)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -9864,19 +9853,36 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>N Gårdby, Öl</t>
+          <t>Gårdby sandhed, Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>601390</v>
+        <v>601193</v>
       </c>
       <c r="R82" t="n">
-        <v>6276813</v>
+        <v>6276727</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9900,22 +9906,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2019-05-18</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2019-05-18</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>10:11</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9930,44 +9926,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>David Hammarberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Guillaume Mercier, Alexandra Johansson</t>
+          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>78025941</v>
+        <v>78025936</v>
       </c>
       <c r="B83" t="n">
-        <v>58238</v>
+        <v>57947</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103012</v>
+        <v>102977</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -10053,32 +10049,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>78025938</v>
+        <v>78025941</v>
       </c>
       <c r="B84" t="n">
-        <v>58327</v>
+        <v>58238</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -10164,32 +10160,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>17021016</v>
+        <v>78025938</v>
       </c>
       <c r="B85" t="n">
-        <v>40503</v>
+        <v>58327</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>214498</v>
+        <v>103015</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sikelsäckmal</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Coleophora lixella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Zeller, 1849</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10197,36 +10193,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Gårdby, Öl</t>
+          <t>N Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>601193</v>
+        <v>601390</v>
       </c>
       <c r="R85" t="n">
-        <v>6276727</v>
+        <v>6276813</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10250,12 +10229,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2019-05-18</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2019-05-18</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10270,22 +10259,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>David Hammarberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
+          <t>Linda Johannesson, Guillaume Mercier, Alexandra Johansson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>102470713</v>
+        <v>17021016</v>
       </c>
       <c r="B86" t="n">
-        <v>43792</v>
+        <v>40503</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10293,21 +10282,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>215481</v>
+        <v>214498</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dubbelbandat ljusmott</t>
+          <t>Sikelsäckmal</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pyrausta ostrinalis</t>
+          <t>Coleophora lixella</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hübner, 1796)</t>
+          <t>Zeller, 1849</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -10322,7 +10311,11 @@
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr">
         <is>
           <t>lampa</t>
@@ -10330,17 +10323,17 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed, Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>601267</v>
+        <v>601193</v>
       </c>
       <c r="R86" t="n">
-        <v>6276623</v>
+        <v>6276727</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10364,12 +10357,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10378,29 +10371,28 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>David Hammarberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>17012459</v>
+        <v>102470713</v>
       </c>
       <c r="B87" t="n">
-        <v>41758</v>
+        <v>43792</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10408,21 +10400,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>215656</v>
+        <v>215481</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rödlätt lövmätare</t>
+          <t>Dubbelbandat ljusmott</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Scopula rubiginata</t>
+          <t>Pyrausta ostrinalis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
+          <t>(Hübner, 1796)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -10437,11 +10429,7 @@
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>lampa</t>
@@ -10449,17 +10437,17 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Gårdby, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>601193</v>
+        <v>601267</v>
       </c>
       <c r="R87" t="n">
-        <v>6276727</v>
+        <v>6276623</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10483,12 +10471,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10497,28 +10485,29 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>David Hammarberg</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>17012454</v>
+        <v>17012459</v>
       </c>
       <c r="B88" t="n">
-        <v>41451</v>
+        <v>41758</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10526,16 +10515,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>215683</v>
+        <v>215656</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mellanmätare</t>
+          <t>Rödlätt lövmätare</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phibalapteryx virgata</t>
+          <t>Scopula rubiginata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -10601,12 +10590,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2014-08-06</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2014-08-06</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10633,7 +10622,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>102470028</v>
+        <v>17012454</v>
       </c>
       <c r="B89" t="n">
         <v>41451</v>
@@ -10673,7 +10662,11 @@
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr">
         <is>
           <t>lampa</t>
@@ -10681,17 +10674,17 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed, Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>601267</v>
+        <v>601193</v>
       </c>
       <c r="R89" t="n">
-        <v>6276623</v>
+        <v>6276727</v>
       </c>
       <c r="S89" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10715,12 +10708,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2014-08-06</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2014-08-06</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10729,29 +10722,28 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>David Hammarberg</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>102470721</v>
+        <v>102470028</v>
       </c>
       <c r="B90" t="n">
-        <v>41667</v>
+        <v>41451</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10759,24 +10751,28 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>215766</v>
+        <v>215683</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vägtornsmätare</t>
+          <t>Mellanmätare</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Triphosa dubitata</t>
+          <t>Phibalapteryx virgata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Hufnagel, 1767)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
@@ -10859,10 +10855,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>102470725</v>
+        <v>102470721</v>
       </c>
       <c r="B91" t="n">
-        <v>41655</v>
+        <v>41667</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10870,28 +10866,24 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>215768</v>
+        <v>215766</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svartbrun klaffmätare</t>
+          <t>Vägtornsmätare</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Philereme transversata</t>
+          <t>Triphosa dubitata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
@@ -10974,10 +10966,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>86918873</v>
+        <v>102470725</v>
       </c>
       <c r="B92" t="n">
-        <v>42417</v>
+        <v>41655</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10985,21 +10977,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>215920</v>
+        <v>215768</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kalkfly</t>
+          <t>Svartbrun klaffmätare</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tyta luctuosa</t>
+          <t>Philereme transversata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Hufnagel, 1767)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11008,16 +11000,16 @@
         </is>
       </c>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>ljusfälla</t>
+          <t>lampa</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11056,12 +11048,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11089,48 +11081,65 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2149811</v>
+        <v>86918873</v>
       </c>
       <c r="B93" t="n">
-        <v>111175</v>
+        <v>42417</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219677</v>
+        <v>215920</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kalkfly</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Tyta luctuosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>ljusfälla</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>barrskog söder Dörby väster landsvägen, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>601143</v>
+        <v>601267</v>
       </c>
       <c r="R93" t="n">
-        <v>6276792</v>
+        <v>6276623</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11154,17 +11163,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>4H5a NV</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11173,34 +11177,26 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>tallskog med lövinslag</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Christer Klingstedt</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2155460</v>
+        <v>2149811</v>
       </c>
       <c r="B94" t="n">
         <v>111175</v>
@@ -11231,14 +11227,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>tallskog mellan Gårdby-Dörby, östra delen, Öl</t>
+          <t>barrskog söder Dörby väster landsvägen, Öl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>601603</v>
+        <v>601143</v>
       </c>
       <c r="R94" t="n">
-        <v>6276691</v>
+        <v>6276792</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11265,12 +11261,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>4H5a NV</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11284,7 +11285,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>tallskog med lövinslag</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11306,7 +11307,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>7176390</v>
+        <v>2155460</v>
       </c>
       <c r="B95" t="n">
         <v>111175</v>
@@ -11335,19 +11336,16 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>tallskog mellan Gårdby-Dörby, östra delen, Öl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>601419</v>
+        <v>601603</v>
       </c>
       <c r="R95" t="n">
-        <v>6276820</v>
+        <v>6276691</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11374,12 +11372,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11390,16 +11388,21 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11410,7 +11413,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>16038415</v>
+        <v>7176390</v>
       </c>
       <c r="B96" t="n">
         <v>111175</v>
@@ -11444,14 +11447,14 @@
       <c r="L96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>601371</v>
+        <v>601419</v>
       </c>
       <c r="R96" t="n">
-        <v>6276796</v>
+        <v>6276820</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11478,12 +11481,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11494,11 +11497,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11508,7 +11506,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11519,10 +11517,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2278736</v>
+        <v>16038415</v>
       </c>
       <c r="B97" t="n">
-        <v>99010</v>
+        <v>111175</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11530,48 +11528,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219769</v>
+        <v>219677</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>601177</v>
+        <v>601371</v>
       </c>
       <c r="R97" t="n">
-        <v>6276650</v>
+        <v>6276796</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11598,12 +11585,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2009-06-09</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2009-06-09</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11617,18 +11604,18 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11639,10 +11626,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2914483</v>
+        <v>2278736</v>
       </c>
       <c r="B98" t="n">
-        <v>99096</v>
+        <v>99010</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11650,37 +11637,51 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219798</v>
+        <v>219769</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Gårdby norr, tallskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>601212</v>
+        <v>601177</v>
       </c>
       <c r="R98" t="n">
-        <v>6276703</v>
+        <v>6276650</v>
       </c>
       <c r="S98" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11704,12 +11705,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2007-07-21</t>
+          <t>2009-06-09</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2007-07-21</t>
+          <t>2009-06-09</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11734,7 +11735,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11745,7 +11746,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>16038422</v>
+        <v>2914483</v>
       </c>
       <c r="B99" t="n">
         <v>99096</v>
@@ -11774,22 +11775,19 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Gårdby norr, tallskogen, Öl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>601286</v>
+        <v>601212</v>
       </c>
       <c r="R99" t="n">
-        <v>6276666</v>
+        <v>6276703</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11813,12 +11811,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2007-07-21</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2007-07-21</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11832,18 +11830,18 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11854,7 +11852,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>16065665</v>
+        <v>16038422</v>
       </c>
       <c r="B100" t="n">
         <v>99096</v>
@@ -11884,11 +11882,7 @@
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11896,10 +11890,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>601222</v>
+        <v>601286</v>
       </c>
       <c r="R100" t="n">
-        <v>6276656</v>
+        <v>6276666</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11926,12 +11920,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11945,7 +11939,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>SANDTAG</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11956,7 +11950,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11967,7 +11961,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>54511725</v>
+        <v>16065665</v>
       </c>
       <c r="B101" t="n">
         <v>99096</v>
@@ -12009,10 +12003,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>601305</v>
+        <v>601222</v>
       </c>
       <c r="R101" t="n">
-        <v>6276660</v>
+        <v>6276656</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -12039,12 +12033,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12058,18 +12052,18 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>SANDTAG</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12080,7 +12074,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>54591834</v>
+        <v>54511725</v>
       </c>
       <c r="B102" t="n">
         <v>99096</v>
@@ -12110,7 +12104,11 @@
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -12118,10 +12116,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>601143</v>
+        <v>601305</v>
       </c>
       <c r="R102" t="n">
-        <v>6276662</v>
+        <v>6276660</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12148,17 +12146,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>liknar tallknipprot subsp. orbicularis</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12172,7 +12165,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>fd banvall, sandig</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12194,7 +12187,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>60656187</v>
+        <v>54591834</v>
       </c>
       <c r="B103" t="n">
         <v>99096</v>
@@ -12224,11 +12217,7 @@
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12236,10 +12225,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>601309</v>
+        <v>601143</v>
       </c>
       <c r="R103" t="n">
-        <v>6276659</v>
+        <v>6276662</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12266,12 +12255,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2015-07-26</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>liknar tallknipprot subsp. orbicularis</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12285,18 +12279,18 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>skogsväg</t>
+          <t>fd banvall, sandig</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12307,7 +12301,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>60675953</v>
+        <v>60656187</v>
       </c>
       <c r="B104" t="n">
         <v>99096</v>
@@ -12345,14 +12339,14 @@
       <c r="L104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Dörby Tallskog, Gårdby sandhed väst, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>601300</v>
+        <v>601309</v>
       </c>
       <c r="R104" t="n">
-        <v>6276643</v>
+        <v>6276659</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12379,12 +12373,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2016-07-21</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2016-07-21</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12395,16 +12389,21 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>skogsväg</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Birgitta Davidsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Birgitta Davidsson, Gunnar Siljestrand</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12415,7 +12414,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>72345744</v>
+        <v>60675953</v>
       </c>
       <c r="B105" t="n">
         <v>99096</v>
@@ -12447,21 +12446,20 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby Tallskog, Gårdby sandhed väst, Öl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>601132</v>
+        <v>601300</v>
       </c>
       <c r="R105" t="n">
-        <v>6276668</v>
+        <v>6276643</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12488,12 +12486,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2016-07-21</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2016-07-21</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12502,19 +12500,18 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Birgitta Davidsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Birgitta Davidsson, Gunnar Siljestrand</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -12525,7 +12522,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>72346273</v>
+        <v>72345744</v>
       </c>
       <c r="B106" t="n">
         <v>99096</v>
@@ -12555,19 +12552,23 @@
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Dörby tallskog, norr sandheden, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>601269</v>
+        <v>601132</v>
       </c>
       <c r="R106" t="n">
-        <v>6276632</v>
+        <v>6276668</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12631,7 +12632,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>94467618</v>
+        <v>72346273</v>
       </c>
       <c r="B107" t="n">
         <v>99096</v>
@@ -12660,19 +12661,20 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Dörby tallskog, N1, Öl</t>
+          <t>Dörby tallskog, norr sandheden, Öl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>601316</v>
+        <v>601269</v>
       </c>
       <c r="R107" t="n">
-        <v>6276639</v>
+        <v>6276632</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12699,12 +12701,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12725,14 +12727,18 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
+          <t>Ingela Carlström, Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>110458149</v>
+        <v>94467618</v>
       </c>
       <c r="B108" t="n">
         <v>99096</v>
@@ -12760,32 +12766,23 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Dörby tallskog, N1, Öl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>601270</v>
+        <v>601316</v>
       </c>
       <c r="R108" t="n">
-        <v>6276638</v>
+        <v>6276639</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12809,12 +12806,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12830,22 +12827,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Hasse Andersson, Birgit Svensson</t>
+          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>72345745</v>
+        <v>110458149</v>
       </c>
       <c r="B109" t="n">
-        <v>99142</v>
+        <v>99096</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12853,41 +12850,49 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>601132</v>
+        <v>601270</v>
       </c>
       <c r="R109" t="n">
-        <v>6276668</v>
+        <v>6276638</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12911,12 +12916,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12932,26 +12937,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Hasse Andersson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Hasse Andersson, Birgit Svensson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>78964858</v>
+        <v>72345745</v>
       </c>
       <c r="B110" t="n">
-        <v>99156</v>
+        <v>99142</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12959,49 +12960,41 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219875</v>
+        <v>219847</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Dörrby, Tallskog, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>601274</v>
+        <v>601132</v>
       </c>
       <c r="R110" t="n">
-        <v>6276714</v>
+        <v>6276668</v>
       </c>
       <c r="S110" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13025,12 +13018,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13046,12 +13039,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Joakim Johansson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Joakim Johansson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -13062,7 +13055,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>94471286</v>
+        <v>78964858</v>
       </c>
       <c r="B111" t="n">
         <v>99156</v>
@@ -13090,7 +13083,12 @@
           <t>(Custer) Rchb.</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -13100,17 +13098,17 @@
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Vägkant norr om Gårdby sanshed, Öl</t>
+          <t>Dörrby, Tallskog, Öl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>601203</v>
+        <v>601274</v>
       </c>
       <c r="R111" t="n">
-        <v>6276671</v>
+        <v>6276714</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13134,22 +13132,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
-        </is>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13165,57 +13153,68 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Joakim Johansson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr"/>
+          <t>Joakim Johansson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2674129</v>
+        <v>94471286</v>
       </c>
       <c r="B112" t="n">
-        <v>109814</v>
+        <v>99156</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220204</v>
+        <v>219875</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Vägkant norr om Gårdby sanshed, Öl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>601222</v>
+        <v>601203</v>
       </c>
       <c r="R112" t="n">
-        <v>6276683</v>
+        <v>6276671</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -13242,12 +13241,22 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2021-06-25</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2021-06-25</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13256,34 +13265,26 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>sandtag</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>16071705</v>
+        <v>2674129</v>
       </c>
       <c r="B113" t="n">
         <v>109814</v>
@@ -13312,19 +13313,16 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>601272</v>
+        <v>601222</v>
       </c>
       <c r="R113" t="n">
-        <v>6276673</v>
+        <v>6276683</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -13351,12 +13349,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13370,18 +13368,18 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>sandtag</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -13392,10 +13390,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135288243</v>
+        <v>16071705</v>
       </c>
       <c r="B114" t="n">
-        <v>109896</v>
+        <v>109814</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13421,19 +13419,22 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Vägområde, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>601301</v>
+        <v>601272</v>
       </c>
       <c r="R114" t="n">
-        <v>6276866</v>
+        <v>6276673</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13457,17 +13458,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>3 plantor i blom på släntkrön 2m från beläggningen(+6plantor utanför vägområdet)</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13478,70 +13474,70 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Edvin Åhman</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Edvin Åhman, Christine Sandberg</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>3025627</v>
+        <v>135288243</v>
       </c>
       <c r="B115" t="n">
-        <v>99118</v>
+        <v>109896</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>220204</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Gårdby N., Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>601256</v>
+        <v>601301</v>
       </c>
       <c r="R115" t="n">
-        <v>6276584</v>
+        <v>6276866</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13568,17 +13564,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2007-08-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2007-08-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Delvis överblommad</t>
+          <t>3 plantor i blom på släntkrön 2m från beläggningen(+6plantor utanför vägområdet)</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13589,32 +13585,27 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>3026664</v>
+        <v>3025627</v>
       </c>
       <c r="B116" t="n">
         <v>99118</v>
@@ -13643,19 +13634,24 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Övre Ålebäck N, Öl</t>
+          <t>Gårdby N., Öl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>601247</v>
+        <v>601256</v>
       </c>
       <c r="R116" t="n">
-        <v>6276600</v>
+        <v>6276584</v>
       </c>
       <c r="S116" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13679,12 +13675,17 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2007-08-10</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2007-08-10</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Delvis överblommad</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13704,12 +13705,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -13720,7 +13721,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>3029119</v>
+        <v>3026664</v>
       </c>
       <c r="B117" t="n">
         <v>99118</v>
@@ -13751,14 +13752,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Dörby S, Öl</t>
+          <t>Övre Ålebäck N, Öl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>601245</v>
+        <v>601247</v>
       </c>
       <c r="R117" t="n">
-        <v>6276602</v>
+        <v>6276600</v>
       </c>
       <c r="S117" t="n">
         <v>50</v>
@@ -13785,12 +13786,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2009-05-05</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2009-05-05</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13826,7 +13827,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>3029132</v>
+        <v>3029119</v>
       </c>
       <c r="B118" t="n">
         <v>99118</v>
@@ -13855,24 +13856,19 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby S, Öl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>601226</v>
+        <v>601245</v>
       </c>
       <c r="R118" t="n">
-        <v>6276599</v>
+        <v>6276602</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13896,12 +13892,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2009-05-05</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2009-05-05</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13915,18 +13911,18 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>gles tallskog med enstaka lövträd</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -13937,7 +13933,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>3029133</v>
+        <v>3029132</v>
       </c>
       <c r="B119" t="n">
         <v>99118</v>
@@ -13966,16 +13962,21 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>601222</v>
+        <v>601226</v>
       </c>
       <c r="R119" t="n">
-        <v>6276594</v>
+        <v>6276599</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -14008,11 +14009,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2009-06-03</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>stort bestånd</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14048,7 +14044,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>3029134</v>
+        <v>3029133</v>
       </c>
       <c r="B120" t="n">
         <v>99118</v>
@@ -14083,10 +14079,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>601306</v>
+        <v>601222</v>
       </c>
       <c r="R120" t="n">
-        <v>6276718</v>
+        <v>6276594</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -14119,6 +14115,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2009-06-03</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>stort bestånd</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14154,7 +14155,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>3029135</v>
+        <v>3029134</v>
       </c>
       <c r="B121" t="n">
         <v>99118</v>
@@ -14189,10 +14190,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>601299</v>
+        <v>601306</v>
       </c>
       <c r="R121" t="n">
-        <v>6276716</v>
+        <v>6276718</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -14260,7 +14261,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>3035150</v>
+        <v>3029135</v>
       </c>
       <c r="B122" t="n">
         <v>99118</v>
@@ -14288,31 +14289,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>tallskog syd Dörby, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>601317</v>
+        <v>601299</v>
       </c>
       <c r="R122" t="n">
-        <v>6276750</v>
+        <v>6276716</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14339,17 +14326,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>hotas av avverkning</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14363,7 +14345,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>gles tallskog med enstaka lövträd</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14385,7 +14367,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>3035151</v>
+        <v>3035150</v>
       </c>
       <c r="B123" t="n">
         <v>99118</v>
@@ -14413,10 +14395,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14425,10 +14416,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>601326</v>
+        <v>601317</v>
       </c>
       <c r="R123" t="n">
-        <v>6276771</v>
+        <v>6276750</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14501,7 +14492,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>3035398</v>
+        <v>3035151</v>
       </c>
       <c r="B124" t="n">
         <v>99118</v>
@@ -14537,14 +14528,14 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>tallskog mellan Dörby-Gårdby, Öl</t>
+          <t>tallskog syd Dörby, Öl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>601300</v>
+        <v>601326</v>
       </c>
       <c r="R124" t="n">
-        <v>6276710</v>
+        <v>6276771</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -14571,17 +14562,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>ej blommande</t>
+          <t>hotas av avverkning</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14595,7 +14586,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14617,7 +14608,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>3035399</v>
+        <v>3035398</v>
       </c>
       <c r="B125" t="n">
         <v>99118</v>
@@ -14657,10 +14648,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>601211</v>
+        <v>601300</v>
       </c>
       <c r="R125" t="n">
-        <v>6276590</v>
+        <v>6276710</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14697,7 +14688,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>täckt av ris för avverkning</t>
+          <t>ej blommande</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14733,7 +14724,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>3042763</v>
+        <v>3035399</v>
       </c>
       <c r="B126" t="n">
         <v>99118</v>
@@ -14761,31 +14752,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Öl</t>
+          <t>tallskog mellan Dörby-Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>601285</v>
+        <v>601211</v>
       </c>
       <c r="R126" t="n">
-        <v>6276690</v>
+        <v>6276590</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14812,17 +14794,17 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>5 blommande, 50 bladrosetter</t>
+          <t>täckt av ris för avverkning</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14858,7 +14840,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>3042764</v>
+        <v>3042763</v>
       </c>
       <c r="B127" t="n">
         <v>99118</v>
@@ -14888,7 +14870,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14907,10 +14889,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>601259</v>
+        <v>601285</v>
       </c>
       <c r="R127" t="n">
-        <v>6276711</v>
+        <v>6276690</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14947,7 +14929,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>1 blommande, 2 bestånd, 14 bladrosetter</t>
+          <t>5 blommande, 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14983,7 +14965,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>3042765</v>
+        <v>3042764</v>
       </c>
       <c r="B128" t="n">
         <v>99118</v>
@@ -15013,7 +14995,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -15032,10 +15014,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>601330</v>
+        <v>601259</v>
       </c>
       <c r="R128" t="n">
-        <v>6276690</v>
+        <v>6276711</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -15072,7 +15054,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>4blommande, 55 bladrosetter, 2 bestånd</t>
+          <t>1 blommande, 2 bestånd, 14 bladrosetter</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15108,7 +15090,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>3042766</v>
+        <v>3042765</v>
       </c>
       <c r="B129" t="n">
         <v>99118</v>
@@ -15138,12 +15120,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -15157,10 +15139,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>601317</v>
+        <v>601330</v>
       </c>
       <c r="R129" t="n">
-        <v>6276649</v>
+        <v>6276690</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -15197,7 +15179,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>9 blommande, 50 bladrosetter</t>
+          <t>4blommande, 55 bladrosetter, 2 bestånd</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15233,7 +15215,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>3052277</v>
+        <v>3042766</v>
       </c>
       <c r="B130" t="n">
         <v>99118</v>
@@ -15263,29 +15245,29 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Dörby, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>601279</v>
+        <v>601317</v>
       </c>
       <c r="R130" t="n">
-        <v>6276712</v>
+        <v>6276649</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -15312,12 +15294,17 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2011-08-31</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2011-08-31</t>
+          <t>2011-07-17</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>9 blommande, 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15331,18 +15318,18 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>Sandtallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Veronika Johansson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Veronika Johansson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -15353,7 +15340,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>79945652</v>
+        <v>3052277</v>
       </c>
       <c r="B131" t="n">
         <v>99118</v>
@@ -15381,28 +15368,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Dörby, Öl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>601267</v>
+        <v>601279</v>
       </c>
       <c r="R131" t="n">
-        <v>6276623</v>
+        <v>6276712</v>
       </c>
       <c r="S131" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15426,12 +15419,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2010-08-07</t>
+          <t>2011-08-31</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2010-08-07</t>
+          <t>2011-08-31</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15440,19 +15433,23 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>Veronika Johansson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>Veronika Johansson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -15463,10 +15460,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134863685</v>
+        <v>79945652</v>
       </c>
       <c r="B132" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15491,29 +15488,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Mörbylånga, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>601249</v>
+        <v>601267</v>
       </c>
       <c r="R132" t="n">
-        <v>6276655</v>
+        <v>6276623</v>
       </c>
       <c r="S132" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15537,22 +15533,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>07:53</t>
+          <t>2010-08-07</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>07:53</t>
+          <t>2010-08-07</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15561,71 +15547,80 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Kjell Stålberg</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Kjell Stålberg, Carolina Stålberg</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr"/>
+          <t>Christer Klingstedt</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>3421658</v>
+        <v>134863685</v>
       </c>
       <c r="B133" t="n">
-        <v>106243</v>
+        <v>99195</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Övre Ålebäck N, Öl</t>
+          <t>Mörbylånga, Öl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>601247</v>
+        <v>601249</v>
       </c>
       <c r="R133" t="n">
-        <v>6276600</v>
+        <v>6276655</v>
       </c>
       <c r="S133" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15649,12 +15644,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15665,32 +15670,23 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Kjell Stålberg</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Kjell Stålberg, Carolina Stålberg</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>3424445</v>
+        <v>3421658</v>
       </c>
       <c r="B134" t="n">
         <v>106243</v>
@@ -15721,22 +15717,22 @@
       <c r="I134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>tallskog syd Dörby, Öl</t>
+          <t>Övre Ålebäck N, Öl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>601286</v>
+        <v>601247</v>
       </c>
       <c r="R134" t="n">
-        <v>6276626</v>
+        <v>6276600</v>
       </c>
       <c r="S134" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15760,12 +15756,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15779,18 +15775,18 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -15801,7 +15797,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>3424446</v>
+        <v>3424445</v>
       </c>
       <c r="B135" t="n">
         <v>106243</v>
@@ -15841,10 +15837,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>601257</v>
+        <v>601286</v>
       </c>
       <c r="R135" t="n">
-        <v>6276610</v>
+        <v>6276626</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -15912,7 +15908,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>3424453</v>
+        <v>3424446</v>
       </c>
       <c r="B136" t="n">
         <v>106243</v>
@@ -15943,19 +15939,19 @@
       <c r="I136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>tallskog mellan Dörby-Gårdby, Öl</t>
+          <t>tallskog syd Dörby, Öl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>601243</v>
+        <v>601257</v>
       </c>
       <c r="R136" t="n">
-        <v>6276628</v>
+        <v>6276610</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15982,12 +15978,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16001,7 +15997,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -16023,7 +16019,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>3425394</v>
+        <v>3424453</v>
       </c>
       <c r="B137" t="n">
         <v>106243</v>
@@ -16059,14 +16055,14 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Öl</t>
+          <t>tallskog mellan Dörby-Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>601237</v>
+        <v>601243</v>
       </c>
       <c r="R137" t="n">
-        <v>6276677</v>
+        <v>6276628</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -16093,12 +16089,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16134,7 +16130,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>7176385</v>
+        <v>3425394</v>
       </c>
       <c r="B138" t="n">
         <v>106243</v>
@@ -16163,19 +16159,21 @@
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>601266</v>
+        <v>601237</v>
       </c>
       <c r="R138" t="n">
-        <v>6276652</v>
+        <v>6276677</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -16202,12 +16200,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16218,16 +16216,21 @@
       </c>
       <c r="AG138" t="b">
         <v>0</v>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>tallskog på sand</t>
+        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -16238,7 +16241,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>16038157</v>
+        <v>7176385</v>
       </c>
       <c r="B139" t="n">
         <v>106243</v>
@@ -16272,14 +16275,14 @@
       <c r="L139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>601227</v>
+        <v>601266</v>
       </c>
       <c r="R139" t="n">
-        <v>6276593</v>
+        <v>6276652</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -16306,12 +16309,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16322,11 +16325,6 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
@@ -16336,7 +16334,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -16347,7 +16345,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>16038171</v>
+        <v>16038157</v>
       </c>
       <c r="B140" t="n">
         <v>106243</v>
@@ -16377,11 +16375,7 @@
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -16389,10 +16383,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>601245</v>
+        <v>601227</v>
       </c>
       <c r="R140" t="n">
-        <v>6276638</v>
+        <v>6276593</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -16460,7 +16454,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>16038187</v>
+        <v>16038171</v>
       </c>
       <c r="B141" t="n">
         <v>106243</v>
@@ -16490,7 +16484,11 @@
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -16498,10 +16496,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>601269</v>
+        <v>601245</v>
       </c>
       <c r="R141" t="n">
-        <v>6276641</v>
+        <v>6276638</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -16569,7 +16567,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>16038207</v>
+        <v>16038187</v>
       </c>
       <c r="B142" t="n">
         <v>106243</v>
@@ -16607,10 +16605,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>601489</v>
+        <v>601269</v>
       </c>
       <c r="R142" t="n">
-        <v>6276715</v>
+        <v>6276641</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -16678,7 +16676,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>16038421</v>
+        <v>16038207</v>
       </c>
       <c r="B143" t="n">
         <v>106243</v>
@@ -16716,10 +16714,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>601286</v>
+        <v>601489</v>
       </c>
       <c r="R143" t="n">
-        <v>6276666</v>
+        <v>6276715</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -16787,7 +16785,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>16065773</v>
+        <v>16038421</v>
       </c>
       <c r="B144" t="n">
         <v>106243</v>
@@ -16825,10 +16823,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>601303</v>
+        <v>601286</v>
       </c>
       <c r="R144" t="n">
-        <v>6276692</v>
+        <v>6276666</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -16855,12 +16853,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16874,7 +16872,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -16885,7 +16883,7 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -16896,7 +16894,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>17204730</v>
+        <v>16065773</v>
       </c>
       <c r="B145" t="n">
         <v>106243</v>
@@ -16926,22 +16924,18 @@
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>601400</v>
+        <v>601303</v>
       </c>
       <c r="R145" t="n">
-        <v>6276601</v>
+        <v>6276692</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -16968,12 +16962,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2015-03-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2015-03-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16987,7 +16981,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -17009,7 +17003,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>54444054</v>
+        <v>17204730</v>
       </c>
       <c r="B146" t="n">
         <v>106243</v>
@@ -17039,18 +17033,22 @@
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>601271</v>
+        <v>601400</v>
       </c>
       <c r="R146" t="n">
-        <v>6276655</v>
+        <v>6276601</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -17077,12 +17075,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17096,7 +17094,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -17118,7 +17116,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>54444133</v>
+        <v>54444054</v>
       </c>
       <c r="B147" t="n">
         <v>106243</v>
@@ -17156,10 +17154,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>601309</v>
+        <v>601271</v>
       </c>
       <c r="R147" t="n">
-        <v>6276695</v>
+        <v>6276655</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -17227,7 +17225,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>54444175</v>
+        <v>54444133</v>
       </c>
       <c r="B148" t="n">
         <v>106243</v>
@@ -17265,10 +17263,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>601351</v>
+        <v>601309</v>
       </c>
       <c r="R148" t="n">
-        <v>6276607</v>
+        <v>6276695</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -17336,7 +17334,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>54511650</v>
+        <v>54444175</v>
       </c>
       <c r="B149" t="n">
         <v>106243</v>
@@ -17374,10 +17372,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>601215</v>
+        <v>601351</v>
       </c>
       <c r="R149" t="n">
-        <v>6276591</v>
+        <v>6276607</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -17404,12 +17402,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17423,18 +17421,18 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -17445,7 +17443,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>54524712</v>
+        <v>54511650</v>
       </c>
       <c r="B150" t="n">
         <v>106243</v>
@@ -17479,17 +17477,17 @@
       <c r="L150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>NO Gårdby sandhed, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>601271</v>
+        <v>601215</v>
       </c>
       <c r="R150" t="n">
-        <v>6276640</v>
+        <v>6276591</v>
       </c>
       <c r="S150" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17513,12 +17511,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2015-07-21</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2015-07-21</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17529,16 +17527,21 @@
       </c>
       <c r="AG150" t="b">
         <v>0</v>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>tallskog på sand</t>
+        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -17549,7 +17552,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>58885018</v>
+        <v>54524712</v>
       </c>
       <c r="B151" t="n">
         <v>106243</v>
@@ -17583,14 +17586,14 @@
       <c r="L151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>NO Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>601246</v>
+        <v>601271</v>
       </c>
       <c r="R151" t="n">
-        <v>6276674</v>
+        <v>6276640</v>
       </c>
       <c r="S151" t="n">
         <v>50</v>
@@ -17617,12 +17620,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2015-07-21</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2015-07-21</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17637,12 +17640,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -17653,7 +17656,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>66113422</v>
+        <v>58885018</v>
       </c>
       <c r="B152" t="n">
         <v>106243</v>
@@ -17683,11 +17686,7 @@
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -17695,10 +17694,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>601321</v>
+        <v>601246</v>
       </c>
       <c r="R152" t="n">
-        <v>6276619</v>
+        <v>6276674</v>
       </c>
       <c r="S152" t="n">
         <v>50</v>
@@ -17725,12 +17724,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17745,12 +17744,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Hans Lindfors</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Hans Lindfors</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -17761,7 +17760,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>66676941</v>
+        <v>66113422</v>
       </c>
       <c r="B153" t="n">
         <v>106243</v>
@@ -17791,21 +17790,25 @@
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Dörby tallskog, N2, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>601276</v>
+        <v>601321</v>
       </c>
       <c r="R153" t="n">
-        <v>6276684</v>
+        <v>6276619</v>
       </c>
       <c r="S153" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17829,12 +17832,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2017-06-04</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2017-06-04</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17849,12 +17852,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Hans Lindfors</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Hans Lindfors</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -17865,7 +17868,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>72346187</v>
+        <v>66676941</v>
       </c>
       <c r="B154" t="n">
         <v>106243</v>
@@ -17895,23 +17898,18 @@
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, N2, Öl</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>601215</v>
+        <v>601276</v>
       </c>
       <c r="R154" t="n">
-        <v>6276612</v>
+        <v>6276684</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -17938,12 +17936,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17952,7 +17950,6 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -17975,7 +17972,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>86801212</v>
+        <v>72346187</v>
       </c>
       <c r="B155" t="n">
         <v>106243</v>
@@ -18007,21 +18004,21 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Dörbytallskog, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>601246</v>
+        <v>601215</v>
       </c>
       <c r="R155" t="n">
-        <v>6276644</v>
+        <v>6276612</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -18048,12 +18045,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18066,20 +18063,15 @@
       <c r="AG155" t="b">
         <v>0</v>
       </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
-      </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -18090,10 +18082,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>94467626</v>
+        <v>86801212</v>
       </c>
       <c r="B156" t="n">
-        <v>106244</v>
+        <v>106243</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18119,19 +18111,24 @@
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Dörby tallskog, norr sandheden, Öl</t>
+          <t>Dörbytallskog, Öl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>601269</v>
+        <v>601246</v>
       </c>
       <c r="R156" t="n">
-        <v>6276632</v>
+        <v>6276644</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -18158,12 +18155,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18176,22 +18173,31 @@
       <c r="AG156" t="b">
         <v>0</v>
       </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>gles tallskog</t>
+        </is>
+      </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
-        </is>
-      </c>
-      <c r="AY156" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>99255605</v>
+        <v>94467626</v>
       </c>
       <c r="B157" t="n">
         <v>106244</v>
@@ -18219,29 +18225,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Gårdby-Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, norr sandheden, Öl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>601203</v>
+        <v>601269</v>
       </c>
       <c r="R157" t="n">
-        <v>6276606</v>
+        <v>6276632</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -18268,12 +18265,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18286,27 +18283,22 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>99255615</v>
+        <v>99255605</v>
       </c>
       <c r="B158" t="n">
         <v>106244</v>
@@ -18334,8 +18326,16 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
@@ -18345,10 +18345,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>601209</v>
+        <v>601203</v>
       </c>
       <c r="R158" t="n">
-        <v>6276612</v>
+        <v>6276606</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -18413,7 +18413,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>99255628</v>
+        <v>99255615</v>
       </c>
       <c r="B159" t="n">
         <v>106244</v>
@@ -18441,16 +18441,8 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
@@ -18460,10 +18452,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>601239</v>
+        <v>601209</v>
       </c>
       <c r="R159" t="n">
-        <v>6276653</v>
+        <v>6276612</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -18528,7 +18520,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>99255660</v>
+        <v>99255628</v>
       </c>
       <c r="B160" t="n">
         <v>106244</v>
@@ -18558,7 +18550,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -18575,10 +18567,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>601321</v>
+        <v>601239</v>
       </c>
       <c r="R160" t="n">
-        <v>6276611</v>
+        <v>6276653</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -18643,7 +18635,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>101612360</v>
+        <v>99255660</v>
       </c>
       <c r="B161" t="n">
         <v>106244</v>
@@ -18671,28 +18663,32 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Gårdby-Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>601240</v>
+        <v>601321</v>
       </c>
       <c r="R161" t="n">
-        <v>6276652</v>
+        <v>6276611</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18716,12 +18712,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18734,22 +18730,27 @@
       <c r="AG161" t="b">
         <v>0</v>
       </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
+      </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Erik F Nordberg</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Erik F Nordberg, Karin Andersson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126780833</v>
+        <v>101612360</v>
       </c>
       <c r="B162" t="n">
         <v>106244</v>
@@ -18779,22 +18780,26 @@
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>601288</v>
+        <v>601240</v>
       </c>
       <c r="R162" t="n">
-        <v>6276671</v>
+        <v>6276652</v>
       </c>
       <c r="S162" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18818,12 +18823,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18836,80 +18841,64 @@
       <c r="AG162" t="b">
         <v>0</v>
       </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>gallrad tallskog</t>
-        </is>
-      </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Erik F Nordberg</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Erik F Nordberg, Karin Andersson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>60656115</v>
+        <v>126780833</v>
       </c>
       <c r="B163" t="n">
-        <v>107294</v>
+        <v>106244</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>221647</v>
+        <v>221144</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Galeopsis ladanum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>601212</v>
+        <v>601288</v>
       </c>
       <c r="R163" t="n">
-        <v>6276638</v>
+        <v>6276671</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -18936,12 +18925,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18950,12 +18939,13 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>igenlagt sandtag</t>
+          <t>gallrad tallskog</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -18969,18 +18959,14 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY163" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+      <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>16065673</v>
+        <v>60656115</v>
       </c>
       <c r="B164" t="n">
-        <v>107516</v>
+        <v>107294</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18988,16 +18974,16 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221849</v>
+        <v>221647</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Galeopsis ladanum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -19005,9 +18991,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
@@ -19045,12 +19043,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19064,7 +19062,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>SANDTAG</t>
+          <t>igenlagt sandtag</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -19086,7 +19084,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>54591844</v>
+        <v>16065673</v>
       </c>
       <c r="B165" t="n">
         <v>107516</v>
@@ -19124,10 +19122,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>601143</v>
+        <v>601212</v>
       </c>
       <c r="R165" t="n">
-        <v>6276662</v>
+        <v>6276638</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -19154,12 +19152,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19173,18 +19171,18 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>fd banvall, sandig</t>
+          <t>SANDTAG</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -19195,7 +19193,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>72696139</v>
+        <v>54591844</v>
       </c>
       <c r="B166" t="n">
         <v>107516</v>
@@ -19227,17 +19225,16 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>601166</v>
+        <v>601143</v>
       </c>
       <c r="R166" t="n">
-        <v>6276823</v>
+        <v>6276662</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -19264,12 +19261,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19278,24 +19275,23 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>sandig gammal banvall</t>
+          <t>fd banvall, sandig</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -19306,27 +19302,27 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>4220789</v>
+        <v>72696139</v>
       </c>
       <c r="B167" t="n">
-        <v>97983</v>
+        <v>107516</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>221945</v>
+        <v>221849</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -19335,16 +19331,20 @@
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Dörby tallskog, öster vägen, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>601369</v>
+        <v>601166</v>
       </c>
       <c r="R167" t="n">
-        <v>6276502</v>
+        <v>6276823</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -19371,12 +19371,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2008-01-27</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2008-01-27</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19385,23 +19385,24 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>sandig tallskog med enstaka hassel/ek</t>
+          <t>sandig gammal banvall</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -19412,7 +19413,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>4220790</v>
+        <v>4220789</v>
       </c>
       <c r="B168" t="n">
         <v>97983</v>
@@ -19447,10 +19448,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>601392</v>
+        <v>601369</v>
       </c>
       <c r="R168" t="n">
-        <v>6276503</v>
+        <v>6276502</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -19518,7 +19519,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>7176403</v>
+        <v>4220790</v>
       </c>
       <c r="B169" t="n">
         <v>97983</v>
@@ -19547,19 +19548,16 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, öster vägen, Öl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>601303</v>
+        <v>601392</v>
       </c>
       <c r="R169" t="n">
-        <v>6276564</v>
+        <v>6276503</v>
       </c>
       <c r="S169" t="n">
         <v>25</v>
@@ -19586,12 +19584,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2008-01-27</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2008-01-27</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19602,16 +19600,21 @@
       </c>
       <c r="AG169" t="b">
         <v>0</v>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>sandig tallskog med enstaka hassel/ek</t>
+        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -19622,7 +19625,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>16065769</v>
+        <v>7176403</v>
       </c>
       <c r="B170" t="n">
         <v>97983</v>
@@ -19656,14 +19659,14 @@
       <c r="L170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>601312</v>
+        <v>601303</v>
       </c>
       <c r="R170" t="n">
-        <v>6276555</v>
+        <v>6276564</v>
       </c>
       <c r="S170" t="n">
         <v>25</v>
@@ -19690,12 +19693,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19706,11 +19709,6 @@
       </c>
       <c r="AG170" t="b">
         <v>0</v>
-      </c>
-      <c r="AI170" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
@@ -19731,32 +19729,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>60656163</v>
+        <v>16065769</v>
       </c>
       <c r="B171" t="n">
-        <v>100292</v>
+        <v>97983</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>222223</v>
+        <v>221945</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Apera spica-venti</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) P. Beauv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19769,10 +19767,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>601222</v>
+        <v>601312</v>
       </c>
       <c r="R171" t="n">
-        <v>6276656</v>
+        <v>6276555</v>
       </c>
       <c r="S171" t="n">
         <v>25</v>
@@ -19799,12 +19797,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19818,7 +19816,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>igenlagt sandtag</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
@@ -19840,10 +19838,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>5144080</v>
+        <v>60656163</v>
       </c>
       <c r="B172" t="n">
-        <v>100797</v>
+        <v>100292</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19851,34 +19849,37 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>222617</v>
+        <v>222223</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Apera spica-venti</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>(L.) P. Beauv.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>601216</v>
+        <v>601222</v>
       </c>
       <c r="R172" t="n">
-        <v>6276667</v>
+        <v>6276656</v>
       </c>
       <c r="S172" t="n">
         <v>25</v>
@@ -19905,12 +19906,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19924,18 +19925,18 @@
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>sandtag</t>
+          <t>igenlagt sandtag</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -19946,7 +19947,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>72345748</v>
+        <v>5144080</v>
       </c>
       <c r="B173" t="n">
         <v>100797</v>
@@ -19975,20 +19976,16 @@
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>601132</v>
+        <v>601216</v>
       </c>
       <c r="R173" t="n">
-        <v>6276668</v>
+        <v>6276667</v>
       </c>
       <c r="S173" t="n">
         <v>25</v>
@@ -20015,12 +20012,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20029,19 +20026,23 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>sandtag</t>
+        </is>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -20052,10 +20053,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>135288104</v>
+        <v>72345748</v>
       </c>
       <c r="B174" t="n">
-        <v>100875</v>
+        <v>100797</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20081,19 +20082,23 @@
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Vägområde, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>601301</v>
+        <v>601132</v>
       </c>
       <c r="R174" t="n">
-        <v>6276866</v>
+        <v>6276668</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -20117,12 +20122,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20131,70 +20136,71 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Edvin Åhman</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Edvin Åhman, Christine Sandberg</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>86801227</v>
+        <v>135288104</v>
       </c>
       <c r="B175" t="n">
-        <v>99097</v>
+        <v>100875</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>223609</v>
+        <v>222617</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr"/>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Dörbytallskog, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>601308</v>
+        <v>601301</v>
       </c>
       <c r="R175" t="n">
-        <v>6276656</v>
+        <v>6276866</v>
       </c>
       <c r="S175" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -20218,12 +20224,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20232,35 +20238,29 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127081837</v>
+        <v>86801227</v>
       </c>
       <c r="B176" t="n">
         <v>99097</v>
@@ -20284,32 +20284,24 @@
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Gårdby tallskog tornet, Öl</t>
+          <t>Dörbytallskog, Öl</t>
         </is>
       </c>
       <c r="Q176" t="n">
         <v>601308</v>
       </c>
       <c r="R176" t="n">
-        <v>6276635</v>
+        <v>6276656</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -20333,22 +20325,12 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20361,25 +20343,34 @@
       <c r="AG176" t="b">
         <v>0</v>
       </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>gles tallskog</t>
+        </is>
+      </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Rolf Kläppe</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Rolf Kläppe</t>
-        </is>
-      </c>
-      <c r="AY176" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>16071746</v>
+        <v>127081837</v>
       </c>
       <c r="B177" t="n">
-        <v>106230</v>
+        <v>99097</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20387,40 +20378,45 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>224098</v>
+        <v>223609</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Wallr.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Gårdby tallskog tornet, Öl</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>601278</v>
+        <v>601308</v>
       </c>
       <c r="R177" t="n">
-        <v>6276674</v>
+        <v>6276635</v>
       </c>
       <c r="S177" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -20444,12 +20440,22 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20458,34 +20464,26 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
-      </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Rolf Kläppe</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY177" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Rolf Kläppe</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>60656204</v>
+        <v>16071746</v>
       </c>
       <c r="B178" t="n">
         <v>106230</v>
@@ -20523,10 +20521,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>601309</v>
+        <v>601278</v>
       </c>
       <c r="R178" t="n">
-        <v>6276659</v>
+        <v>6276674</v>
       </c>
       <c r="S178" t="n">
         <v>25</v>
@@ -20553,12 +20551,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20572,7 +20570,7 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>skogsväg</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr"/>
@@ -20594,7 +20592,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>66674736</v>
+        <v>60656204</v>
       </c>
       <c r="B179" t="n">
         <v>106230</v>
@@ -20624,22 +20622,18 @@
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Dörby tallskog, N1, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>601316</v>
+        <v>601309</v>
       </c>
       <c r="R179" t="n">
-        <v>6276639</v>
+        <v>6276659</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>
@@ -20666,12 +20660,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20682,16 +20676,21 @@
       </c>
       <c r="AG179" t="b">
         <v>0</v>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>skogsväg</t>
+        </is>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Ingela Carlström</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -20702,46 +20701,52 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>6187223</v>
+        <v>66674736</v>
       </c>
       <c r="B180" t="n">
-        <v>107062</v>
+        <v>106230</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>224354</v>
+        <v>224098</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vanlig axveronika</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Veronica spicata subsp. spicata</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr"/>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
       <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Öl</t>
+          <t>Dörby tallskog, N1, Öl</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>601335</v>
+        <v>601316</v>
       </c>
       <c r="R180" t="n">
-        <v>6276698</v>
+        <v>6276639</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>
@@ -20768,12 +20773,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20784,21 +20789,16 @@
       </c>
       <c r="AG180" t="b">
         <v>0</v>
-      </c>
-      <c r="AI180" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Tommy Carlström, Ingela Carlström</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
@@ -20809,7 +20809,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>66677098</v>
+        <v>6187223</v>
       </c>
       <c r="B181" t="n">
         <v>107062</v>
@@ -20834,26 +20834,24 @@
       </c>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Dörby tallskog, infart, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>601217</v>
+        <v>601335</v>
       </c>
       <c r="R181" t="n">
-        <v>6276653</v>
+        <v>6276698</v>
       </c>
       <c r="S181" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -20877,12 +20875,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20893,16 +20891,21 @@
       </c>
       <c r="AG181" t="b">
         <v>0</v>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>tallskog på sand</t>
+        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
@@ -20913,47 +20916,51 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>54511699</v>
+        <v>66677098</v>
       </c>
       <c r="B182" t="n">
-        <v>97985</v>
+        <v>107062</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>224363</v>
+        <v>224354</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig axveronika</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Veronica spicata subsp. spicata</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, infart, Öl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>601285</v>
+        <v>601217</v>
       </c>
       <c r="R182" t="n">
-        <v>6276569</v>
+        <v>6276653</v>
       </c>
       <c r="S182" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20977,12 +20984,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20993,21 +21000,16 @@
       </c>
       <c r="AG182" t="b">
         <v>0</v>
-      </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -21018,7 +21020,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>54511702</v>
+        <v>54511699</v>
       </c>
       <c r="B183" t="n">
         <v>97985</v>
@@ -21052,10 +21054,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>601304</v>
+        <v>601285</v>
       </c>
       <c r="R183" t="n">
-        <v>6276567</v>
+        <v>6276569</v>
       </c>
       <c r="S183" t="n">
         <v>25</v>
@@ -21123,41 +21125,44 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>6247724</v>
+        <v>54511702</v>
       </c>
       <c r="B184" t="n">
-        <v>104640</v>
+        <v>97985</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>224416</v>
+        <v>224363</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>601216</v>
+        <v>601304</v>
       </c>
       <c r="R184" t="n">
-        <v>6276667</v>
+        <v>6276567</v>
       </c>
       <c r="S184" t="n">
         <v>25</v>
@@ -21184,12 +21189,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21203,7 +21208,7 @@
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>sandtag</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -21225,7 +21230,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>16065671</v>
+        <v>6247724</v>
       </c>
       <c r="B185" t="n">
         <v>104640</v>
@@ -21250,19 +21255,16 @@
       </c>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>601212</v>
+        <v>601216</v>
       </c>
       <c r="R185" t="n">
-        <v>6276638</v>
+        <v>6276667</v>
       </c>
       <c r="S185" t="n">
         <v>25</v>
@@ -21289,12 +21291,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21308,21 +21310,126 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>SANDTAG</t>
+          <t>sandtag</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>16065671</v>
+      </c>
+      <c r="B186" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Dörby tallskog, Öl</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>601212</v>
+      </c>
+      <c r="R186" t="n">
+        <v>6276638</v>
+      </c>
+      <c r="S186" t="n">
+        <v>25</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2014-07-07</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2014-07-07</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>SANDTAG</t>
+        </is>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
           <t>Ulla-Britt Andersson</t>
         </is>
       </c>
-      <c r="AX185" t="inlineStr">
+      <c r="AX186" t="inlineStr">
         <is>
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY185" t="inlineStr">
+      <c r="AY186" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY186"/>
+  <dimension ref="A1:AZ186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -786,6 +791,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16065824</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129978</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129979</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1151,6 +1171,11 @@
           <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129986</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1271,6 +1296,11 @@
           <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130944</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1386,6 +1416,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132652</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1506,6 +1541,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132653</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1621,6 +1661,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133553</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1736,6 +1781,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133554</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1861,6 +1911,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134028</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1986,6 +2041,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134029</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2111,6 +2171,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134033</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2231,6 +2296,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134049</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2351,6 +2421,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134050</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2471,6 +2546,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2591,6 +2671,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134052</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2711,6 +2796,11 @@
           <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134259</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2831,6 +2921,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2943,6 +3038,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7176384</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3055,6 +3155,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7176386</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3167,6 +3272,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7176387</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3279,6 +3389,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7176401</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3391,6 +3506,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7176402</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3512,6 +3632,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16038164</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3633,6 +3758,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16038175</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3750,6 +3880,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16038178</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3867,6 +4002,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16038186</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3984,6 +4124,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16038189</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4101,6 +4246,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16038428</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4218,6 +4368,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16038430</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4339,6 +4494,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16065788</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4456,6 +4616,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16071702</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4573,6 +4738,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16071703</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4690,6 +4860,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16071704</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4806,6 +4981,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16432436</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4923,6 +5103,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17204727</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5040,6 +5225,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17204731</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5161,6 +5351,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54444032</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5278,6 +5473,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54444046</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5395,6 +5595,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54444064</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5512,6 +5717,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54444116</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5629,6 +5839,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54444150</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5748,6 +5963,11 @@
       <c r="AY44" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54511647</t>
         </is>
       </c>
     </row>
@@ -5854,6 +6074,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54524711</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5971,6 +6196,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54592439</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6077,6 +6307,11 @@
       <c r="AY47" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54964293</t>
         </is>
       </c>
     </row>
@@ -6183,6 +6418,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56867190</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6287,6 +6527,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58885087</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6395,6 +6640,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59476530</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6503,6 +6753,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60675948</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6611,6 +6866,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66676943</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6719,6 +6979,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67231376</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6829,6 +7094,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72346124</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6939,6 +7209,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79087782</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7054,6 +7329,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86801215</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7168,6 +7448,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88752757</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7273,6 +7558,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94467631</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7388,6 +7678,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95770410</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7500,6 +7795,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99257266</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7599,6 +7899,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101733531</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7712,6 +8017,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102189039</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7818,6 +8128,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110458137</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7924,6 +8239,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117212950</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8039,6 +8359,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129903845</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8154,6 +8479,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113030917</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8257,6 +8587,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113033262</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8358,6 +8693,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113215087</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8469,6 +8809,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121707112</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8584,6 +8929,11 @@
           <t>Inventering av Ölands kärlväxtflora., Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/471548</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8704,6 +9054,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/471871</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8824,6 +9179,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/473219</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8931,6 +9291,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135447260</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9046,6 +9411,11 @@
           <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/636681</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9161,6 +9531,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/636940</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9274,6 +9649,11 @@
       <c r="AY76" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/637468</t>
         </is>
       </c>
     </row>
@@ -9383,6 +9763,11 @@
       <c r="AY77" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54591847</t>
         </is>
       </c>
     </row>
@@ -9501,6 +9886,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72696154</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9607,6 +9997,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121707046</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9711,6 +10106,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58884981</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9817,6 +10217,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13438719</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9935,6 +10340,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17012458</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10046,6 +10456,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78025936</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10157,6 +10572,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78025941</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10268,6 +10688,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78025938</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10386,6 +10811,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17021016</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10501,6 +10931,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102470713</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10619,6 +11054,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17012459</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10737,6 +11177,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17012454</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10852,6 +11297,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102470028</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10963,6 +11413,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102470721</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11078,6 +11533,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102470725</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11193,6 +11653,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86918873</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11304,6 +11769,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2149811</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11408,6 +11878,11 @@
       <c r="AY95" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2155460</t>
         </is>
       </c>
     </row>
@@ -11514,6 +11989,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7176390</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11623,6 +12103,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16038415</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11743,6 +12228,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2278736</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11847,6 +12337,11 @@
       <c r="AY99" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2914483</t>
         </is>
       </c>
     </row>
@@ -11958,6 +12453,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16038422</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12071,6 +12571,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16065665</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12182,6 +12687,11 @@
       <c r="AY102" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54511725</t>
         </is>
       </c>
     </row>
@@ -12298,6 +12808,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54591834</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12411,6 +12926,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60656187</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12519,6 +13039,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60675953</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12627,6 +13152,11 @@
       <c r="AY106" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72345744</t>
         </is>
       </c>
     </row>
@@ -12735,6 +13265,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72346273</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12836,6 +13371,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94467618</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12946,6 +13486,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110458149</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13052,6 +13597,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72345745</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13166,6 +13716,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78964858</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13281,6 +13836,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94471286</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13385,6 +13945,11 @@
       <c r="AY113" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2674129</t>
         </is>
       </c>
     </row>
@@ -13496,6 +14061,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16071705</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13602,6 +14172,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135288243</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13718,6 +14293,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3025627</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13824,6 +14404,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3026664</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13930,6 +14515,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3029119</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14041,6 +14631,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3029132</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14152,6 +14747,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3029133</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14258,6 +14858,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3029134</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14364,6 +14969,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3029135</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14489,6 +15099,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3035150</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14605,6 +15220,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3035151</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14721,6 +15341,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3035398</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14837,6 +15462,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3035399</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14962,6 +15592,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3042763</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15087,6 +15722,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3042764</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15212,6 +15852,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3042765</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15337,6 +15982,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3042766</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15455,6 +16105,11 @@
       <c r="AY131" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3052277</t>
         </is>
       </c>
     </row>
@@ -15567,6 +16222,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79945652</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15683,6 +16343,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134863685</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15794,6 +16459,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3421658</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15905,6 +16575,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3424445</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16016,6 +16691,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3424446</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16127,6 +16807,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3424453</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16236,6 +16921,11 @@
       <c r="AY138" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3425394</t>
         </is>
       </c>
     </row>
@@ -16342,6 +17032,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7176385</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16451,6 +17146,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16038157</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16562,6 +17262,11 @@
       <c r="AY141" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16038171</t>
         </is>
       </c>
     </row>
@@ -16673,6 +17378,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16038187</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16782,6 +17492,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16038207</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16891,6 +17606,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16038421</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17000,6 +17720,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16065773</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17111,6 +17836,11 @@
       <c r="AY146" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17204730</t>
         </is>
       </c>
     </row>
@@ -17222,6 +17952,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54444054</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17331,6 +18066,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54444133</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17440,6 +18180,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54444175</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17549,6 +18294,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54511650</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17653,6 +18403,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54524712</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17757,6 +18512,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58885018</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17863,6 +18623,11 @@
       <c r="AY153" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66113422</t>
         </is>
       </c>
     </row>
@@ -17969,6 +18734,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66676941</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18079,6 +18849,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72346187</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18192,6 +18967,11 @@
       <c r="AY156" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86801212</t>
         </is>
       </c>
     </row>
@@ -18295,6 +19075,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94467626</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18410,6 +19195,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99255605</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18517,6 +19307,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99255615</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18632,6 +19427,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99255628</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18747,6 +19547,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99255660</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18853,6 +19658,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101612360</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18960,6 +19770,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126780833</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19079,6 +19894,11 @@
       <c r="AY164" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60656115</t>
         </is>
       </c>
     </row>
@@ -19190,6 +20010,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16065673</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19297,6 +20122,11 @@
       <c r="AY166" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54591844</t>
         </is>
       </c>
     </row>
@@ -19410,6 +20240,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72696139</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19516,6 +20351,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4220789</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19620,6 +20460,11 @@
       <c r="AY169" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4220790</t>
         </is>
       </c>
     </row>
@@ -19726,6 +20571,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7176403</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19835,6 +20685,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16065769</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19944,6 +20799,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60656163</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20048,6 +20908,11 @@
       <c r="AY173" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5144080</t>
         </is>
       </c>
     </row>
@@ -20156,6 +21021,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72345748</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20255,6 +21125,11 @@
       <c r="AY175" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135288104</t>
         </is>
       </c>
     </row>
@@ -20364,6 +21239,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86801227</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20480,6 +21360,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127081837</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20589,6 +21474,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16071746</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20698,6 +21588,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60656204</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20806,6 +21701,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66674736</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20913,6 +21813,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6187223</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21015,6 +21920,11 @@
       <c r="AY182" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66677098</t>
         </is>
       </c>
     </row>
@@ -21122,6 +22032,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54511699</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21227,6 +22142,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54511702</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21327,6 +22247,11 @@
       <c r="AY185" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6247724</t>
         </is>
       </c>
     </row>
@@ -21434,8 +22359,200 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16065671</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -9190,7 +9190,7 @@
         <v>135447260</v>
       </c>
       <c r="B73" t="n">
-        <v>104760</v>
+        <v>104814</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>135288243</v>
       </c>
       <c r="B115" t="n">
-        <v>109896</v>
+        <v>109952</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>135288104</v>
       </c>
       <c r="B175" t="n">
-        <v>100875</v>
+        <v>100923</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -9190,7 +9190,7 @@
         <v>135447260</v>
       </c>
       <c r="B73" t="n">
-        <v>104814</v>
+        <v>104841</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>135288243</v>
       </c>
       <c r="B115" t="n">
-        <v>109952</v>
+        <v>109979</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>135288104</v>
       </c>
       <c r="B175" t="n">
-        <v>100923</v>
+        <v>100950</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ183"/>
+  <dimension ref="A1:AZ186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9187,57 +9187,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>636681</v>
+        <v>135447260</v>
       </c>
       <c r="B73" t="n">
-        <v>100693</v>
+        <v>104846</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1888</v>
+        <v>1852</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tofsäxing</t>
+          <t>Grådådra</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Koeleria glauca</t>
+          <t>Alyssum alyssoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) DC.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Gårdby-Dörby tallskog (23), Öl</t>
+          <t>Väg 925, fyndplats 020, Öl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>601286</v>
+        <v>601307</v>
       </c>
       <c r="R73" t="n">
-        <v>6276636</v>
+        <v>6276876</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9259,19 +9250,20 @@
           <t>Norra Möckleby</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>Hö-Mör-3051</t>
-        </is>
-      </c>
+      <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2007-07-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2007-07-21</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt i blom just här i vägskäl till skogsbilväg</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9286,28 +9278,28 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Öland- Floraväktarna</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/636681</t>
+          <t>https://artportalen.se/Sighting/135447260</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>636940</v>
+        <v>636681</v>
       </c>
       <c r="B74" t="n">
         <v>100693</v>
@@ -9337,7 +9329,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9347,17 +9339,17 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Gårdby-Dörby tallskog (23), Öl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>601222</v>
+        <v>601286</v>
       </c>
       <c r="R74" t="n">
-        <v>6276683</v>
+        <v>6276636</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9379,14 +9371,19 @@
           <t>Norra Möckleby</t>
         </is>
       </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Hö-Mör-3051</t>
+        </is>
+      </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2007-07-21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2007-07-21</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9397,37 +9394,32 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>sandtag</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Öland- Floraväktarna</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/636940</t>
+          <t>https://artportalen.se/Sighting/636681</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>637468</v>
+        <v>636940</v>
       </c>
       <c r="B75" t="n">
         <v>100693</v>
@@ -9457,7 +9449,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9467,14 +9459,14 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>talldunge mellan Gårdby-Dörby, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>601174</v>
+        <v>601222</v>
       </c>
       <c r="R75" t="n">
-        <v>6276841</v>
+        <v>6276683</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9501,12 +9493,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9520,7 +9512,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>f.d. banvall, kalkrik sand</t>
+          <t>sandtag</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9541,13 +9533,13 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/637468</t>
+          <t>https://artportalen.se/Sighting/636940</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>54591847</v>
+        <v>637468</v>
       </c>
       <c r="B76" t="n">
         <v>100693</v>
@@ -9575,20 +9567,26 @@
           <t>(Spreng.) DC.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>talldunge mellan Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>601143</v>
+        <v>601174</v>
       </c>
       <c r="R76" t="n">
-        <v>6276662</v>
+        <v>6276841</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9615,12 +9613,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9634,7 +9632,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>fd banvall, sandig</t>
+          <t>f.d. banvall, kalkrik sand</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9655,13 +9653,13 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54591847</t>
+          <t>https://artportalen.se/Sighting/637468</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>72696154</v>
+        <v>54591847</v>
       </c>
       <c r="B77" t="n">
         <v>100693</v>
@@ -9693,17 +9691,16 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>601173</v>
+        <v>601143</v>
       </c>
       <c r="R77" t="n">
-        <v>6276842</v>
+        <v>6276662</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9730,17 +9727,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>ganska gott om</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9749,24 +9741,23 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>sandig gammal banvall</t>
+          <t>fd banvall, sandig</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9776,43 +9767,44 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72696154</t>
+          <t>https://artportalen.se/Sighting/54591847</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121707046</v>
+        <v>72696154</v>
       </c>
       <c r="B78" t="n">
-        <v>92567</v>
+        <v>100693</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6031</v>
+        <v>1888</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tofsäxing</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Koeleria glauca</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Spreng.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9820,13 +9812,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>601443</v>
+        <v>601173</v>
       </c>
       <c r="R78" t="n">
-        <v>6276610</v>
+        <v>6276842</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9850,12 +9842,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2018-08-13</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>ganska gott om</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9870,7 +9867,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>vid basen av tall, sandigt</t>
+          <t>sandig gammal banvall</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9884,19 +9881,23 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY78" t="inlineStr"/>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121707046</t>
+          <t>https://artportalen.se/Sighting/72696154</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>58884981</v>
+        <v>121707046</v>
       </c>
       <c r="B79" t="n">
-        <v>57950</v>
+        <v>92567</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9904,44 +9905,40 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>601246</v>
+        <v>601443</v>
       </c>
       <c r="R79" t="n">
-        <v>6276674</v>
+        <v>6276610</v>
       </c>
       <c r="S79" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9965,12 +9962,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9979,55 +9976,61 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>vid basen av tall, sandigt</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/58884981</t>
+          <t>https://artportalen.se/Sighting/121707046</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>13438719</v>
+        <v>58884981</v>
       </c>
       <c r="B80" t="n">
-        <v>45049</v>
+        <v>57950</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>102021</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -10035,21 +10038,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Gårdby sandhed/talle, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>601163</v>
+        <v>601246</v>
       </c>
       <c r="R80" t="n">
-        <v>6276740</v>
+        <v>6276674</v>
       </c>
       <c r="S80" t="n">
         <v>50</v>
@@ -10076,12 +10077,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10096,49 +10097,49 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Stefan Lithner</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Stefan Lithner</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/13438719</t>
+          <t>https://artportalen.se/Sighting/58884981</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>17012458</v>
+        <v>13438719</v>
       </c>
       <c r="B81" t="n">
-        <v>9463</v>
+        <v>45049</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>102176</v>
+        <v>102021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Heddyngbagge</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bodilopsis sordida</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fabricius, 1775)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -10146,36 +10147,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Gårdby, Öl</t>
+          <t>Gårdby sandhed/talle, Öl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>601193</v>
+        <v>601163</v>
       </c>
       <c r="R81" t="n">
-        <v>6276727</v>
+        <v>6276740</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10199,12 +10188,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2006-08-01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2006-08-01</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10219,49 +10208,49 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>David Hammarberg</t>
+          <t>Stefan Lithner</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
+          <t>Stefan Lithner</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17012458</t>
+          <t>https://artportalen.se/Sighting/13438719</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>78025936</v>
+        <v>17012458</v>
       </c>
       <c r="B82" t="n">
-        <v>57947</v>
+        <v>9463</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102977</v>
+        <v>102176</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Heddyngbagge</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Bodilopsis sordida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fabricius, 1775)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -10269,19 +10258,36 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>N Gårdby, Öl</t>
+          <t>Gårdby sandhed, Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>601390</v>
+        <v>601193</v>
       </c>
       <c r="R82" t="n">
-        <v>6276813</v>
+        <v>6276727</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10305,22 +10311,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2019-05-18</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2019-05-18</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>10:11</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10335,49 +10331,49 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>David Hammarberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Guillaume Mercier, Alexandra Johansson</t>
+          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78025936</t>
+          <t>https://artportalen.se/Sighting/17012458</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>78025941</v>
+        <v>78025936</v>
       </c>
       <c r="B83" t="n">
-        <v>58238</v>
+        <v>57947</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103012</v>
+        <v>102977</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -10462,38 +10458,38 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78025941</t>
+          <t>https://artportalen.se/Sighting/78025936</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>78025938</v>
+        <v>78025941</v>
       </c>
       <c r="B84" t="n">
-        <v>58327</v>
+        <v>58238</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -10578,38 +10574,38 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78025938</t>
+          <t>https://artportalen.se/Sighting/78025941</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>17021016</v>
+        <v>78025938</v>
       </c>
       <c r="B85" t="n">
-        <v>40503</v>
+        <v>58327</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>214498</v>
+        <v>103015</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sikelsäckmal</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Coleophora lixella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Zeller, 1849</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10617,36 +10613,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Gårdby, Öl</t>
+          <t>N Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>601193</v>
+        <v>601390</v>
       </c>
       <c r="R85" t="n">
-        <v>6276727</v>
+        <v>6276813</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10670,12 +10649,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2019-05-18</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2019-05-18</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10690,27 +10679,27 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>David Hammarberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
+          <t>Linda Johannesson, Guillaume Mercier, Alexandra Johansson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17021016</t>
+          <t>https://artportalen.se/Sighting/78025938</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>102470713</v>
+        <v>17021016</v>
       </c>
       <c r="B86" t="n">
-        <v>43792</v>
+        <v>40503</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10718,21 +10707,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>215481</v>
+        <v>214498</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dubbelbandat ljusmott</t>
+          <t>Sikelsäckmal</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pyrausta ostrinalis</t>
+          <t>Coleophora lixella</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hübner, 1796)</t>
+          <t>Zeller, 1849</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -10747,7 +10736,11 @@
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr">
         <is>
           <t>lampa</t>
@@ -10755,17 +10748,17 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed, Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>601267</v>
+        <v>601193</v>
       </c>
       <c r="R86" t="n">
-        <v>6276623</v>
+        <v>6276727</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10789,12 +10782,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10803,34 +10796,33 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>David Hammarberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102470713</t>
+          <t>https://artportalen.se/Sighting/17021016</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>17012459</v>
+        <v>102470713</v>
       </c>
       <c r="B87" t="n">
-        <v>41758</v>
+        <v>43792</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10838,21 +10830,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>215656</v>
+        <v>215481</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rödlätt lövmätare</t>
+          <t>Dubbelbandat ljusmott</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Scopula rubiginata</t>
+          <t>Pyrausta ostrinalis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
+          <t>(Hübner, 1796)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -10867,11 +10859,7 @@
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>lampa</t>
@@ -10879,17 +10867,17 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Gårdby, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>601193</v>
+        <v>601267</v>
       </c>
       <c r="R87" t="n">
-        <v>6276727</v>
+        <v>6276623</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10913,12 +10901,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10927,33 +10915,34 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>David Hammarberg</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17012459</t>
+          <t>https://artportalen.se/Sighting/102470713</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>17012454</v>
+        <v>17012459</v>
       </c>
       <c r="B88" t="n">
-        <v>41451</v>
+        <v>41758</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10961,16 +10950,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>215683</v>
+        <v>215656</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mellanmätare</t>
+          <t>Rödlätt lövmätare</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phibalapteryx virgata</t>
+          <t>Scopula rubiginata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -11036,12 +11025,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2014-08-06</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2014-08-06</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11067,13 +11056,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17012454</t>
+          <t>https://artportalen.se/Sighting/17012459</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>102470028</v>
+        <v>17012454</v>
       </c>
       <c r="B89" t="n">
         <v>41451</v>
@@ -11113,7 +11102,11 @@
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr">
         <is>
           <t>lampa</t>
@@ -11121,17 +11114,17 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed, Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>601267</v>
+        <v>601193</v>
       </c>
       <c r="R89" t="n">
-        <v>6276623</v>
+        <v>6276727</v>
       </c>
       <c r="S89" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11155,12 +11148,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2014-08-06</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2014-08-06</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11169,34 +11162,33 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>David Hammarberg</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102470028</t>
+          <t>https://artportalen.se/Sighting/17012454</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>102470721</v>
+        <v>102470028</v>
       </c>
       <c r="B90" t="n">
-        <v>41667</v>
+        <v>41451</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11204,24 +11196,28 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>215766</v>
+        <v>215683</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vägtornsmätare</t>
+          <t>Mellanmätare</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Triphosa dubitata</t>
+          <t>Phibalapteryx virgata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Hufnagel, 1767)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
@@ -11303,16 +11299,16 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102470721</t>
+          <t>https://artportalen.se/Sighting/102470028</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>102470725</v>
+        <v>102470721</v>
       </c>
       <c r="B91" t="n">
-        <v>41655</v>
+        <v>41667</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11320,28 +11316,24 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>215768</v>
+        <v>215766</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svartbrun klaffmätare</t>
+          <t>Vägtornsmätare</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Philereme transversata</t>
+          <t>Triphosa dubitata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
@@ -11423,16 +11415,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102470725</t>
+          <t>https://artportalen.se/Sighting/102470721</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>86918873</v>
+        <v>102470725</v>
       </c>
       <c r="B92" t="n">
-        <v>42417</v>
+        <v>41655</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11440,21 +11432,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>215920</v>
+        <v>215768</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kalkfly</t>
+          <t>Svartbrun klaffmätare</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tyta luctuosa</t>
+          <t>Philereme transversata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Hufnagel, 1767)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11463,16 +11455,16 @@
         </is>
       </c>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>ljusfälla</t>
+          <t>lampa</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11511,12 +11503,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11543,54 +11535,71 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86918873</t>
+          <t>https://artportalen.se/Sighting/102470725</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2149811</v>
+        <v>86918873</v>
       </c>
       <c r="B93" t="n">
-        <v>111175</v>
+        <v>42417</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219677</v>
+        <v>215920</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kalkfly</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Tyta luctuosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>ljusfälla</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>barrskog söder Dörby väster landsvägen, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>601143</v>
+        <v>601267</v>
       </c>
       <c r="R93" t="n">
-        <v>6276792</v>
+        <v>6276623</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11614,17 +11623,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>4H5a NV</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11633,39 +11637,31 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>tallskog med lövinslag</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Christer Klingstedt</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2149811</t>
+          <t>https://artportalen.se/Sighting/86918873</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2155460</v>
+        <v>2149811</v>
       </c>
       <c r="B94" t="n">
         <v>111175</v>
@@ -11696,14 +11692,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>tallskog mellan Gårdby-Dörby, östra delen, Öl</t>
+          <t>barrskog söder Dörby väster landsvägen, Öl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>601603</v>
+        <v>601143</v>
       </c>
       <c r="R94" t="n">
-        <v>6276691</v>
+        <v>6276792</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11730,12 +11726,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>4H5a NV</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11749,7 +11750,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>tallskog med lövinslag</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11770,13 +11771,13 @@
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2155460</t>
+          <t>https://artportalen.se/Sighting/2149811</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>7176390</v>
+        <v>2155460</v>
       </c>
       <c r="B95" t="n">
         <v>111175</v>
@@ -11805,19 +11806,16 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>tallskog mellan Gårdby-Dörby, östra delen, Öl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>601419</v>
+        <v>601603</v>
       </c>
       <c r="R95" t="n">
-        <v>6276820</v>
+        <v>6276691</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11844,12 +11842,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11860,16 +11858,21 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11879,13 +11882,13 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7176390</t>
+          <t>https://artportalen.se/Sighting/2155460</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>16038415</v>
+        <v>7176390</v>
       </c>
       <c r="B96" t="n">
         <v>111175</v>
@@ -11919,14 +11922,14 @@
       <c r="L96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>601371</v>
+        <v>601419</v>
       </c>
       <c r="R96" t="n">
-        <v>6276796</v>
+        <v>6276820</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11953,12 +11956,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11969,11 +11972,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11983,7 +11981,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11993,16 +11991,16 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038415</t>
+          <t>https://artportalen.se/Sighting/7176390</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2278736</v>
+        <v>16038415</v>
       </c>
       <c r="B97" t="n">
-        <v>99010</v>
+        <v>111175</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12010,48 +12008,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219769</v>
+        <v>219677</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>601177</v>
+        <v>601371</v>
       </c>
       <c r="R97" t="n">
-        <v>6276650</v>
+        <v>6276796</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -12078,12 +12065,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2009-06-09</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2009-06-09</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12097,18 +12084,18 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -12118,16 +12105,16 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2278736</t>
+          <t>https://artportalen.se/Sighting/16038415</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2914483</v>
+        <v>2278736</v>
       </c>
       <c r="B98" t="n">
-        <v>99096</v>
+        <v>99010</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12135,37 +12122,51 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219798</v>
+        <v>219769</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Gårdby norr, tallskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>601212</v>
+        <v>601177</v>
       </c>
       <c r="R98" t="n">
-        <v>6276703</v>
+        <v>6276650</v>
       </c>
       <c r="S98" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12189,12 +12190,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2007-07-21</t>
+          <t>2009-06-09</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2007-07-21</t>
+          <t>2009-06-09</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12219,7 +12220,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -12229,13 +12230,13 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2914483</t>
+          <t>https://artportalen.se/Sighting/2278736</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>16038422</v>
+        <v>2914483</v>
       </c>
       <c r="B99" t="n">
         <v>99096</v>
@@ -12264,22 +12265,19 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Gårdby norr, tallskogen, Öl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>601286</v>
+        <v>601212</v>
       </c>
       <c r="R99" t="n">
-        <v>6276666</v>
+        <v>6276703</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12303,12 +12301,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2007-07-21</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2007-07-21</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12322,18 +12320,18 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -12343,13 +12341,13 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038422</t>
+          <t>https://artportalen.se/Sighting/2914483</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>16065665</v>
+        <v>16038422</v>
       </c>
       <c r="B100" t="n">
         <v>99096</v>
@@ -12379,11 +12377,7 @@
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -12391,10 +12385,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>601222</v>
+        <v>601286</v>
       </c>
       <c r="R100" t="n">
-        <v>6276656</v>
+        <v>6276666</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -12421,12 +12415,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12440,7 +12434,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>SANDTAG</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -12451,7 +12445,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12461,13 +12455,13 @@
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16065665</t>
+          <t>https://artportalen.se/Sighting/16038422</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>54511725</v>
+        <v>16065665</v>
       </c>
       <c r="B101" t="n">
         <v>99096</v>
@@ -12509,10 +12503,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>601305</v>
+        <v>601222</v>
       </c>
       <c r="R101" t="n">
-        <v>6276660</v>
+        <v>6276656</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -12539,12 +12533,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12558,18 +12552,18 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>SANDTAG</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12579,13 +12573,13 @@
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54511725</t>
+          <t>https://artportalen.se/Sighting/16065665</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>54591834</v>
+        <v>54511725</v>
       </c>
       <c r="B102" t="n">
         <v>99096</v>
@@ -12615,7 +12609,11 @@
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -12623,10 +12621,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>601143</v>
+        <v>601305</v>
       </c>
       <c r="R102" t="n">
-        <v>6276662</v>
+        <v>6276660</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12653,17 +12651,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>liknar tallknipprot subsp. orbicularis</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12677,7 +12670,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>fd banvall, sandig</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12698,13 +12691,13 @@
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54591834</t>
+          <t>https://artportalen.se/Sighting/54511725</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>60656187</v>
+        <v>54591834</v>
       </c>
       <c r="B103" t="n">
         <v>99096</v>
@@ -12734,11 +12727,7 @@
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12746,10 +12735,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>601309</v>
+        <v>601143</v>
       </c>
       <c r="R103" t="n">
-        <v>6276659</v>
+        <v>6276662</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12776,12 +12765,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2015-07-26</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>liknar tallknipprot subsp. orbicularis</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12795,18 +12789,18 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>skogsväg</t>
+          <t>fd banvall, sandig</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12816,13 +12810,13 @@
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60656187</t>
+          <t>https://artportalen.se/Sighting/54591834</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>60675953</v>
+        <v>60656187</v>
       </c>
       <c r="B104" t="n">
         <v>99096</v>
@@ -12860,14 +12854,14 @@
       <c r="L104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Dörby Tallskog, Gårdby sandhed väst, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>601300</v>
+        <v>601309</v>
       </c>
       <c r="R104" t="n">
-        <v>6276643</v>
+        <v>6276659</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12894,12 +12888,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2016-07-21</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2016-07-21</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12910,16 +12904,21 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>skogsväg</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Birgitta Davidsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Birgitta Davidsson, Gunnar Siljestrand</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12929,13 +12928,13 @@
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60675953</t>
+          <t>https://artportalen.se/Sighting/60656187</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>72345744</v>
+        <v>60675953</v>
       </c>
       <c r="B105" t="n">
         <v>99096</v>
@@ -12967,21 +12966,20 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby Tallskog, Gårdby sandhed väst, Öl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>601132</v>
+        <v>601300</v>
       </c>
       <c r="R105" t="n">
-        <v>6276668</v>
+        <v>6276643</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -13008,12 +13006,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2016-07-21</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2016-07-21</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13022,19 +13020,18 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Birgitta Davidsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Birgitta Davidsson, Gunnar Siljestrand</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -13044,13 +13041,13 @@
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72345744</t>
+          <t>https://artportalen.se/Sighting/60675953</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>72346273</v>
+        <v>72345744</v>
       </c>
       <c r="B106" t="n">
         <v>99096</v>
@@ -13080,19 +13077,23 @@
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Dörby tallskog, norr sandheden, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>601269</v>
+        <v>601132</v>
       </c>
       <c r="R106" t="n">
-        <v>6276632</v>
+        <v>6276668</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -13155,13 +13156,13 @@
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72346273</t>
+          <t>https://artportalen.se/Sighting/72345744</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>94467618</v>
+        <v>72346273</v>
       </c>
       <c r="B107" t="n">
         <v>99096</v>
@@ -13190,19 +13191,20 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Dörby tallskog, N1, Öl</t>
+          <t>Dörby tallskog, norr sandheden, Öl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>601316</v>
+        <v>601269</v>
       </c>
       <c r="R107" t="n">
-        <v>6276639</v>
+        <v>6276632</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -13229,12 +13231,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13255,19 +13257,23 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
+          <t>Ingela Carlström, Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94467618</t>
+          <t>https://artportalen.se/Sighting/72346273</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>110458149</v>
+        <v>94467618</v>
       </c>
       <c r="B108" t="n">
         <v>99096</v>
@@ -13295,32 +13301,23 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Dörby tallskog, N1, Öl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>601270</v>
+        <v>601316</v>
       </c>
       <c r="R108" t="n">
-        <v>6276638</v>
+        <v>6276639</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13344,12 +13341,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13365,27 +13362,27 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Hasse Andersson, Birgit Svensson</t>
+          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110458149</t>
+          <t>https://artportalen.se/Sighting/94467618</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>72345745</v>
+        <v>110458149</v>
       </c>
       <c r="B109" t="n">
-        <v>99142</v>
+        <v>99096</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13393,41 +13390,49 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>601132</v>
+        <v>601270</v>
       </c>
       <c r="R109" t="n">
-        <v>6276668</v>
+        <v>6276638</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13451,12 +13456,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13472,31 +13477,27 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Hasse Andersson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Hasse Andersson, Birgit Svensson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72345745</t>
+          <t>https://artportalen.se/Sighting/110458149</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>78964858</v>
+        <v>72345745</v>
       </c>
       <c r="B110" t="n">
-        <v>99156</v>
+        <v>99142</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13504,49 +13505,41 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219875</v>
+        <v>219847</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Dörrby, Tallskog, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>601274</v>
+        <v>601132</v>
       </c>
       <c r="R110" t="n">
-        <v>6276714</v>
+        <v>6276668</v>
       </c>
       <c r="S110" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13570,12 +13563,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13591,12 +13584,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Joakim Johansson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Joakim Johansson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -13606,13 +13599,13 @@
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78964858</t>
+          <t>https://artportalen.se/Sighting/72345745</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>94471286</v>
+        <v>78964858</v>
       </c>
       <c r="B111" t="n">
         <v>99156</v>
@@ -13640,7 +13633,12 @@
           <t>(Custer) Rchb.</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -13650,17 +13648,17 @@
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Vägkant norr om Gårdby sanshed, Öl</t>
+          <t>Dörrby, Tallskog, Öl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>601203</v>
+        <v>601274</v>
       </c>
       <c r="R111" t="n">
-        <v>6276671</v>
+        <v>6276714</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13684,22 +13682,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
-        </is>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13715,62 +13703,73 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Joakim Johansson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr"/>
+          <t>Joakim Johansson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94471286</t>
+          <t>https://artportalen.se/Sighting/78964858</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2674129</v>
+        <v>94471286</v>
       </c>
       <c r="B112" t="n">
-        <v>109814</v>
+        <v>99156</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220204</v>
+        <v>219875</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Vägkant norr om Gårdby sanshed, Öl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>601222</v>
+        <v>601203</v>
       </c>
       <c r="R112" t="n">
-        <v>6276683</v>
+        <v>6276671</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -13797,12 +13796,22 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2021-06-25</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2021-06-25</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13811,39 +13820,31 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>sandtag</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2674129</t>
+          <t>https://artportalen.se/Sighting/94471286</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>16071705</v>
+        <v>2674129</v>
       </c>
       <c r="B113" t="n">
         <v>109814</v>
@@ -13872,19 +13873,16 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>601272</v>
+        <v>601222</v>
       </c>
       <c r="R113" t="n">
-        <v>6276673</v>
+        <v>6276683</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -13911,12 +13909,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13930,18 +13928,18 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>sandtag</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -13951,59 +13949,57 @@
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16071705</t>
+          <t>https://artportalen.se/Sighting/2674129</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>3025627</v>
+        <v>16071705</v>
       </c>
       <c r="B114" t="n">
-        <v>99118</v>
+        <v>109814</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>220204</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Gårdby N., Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>601256</v>
+        <v>601272</v>
       </c>
       <c r="R114" t="n">
-        <v>6276584</v>
+        <v>6276673</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14027,17 +14023,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2007-08-10</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2007-08-10</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Delvis överblommad</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14051,18 +14042,18 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -14072,54 +14063,54 @@
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3025627</t>
+          <t>https://artportalen.se/Sighting/16071705</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>3026664</v>
+        <v>135288243</v>
       </c>
       <c r="B115" t="n">
-        <v>99118</v>
+        <v>109984</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>220204</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Övre Ålebäck N, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>601247</v>
+        <v>601301</v>
       </c>
       <c r="R115" t="n">
-        <v>6276600</v>
+        <v>6276866</v>
       </c>
       <c r="S115" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14143,12 +14134,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>3 plantor i blom på släntkrön 2m från beläggningen(+6plantor utanför vägområdet)</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14159,37 +14155,32 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3026664</t>
+          <t>https://artportalen.se/Sighting/135288243</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>3029119</v>
+        <v>3025627</v>
       </c>
       <c r="B116" t="n">
         <v>99118</v>
@@ -14218,19 +14209,24 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Dörby S, Öl</t>
+          <t>Gårdby N., Öl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>601245</v>
+        <v>601256</v>
       </c>
       <c r="R116" t="n">
-        <v>6276602</v>
+        <v>6276584</v>
       </c>
       <c r="S116" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14254,12 +14250,17 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2009-05-05</t>
+          <t>2007-08-10</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2009-05-05</t>
+          <t>2007-08-10</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Delvis överblommad</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14279,12 +14280,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -14294,13 +14295,13 @@
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3029119</t>
+          <t>https://artportalen.se/Sighting/3025627</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>3029132</v>
+        <v>3026664</v>
       </c>
       <c r="B117" t="n">
         <v>99118</v>
@@ -14329,24 +14330,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Övre Ålebäck N, Öl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>601226</v>
+        <v>601247</v>
       </c>
       <c r="R117" t="n">
-        <v>6276599</v>
+        <v>6276600</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14370,12 +14366,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14389,18 +14385,18 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>gles tallskog med enstaka lövträd</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -14410,13 +14406,13 @@
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3029132</t>
+          <t>https://artportalen.se/Sighting/3026664</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>3029133</v>
+        <v>3029119</v>
       </c>
       <c r="B118" t="n">
         <v>99118</v>
@@ -14447,17 +14443,17 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby S, Öl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>601222</v>
+        <v>601245</v>
       </c>
       <c r="R118" t="n">
-        <v>6276594</v>
+        <v>6276602</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14481,17 +14477,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2009-05-05</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>stort bestånd</t>
+          <t>2009-05-05</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14505,18 +14496,18 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>gles tallskog med enstaka lövträd</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -14526,13 +14517,13 @@
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3029133</t>
+          <t>https://artportalen.se/Sighting/3029119</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>3029134</v>
+        <v>3029132</v>
       </c>
       <c r="B119" t="n">
         <v>99118</v>
@@ -14561,16 +14552,21 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>601306</v>
+        <v>601226</v>
       </c>
       <c r="R119" t="n">
-        <v>6276718</v>
+        <v>6276599</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -14637,13 +14633,13 @@
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3029134</t>
+          <t>https://artportalen.se/Sighting/3029132</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>3029135</v>
+        <v>3029133</v>
       </c>
       <c r="B120" t="n">
         <v>99118</v>
@@ -14678,10 +14674,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>601299</v>
+        <v>601222</v>
       </c>
       <c r="R120" t="n">
-        <v>6276716</v>
+        <v>6276594</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -14716,6 +14712,11 @@
           <t>2009-06-03</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>stort bestånd</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -14748,13 +14749,13 @@
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3029135</t>
+          <t>https://artportalen.se/Sighting/3029133</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>3035150</v>
+        <v>3029134</v>
       </c>
       <c r="B121" t="n">
         <v>99118</v>
@@ -14782,31 +14783,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>tallskog syd Dörby, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>601317</v>
+        <v>601306</v>
       </c>
       <c r="R121" t="n">
-        <v>6276750</v>
+        <v>6276718</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -14833,17 +14820,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>hotas av avverkning</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14857,7 +14839,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>gles tallskog med enstaka lövträd</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14878,13 +14860,13 @@
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3035150</t>
+          <t>https://artportalen.se/Sighting/3029134</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>3035151</v>
+        <v>3029135</v>
       </c>
       <c r="B122" t="n">
         <v>99118</v>
@@ -14913,21 +14895,16 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>tallskog syd Dörby, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>601326</v>
+        <v>601299</v>
       </c>
       <c r="R122" t="n">
-        <v>6276771</v>
+        <v>6276716</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14954,17 +14931,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>hotas av avverkning</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14978,7 +14950,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>gles tallskog med enstaka lövträd</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14999,13 +14971,13 @@
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3035151</t>
+          <t>https://artportalen.se/Sighting/3029135</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>3035398</v>
+        <v>3035150</v>
       </c>
       <c r="B123" t="n">
         <v>99118</v>
@@ -15033,22 +15005,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>tallskog mellan Dörby-Gårdby, Öl</t>
+          <t>tallskog syd Dörby, Öl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>601300</v>
+        <v>601317</v>
       </c>
       <c r="R123" t="n">
-        <v>6276710</v>
+        <v>6276750</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -15075,17 +15056,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>ej blommande</t>
+          <t>hotas av avverkning</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15099,7 +15080,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -15120,13 +15101,13 @@
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3035398</t>
+          <t>https://artportalen.se/Sighting/3035150</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>3035399</v>
+        <v>3035151</v>
       </c>
       <c r="B124" t="n">
         <v>99118</v>
@@ -15162,14 +15143,14 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>tallskog mellan Dörby-Gårdby, Öl</t>
+          <t>tallskog syd Dörby, Öl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>601211</v>
+        <v>601326</v>
       </c>
       <c r="R124" t="n">
-        <v>6276590</v>
+        <v>6276771</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -15196,17 +15177,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>täckt av ris för avverkning</t>
+          <t>hotas av avverkning</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15220,7 +15201,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -15241,13 +15222,13 @@
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3035399</t>
+          <t>https://artportalen.se/Sighting/3035151</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>3042763</v>
+        <v>3035398</v>
       </c>
       <c r="B125" t="n">
         <v>99118</v>
@@ -15275,31 +15256,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Öl</t>
+          <t>tallskog mellan Dörby-Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>601285</v>
+        <v>601300</v>
       </c>
       <c r="R125" t="n">
-        <v>6276690</v>
+        <v>6276710</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -15326,17 +15298,17 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>5 blommande, 50 bladrosetter</t>
+          <t>ej blommande</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15371,13 +15343,13 @@
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3042763</t>
+          <t>https://artportalen.se/Sighting/3035398</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>3042764</v>
+        <v>3035399</v>
       </c>
       <c r="B126" t="n">
         <v>99118</v>
@@ -15405,31 +15377,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Öl</t>
+          <t>tallskog mellan Dörby-Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>601259</v>
+        <v>601211</v>
       </c>
       <c r="R126" t="n">
-        <v>6276711</v>
+        <v>6276590</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -15456,17 +15419,17 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>1 blommande, 2 bestånd, 14 bladrosetter</t>
+          <t>täckt av ris för avverkning</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15501,13 +15464,13 @@
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3042764</t>
+          <t>https://artportalen.se/Sighting/3035399</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>3042765</v>
+        <v>3042763</v>
       </c>
       <c r="B127" t="n">
         <v>99118</v>
@@ -15537,7 +15500,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15556,7 +15519,7 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>601330</v>
+        <v>601285</v>
       </c>
       <c r="R127" t="n">
         <v>6276690</v>
@@ -15596,7 +15559,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>4blommande, 55 bladrosetter, 2 bestånd</t>
+          <t>5 blommande, 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15631,13 +15594,13 @@
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3042765</t>
+          <t>https://artportalen.se/Sighting/3042763</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>3042766</v>
+        <v>3042764</v>
       </c>
       <c r="B128" t="n">
         <v>99118</v>
@@ -15667,12 +15630,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -15686,10 +15649,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>601317</v>
+        <v>601259</v>
       </c>
       <c r="R128" t="n">
-        <v>6276649</v>
+        <v>6276711</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -15726,7 +15689,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>9 blommande, 50 bladrosetter</t>
+          <t>1 blommande, 2 bestånd, 14 bladrosetter</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15761,13 +15724,13 @@
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3042766</t>
+          <t>https://artportalen.se/Sighting/3042764</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>3052277</v>
+        <v>3042765</v>
       </c>
       <c r="B129" t="n">
         <v>99118</v>
@@ -15797,7 +15760,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -15807,19 +15770,19 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Dörby, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>601279</v>
+        <v>601330</v>
       </c>
       <c r="R129" t="n">
-        <v>6276712</v>
+        <v>6276690</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -15846,12 +15809,17 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2011-08-31</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2011-08-31</t>
+          <t>2011-07-17</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>4blommande, 55 bladrosetter, 2 bestånd</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15865,18 +15833,18 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Sandtallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Veronika Johansson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Veronika Johansson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -15886,13 +15854,13 @@
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3052277</t>
+          <t>https://artportalen.se/Sighting/3042765</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>79945652</v>
+        <v>3042766</v>
       </c>
       <c r="B130" t="n">
         <v>99118</v>
@@ -15920,28 +15888,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>601267</v>
+        <v>601317</v>
       </c>
       <c r="R130" t="n">
-        <v>6276623</v>
+        <v>6276649</v>
       </c>
       <c r="S130" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15965,12 +15939,17 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2010-08-07</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2010-08-07</t>
+          <t>2011-07-17</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>9 blommande, 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15979,19 +15958,23 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>tallskog på sand</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -16001,16 +15984,16 @@
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79945652</t>
+          <t>https://artportalen.se/Sighting/3042766</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>134863685</v>
+        <v>3052277</v>
       </c>
       <c r="B131" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16037,24 +16020,29 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Mörbylånga, Öl</t>
+          <t>Dörby, Öl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>601249</v>
+        <v>601279</v>
       </c>
       <c r="R131" t="n">
-        <v>6276655</v>
+        <v>6276712</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -16081,22 +16069,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>07:53</t>
+          <t>2011-08-31</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>07:53</t>
+          <t>2011-08-31</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16107,71 +16085,83 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Kjell Stålberg</t>
+          <t>Veronika Johansson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Kjell Stålberg, Carolina Stålberg</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr"/>
+          <t>Veronika Johansson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134863685</t>
+          <t>https://artportalen.se/Sighting/3052277</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>3421658</v>
+        <v>79945652</v>
       </c>
       <c r="B132" t="n">
-        <v>106243</v>
+        <v>99118</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Övre Ålebäck N, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>601247</v>
+        <v>601267</v>
       </c>
       <c r="R132" t="n">
-        <v>6276600</v>
+        <v>6276623</v>
       </c>
       <c r="S132" t="n">
         <v>50</v>
@@ -16198,12 +16188,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2010-08-07</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2010-08-07</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16212,23 +16202,19 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -16238,56 +16224,60 @@
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3421658</t>
+          <t>https://artportalen.se/Sighting/79945652</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>3424445</v>
+        <v>134863685</v>
       </c>
       <c r="B133" t="n">
-        <v>106243</v>
+        <v>99195</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>tallskog syd Dörby, Öl</t>
+          <t>Mörbylånga, Öl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>601286</v>
+        <v>601249</v>
       </c>
       <c r="R133" t="n">
-        <v>6276626</v>
+        <v>6276655</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -16314,12 +16304,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16330,37 +16330,28 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Kjell Stålberg</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Kjell Stålberg, Carolina Stålberg</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3424445</t>
+          <t>https://artportalen.se/Sighting/134863685</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>3424446</v>
+        <v>3421658</v>
       </c>
       <c r="B134" t="n">
         <v>106243</v>
@@ -16391,22 +16382,22 @@
       <c r="I134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>tallskog syd Dörby, Öl</t>
+          <t>Övre Ålebäck N, Öl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>601257</v>
+        <v>601247</v>
       </c>
       <c r="R134" t="n">
-        <v>6276610</v>
+        <v>6276600</v>
       </c>
       <c r="S134" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16430,12 +16421,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16449,18 +16440,18 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -16470,13 +16461,13 @@
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3424446</t>
+          <t>https://artportalen.se/Sighting/3421658</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>3424453</v>
+        <v>3424445</v>
       </c>
       <c r="B135" t="n">
         <v>106243</v>
@@ -16507,19 +16498,19 @@
       <c r="I135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>tallskog mellan Dörby-Gårdby, Öl</t>
+          <t>tallskog syd Dörby, Öl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>601243</v>
+        <v>601286</v>
       </c>
       <c r="R135" t="n">
-        <v>6276628</v>
+        <v>6276626</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -16546,12 +16537,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16565,7 +16556,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -16586,13 +16577,13 @@
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3424453</t>
+          <t>https://artportalen.se/Sighting/3424445</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>3425394</v>
+        <v>3424446</v>
       </c>
       <c r="B136" t="n">
         <v>106243</v>
@@ -16623,19 +16614,19 @@
       <c r="I136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Öl</t>
+          <t>tallskog syd Dörby, Öl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>601237</v>
+        <v>601257</v>
       </c>
       <c r="R136" t="n">
-        <v>6276677</v>
+        <v>6276610</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -16662,12 +16653,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16681,7 +16672,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -16702,13 +16693,13 @@
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3425394</t>
+          <t>https://artportalen.se/Sighting/3424446</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>7176385</v>
+        <v>3424453</v>
       </c>
       <c r="B137" t="n">
         <v>106243</v>
@@ -16737,19 +16728,21 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>tallskog mellan Dörby-Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>601266</v>
+        <v>601243</v>
       </c>
       <c r="R137" t="n">
-        <v>6276652</v>
+        <v>6276628</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -16776,12 +16769,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16792,16 +16785,21 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>tallskog på sand</t>
+        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -16811,13 +16809,13 @@
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7176385</t>
+          <t>https://artportalen.se/Sighting/3424453</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>16038157</v>
+        <v>3425394</v>
       </c>
       <c r="B138" t="n">
         <v>106243</v>
@@ -16846,19 +16844,21 @@
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>601227</v>
+        <v>601237</v>
       </c>
       <c r="R138" t="n">
-        <v>6276593</v>
+        <v>6276677</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -16885,12 +16885,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16910,12 +16910,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -16925,13 +16925,13 @@
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038157</t>
+          <t>https://artportalen.se/Sighting/3425394</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>16038171</v>
+        <v>7176385</v>
       </c>
       <c r="B139" t="n">
         <v>106243</v>
@@ -16961,22 +16961,18 @@
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>601245</v>
+        <v>601266</v>
       </c>
       <c r="R139" t="n">
-        <v>6276638</v>
+        <v>6276652</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -17003,12 +16999,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17019,11 +17015,6 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
@@ -17033,7 +17024,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -17043,13 +17034,13 @@
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038171</t>
+          <t>https://artportalen.se/Sighting/7176385</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>16038187</v>
+        <v>16038157</v>
       </c>
       <c r="B140" t="n">
         <v>106243</v>
@@ -17087,10 +17078,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>601269</v>
+        <v>601227</v>
       </c>
       <c r="R140" t="n">
-        <v>6276641</v>
+        <v>6276593</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -17157,13 +17148,13 @@
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038187</t>
+          <t>https://artportalen.se/Sighting/16038157</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>16038207</v>
+        <v>16038171</v>
       </c>
       <c r="B141" t="n">
         <v>106243</v>
@@ -17193,7 +17184,11 @@
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -17201,10 +17196,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>601489</v>
+        <v>601245</v>
       </c>
       <c r="R141" t="n">
-        <v>6276715</v>
+        <v>6276638</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -17271,13 +17266,13 @@
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038207</t>
+          <t>https://artportalen.se/Sighting/16038171</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>16038421</v>
+        <v>16038187</v>
       </c>
       <c r="B142" t="n">
         <v>106243</v>
@@ -17315,10 +17310,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>601286</v>
+        <v>601269</v>
       </c>
       <c r="R142" t="n">
-        <v>6276666</v>
+        <v>6276641</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -17385,13 +17380,13 @@
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038421</t>
+          <t>https://artportalen.se/Sighting/16038187</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>16065773</v>
+        <v>16038207</v>
       </c>
       <c r="B143" t="n">
         <v>106243</v>
@@ -17429,10 +17424,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>601303</v>
+        <v>601489</v>
       </c>
       <c r="R143" t="n">
-        <v>6276692</v>
+        <v>6276715</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -17459,12 +17454,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17478,7 +17473,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>
@@ -17489,7 +17484,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -17499,13 +17494,13 @@
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16065773</t>
+          <t>https://artportalen.se/Sighting/16038207</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>17204730</v>
+        <v>16038421</v>
       </c>
       <c r="B144" t="n">
         <v>106243</v>
@@ -17535,22 +17530,18 @@
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>601400</v>
+        <v>601286</v>
       </c>
       <c r="R144" t="n">
-        <v>6276601</v>
+        <v>6276666</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -17577,12 +17568,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2015-03-17</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2015-03-17</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17607,7 +17598,7 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -17617,13 +17608,13 @@
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17204730</t>
+          <t>https://artportalen.se/Sighting/16038421</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>54444054</v>
+        <v>16065773</v>
       </c>
       <c r="B145" t="n">
         <v>106243</v>
@@ -17661,10 +17652,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>601271</v>
+        <v>601303</v>
       </c>
       <c r="R145" t="n">
-        <v>6276655</v>
+        <v>6276692</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -17691,12 +17682,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17731,13 +17722,13 @@
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54444054</t>
+          <t>https://artportalen.se/Sighting/16065773</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>54444133</v>
+        <v>17204730</v>
       </c>
       <c r="B146" t="n">
         <v>106243</v>
@@ -17767,18 +17758,22 @@
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>601309</v>
+        <v>601400</v>
       </c>
       <c r="R146" t="n">
-        <v>6276695</v>
+        <v>6276601</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -17805,12 +17800,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17824,7 +17819,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -17845,13 +17840,13 @@
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54444133</t>
+          <t>https://artportalen.se/Sighting/17204730</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>54444175</v>
+        <v>54444054</v>
       </c>
       <c r="B147" t="n">
         <v>106243</v>
@@ -17889,10 +17884,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>601351</v>
+        <v>601271</v>
       </c>
       <c r="R147" t="n">
-        <v>6276607</v>
+        <v>6276655</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -17959,13 +17954,13 @@
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54444175</t>
+          <t>https://artportalen.se/Sighting/54444054</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>54511650</v>
+        <v>54444133</v>
       </c>
       <c r="B148" t="n">
         <v>106243</v>
@@ -18003,10 +17998,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>601215</v>
+        <v>601309</v>
       </c>
       <c r="R148" t="n">
-        <v>6276591</v>
+        <v>6276695</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -18033,12 +18028,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18052,18 +18047,18 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -18073,13 +18068,13 @@
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54511650</t>
+          <t>https://artportalen.se/Sighting/54444133</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>54524712</v>
+        <v>54444175</v>
       </c>
       <c r="B149" t="n">
         <v>106243</v>
@@ -18113,17 +18108,17 @@
       <c r="L149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>NO Gårdby sandhed, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>601271</v>
+        <v>601351</v>
       </c>
       <c r="R149" t="n">
-        <v>6276640</v>
+        <v>6276607</v>
       </c>
       <c r="S149" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -18147,12 +18142,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2015-07-21</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2015-07-21</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18163,16 +18158,21 @@
       </c>
       <c r="AG149" t="b">
         <v>0</v>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -18182,13 +18182,13 @@
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54524712</t>
+          <t>https://artportalen.se/Sighting/54444175</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>58885018</v>
+        <v>54511650</v>
       </c>
       <c r="B150" t="n">
         <v>106243</v>
@@ -18226,13 +18226,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>601246</v>
+        <v>601215</v>
       </c>
       <c r="R150" t="n">
-        <v>6276674</v>
+        <v>6276591</v>
       </c>
       <c r="S150" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -18256,12 +18256,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18272,16 +18272,21 @@
       </c>
       <c r="AG150" t="b">
         <v>0</v>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>tallskog på sand</t>
+        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -18291,13 +18296,13 @@
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/58885018</t>
+          <t>https://artportalen.se/Sighting/54511650</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>66113422</v>
+        <v>54524712</v>
       </c>
       <c r="B151" t="n">
         <v>106243</v>
@@ -18327,22 +18332,18 @@
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>NO Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>601321</v>
+        <v>601271</v>
       </c>
       <c r="R151" t="n">
-        <v>6276619</v>
+        <v>6276640</v>
       </c>
       <c r="S151" t="n">
         <v>50</v>
@@ -18369,12 +18370,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2015-07-21</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2015-07-21</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18389,12 +18390,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Hans Lindfors</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Hans Lindfors</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -18404,13 +18405,13 @@
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66113422</t>
+          <t>https://artportalen.se/Sighting/54524712</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>66676941</v>
+        <v>58885018</v>
       </c>
       <c r="B152" t="n">
         <v>106243</v>
@@ -18444,17 +18445,17 @@
       <c r="L152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Dörby tallskog, N2, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>601276</v>
+        <v>601246</v>
       </c>
       <c r="R152" t="n">
-        <v>6276684</v>
+        <v>6276674</v>
       </c>
       <c r="S152" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -18478,12 +18479,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18498,12 +18499,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -18513,13 +18514,13 @@
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66676941</t>
+          <t>https://artportalen.se/Sighting/58885018</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>72346187</v>
+        <v>66113422</v>
       </c>
       <c r="B153" t="n">
         <v>106243</v>
@@ -18551,24 +18552,23 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>601215</v>
+        <v>601321</v>
       </c>
       <c r="R153" t="n">
-        <v>6276612</v>
+        <v>6276619</v>
       </c>
       <c r="S153" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -18592,12 +18592,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2017-06-04</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2017-06-04</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18606,19 +18606,18 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Hans Lindfors</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Hans Lindfors</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -18628,13 +18627,13 @@
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72346187</t>
+          <t>https://artportalen.se/Sighting/66113422</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>86801212</v>
+        <v>66676941</v>
       </c>
       <c r="B154" t="n">
         <v>106243</v>
@@ -18664,23 +18663,18 @@
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Dörbytallskog, Öl</t>
+          <t>Dörby tallskog, N2, Öl</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>601246</v>
+        <v>601276</v>
       </c>
       <c r="R154" t="n">
-        <v>6276644</v>
+        <v>6276684</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -18707,12 +18701,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18721,24 +18715,18 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -18748,16 +18736,16 @@
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86801212</t>
+          <t>https://artportalen.se/Sighting/66676941</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>94467626</v>
+        <v>72346187</v>
       </c>
       <c r="B155" t="n">
-        <v>106244</v>
+        <v>106243</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18783,19 +18771,24 @@
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Dörby tallskog, norr sandheden, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>601269</v>
+        <v>601215</v>
       </c>
       <c r="R155" t="n">
-        <v>6276632</v>
+        <v>6276612</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -18822,12 +18815,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18848,22 +18841,26 @@
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr"/>
+          <t>Ingela Carlström, Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94467626</t>
+          <t>https://artportalen.se/Sighting/72346187</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>99255605</v>
+        <v>86801212</v>
       </c>
       <c r="B156" t="n">
-        <v>106244</v>
+        <v>106243</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18888,29 +18885,25 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Gårdby-Dörby tallskog, Öl</t>
+          <t>Dörbytallskog, Öl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>601203</v>
+        <v>601246</v>
       </c>
       <c r="R156" t="n">
-        <v>6276606</v>
+        <v>6276644</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -18937,12 +18930,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18957,7 +18950,7 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>gles tallskog</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -18968,19 +18961,23 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY156" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99255605</t>
+          <t>https://artportalen.se/Sighting/86801212</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>99255615</v>
+        <v>94467626</v>
       </c>
       <c r="B157" t="n">
         <v>106244</v>
@@ -19009,20 +19006,19 @@
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Gårdby-Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, norr sandheden, Öl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>601209</v>
+        <v>601269</v>
       </c>
       <c r="R157" t="n">
-        <v>6276612</v>
+        <v>6276632</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -19049,12 +19045,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -19067,32 +19063,27 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99255615</t>
+          <t>https://artportalen.se/Sighting/94467626</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>99255628</v>
+        <v>99255605</v>
       </c>
       <c r="B158" t="n">
         <v>106244</v>
@@ -19122,7 +19113,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -19139,10 +19130,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>601239</v>
+        <v>601203</v>
       </c>
       <c r="R158" t="n">
-        <v>6276653</v>
+        <v>6276606</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -19206,13 +19197,13 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99255628</t>
+          <t>https://artportalen.se/Sighting/99255605</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>99255660</v>
+        <v>99255615</v>
       </c>
       <c r="B159" t="n">
         <v>106244</v>
@@ -19240,16 +19231,8 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
@@ -19259,10 +19242,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>601321</v>
+        <v>601209</v>
       </c>
       <c r="R159" t="n">
-        <v>6276611</v>
+        <v>6276612</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -19326,13 +19309,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99255660</t>
+          <t>https://artportalen.se/Sighting/99255615</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>101612360</v>
+        <v>99255628</v>
       </c>
       <c r="B160" t="n">
         <v>106244</v>
@@ -19360,28 +19343,32 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Gårdby-Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>601240</v>
+        <v>601239</v>
       </c>
       <c r="R160" t="n">
-        <v>6276652</v>
+        <v>6276653</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -19405,12 +19392,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19423,27 +19410,32 @@
       <c r="AG160" t="b">
         <v>0</v>
       </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
+      </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Erik F Nordberg</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Erik F Nordberg, Karin Andersson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101612360</t>
+          <t>https://artportalen.se/Sighting/99255628</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126780833</v>
+        <v>99255660</v>
       </c>
       <c r="B161" t="n">
         <v>106244</v>
@@ -19471,21 +19463,29 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Gårdby-Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>601288</v>
+        <v>601321</v>
       </c>
       <c r="R161" t="n">
-        <v>6276671</v>
+        <v>6276611</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -19512,12 +19512,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>gallrad tallskog</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr"/>
@@ -19543,75 +19543,68 @@
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126780833</t>
+          <t>https://artportalen.se/Sighting/99255660</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>60656115</v>
+        <v>101612360</v>
       </c>
       <c r="B162" t="n">
-        <v>107294</v>
+        <v>106244</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>221647</v>
+        <v>221144</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Galeopsis ladanum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>601212</v>
+        <v>601240</v>
       </c>
       <c r="R162" t="n">
-        <v>6276638</v>
+        <v>6276652</v>
       </c>
       <c r="S162" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -19635,12 +19628,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19649,80 +19642,73 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>igenlagt sandtag</t>
-        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Erik F Nordberg</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY162" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Erik F Nordberg, Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60656115</t>
+          <t>https://artportalen.se/Sighting/101612360</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>16065673</v>
+        <v>126780833</v>
       </c>
       <c r="B163" t="n">
-        <v>107516</v>
+        <v>106244</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>221849</v>
+        <v>221144</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>601212</v>
+        <v>601288</v>
       </c>
       <c r="R163" t="n">
-        <v>6276638</v>
+        <v>6276671</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -19749,12 +19735,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19763,12 +19749,13 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>SANDTAG</t>
+          <t>gallrad tallskog</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -19782,23 +19769,19 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY163" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+      <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16065673</t>
+          <t>https://artportalen.se/Sighting/126780833</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>54591844</v>
+        <v>60656115</v>
       </c>
       <c r="B164" t="n">
-        <v>107516</v>
+        <v>107294</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19806,16 +19789,16 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221849</v>
+        <v>221647</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Galeopsis ladanum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -19823,9 +19806,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
@@ -19833,10 +19828,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>601143</v>
+        <v>601212</v>
       </c>
       <c r="R164" t="n">
-        <v>6276662</v>
+        <v>6276638</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -19863,12 +19858,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19882,18 +19877,18 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>fd banvall, sandig</t>
+          <t>igenlagt sandtag</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -19903,13 +19898,13 @@
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54591844</t>
+          <t>https://artportalen.se/Sighting/60656115</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>72696139</v>
+        <v>16065673</v>
       </c>
       <c r="B165" t="n">
         <v>107516</v>
@@ -19941,17 +19936,16 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>601166</v>
+        <v>601212</v>
       </c>
       <c r="R165" t="n">
-        <v>6276823</v>
+        <v>6276638</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -19978,12 +19972,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19992,13 +19986,12 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>sandig gammal banvall</t>
+          <t>SANDTAG</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -20019,33 +20012,33 @@
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72696139</t>
+          <t>https://artportalen.se/Sighting/16065673</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>4220789</v>
+        <v>54591844</v>
       </c>
       <c r="B166" t="n">
-        <v>97983</v>
+        <v>107516</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>221945</v>
+        <v>221849</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -20054,16 +20047,19 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Dörby tallskog, öster vägen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>601369</v>
+        <v>601143</v>
       </c>
       <c r="R166" t="n">
-        <v>6276502</v>
+        <v>6276662</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -20090,12 +20086,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2008-01-27</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2008-01-27</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20109,7 +20105,7 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>sandig tallskog med enstaka hassel/ek</t>
+          <t>fd banvall, sandig</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
@@ -20130,33 +20126,33 @@
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4220789</t>
+          <t>https://artportalen.se/Sighting/54591844</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>4220790</v>
+        <v>72696139</v>
       </c>
       <c r="B167" t="n">
-        <v>97983</v>
+        <v>107516</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>221945</v>
+        <v>221849</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -20165,16 +20161,20 @@
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Dörby tallskog, öster vägen, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>601392</v>
+        <v>601166</v>
       </c>
       <c r="R167" t="n">
-        <v>6276503</v>
+        <v>6276823</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -20201,12 +20201,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2008-01-27</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2008-01-27</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20215,23 +20215,24 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>sandig tallskog med enstaka hassel/ek</t>
+          <t>sandig gammal banvall</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -20241,13 +20242,13 @@
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4220790</t>
+          <t>https://artportalen.se/Sighting/72696139</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>7176403</v>
+        <v>4220789</v>
       </c>
       <c r="B168" t="n">
         <v>97983</v>
@@ -20276,19 +20277,16 @@
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, öster vägen, Öl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>601303</v>
+        <v>601369</v>
       </c>
       <c r="R168" t="n">
-        <v>6276564</v>
+        <v>6276502</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -20315,12 +20313,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2008-01-27</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2008-01-27</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20331,16 +20329,21 @@
       </c>
       <c r="AG168" t="b">
         <v>0</v>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>sandig tallskog med enstaka hassel/ek</t>
+        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -20350,13 +20353,13 @@
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7176403</t>
+          <t>https://artportalen.se/Sighting/4220789</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>16065769</v>
+        <v>4220790</v>
       </c>
       <c r="B169" t="n">
         <v>97983</v>
@@ -20385,19 +20388,16 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, öster vägen, Öl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>601312</v>
+        <v>601392</v>
       </c>
       <c r="R169" t="n">
-        <v>6276555</v>
+        <v>6276503</v>
       </c>
       <c r="S169" t="n">
         <v>25</v>
@@ -20424,12 +20424,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2008-01-27</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2008-01-27</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20443,18 +20443,18 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>sandig tallskog med enstaka hassel/ek</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -20464,38 +20464,38 @@
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16065769</t>
+          <t>https://artportalen.se/Sighting/4220790</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>60656163</v>
+        <v>7176403</v>
       </c>
       <c r="B170" t="n">
-        <v>100292</v>
+        <v>97983</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>222223</v>
+        <v>221945</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Apera spica-venti</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) P. Beauv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -20504,14 +20504,14 @@
       <c r="L170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>601222</v>
+        <v>601303</v>
       </c>
       <c r="R170" t="n">
-        <v>6276656</v>
+        <v>6276564</v>
       </c>
       <c r="S170" t="n">
         <v>25</v>
@@ -20538,12 +20538,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20554,11 +20554,6 @@
       </c>
       <c r="AG170" t="b">
         <v>0</v>
-      </c>
-      <c r="AI170" t="inlineStr">
-        <is>
-          <t>igenlagt sandtag</t>
-        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
@@ -20578,51 +20573,54 @@
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60656163</t>
+          <t>https://artportalen.se/Sighting/7176403</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>5144080</v>
+        <v>16065769</v>
       </c>
       <c r="B171" t="n">
-        <v>100797</v>
+        <v>97983</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>222617</v>
+        <v>221945</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>601216</v>
+        <v>601312</v>
       </c>
       <c r="R171" t="n">
-        <v>6276667</v>
+        <v>6276555</v>
       </c>
       <c r="S171" t="n">
         <v>25</v>
@@ -20649,12 +20647,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20668,18 +20666,18 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>sandtag</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -20689,16 +20687,16 @@
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5144080</t>
+          <t>https://artportalen.se/Sighting/16065769</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>72345748</v>
+        <v>60656163</v>
       </c>
       <c r="B172" t="n">
-        <v>100797</v>
+        <v>100292</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20706,38 +20704,37 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>222617</v>
+        <v>222223</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Apera spica-venti</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>(L.) P. Beauv.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>601132</v>
+        <v>601222</v>
       </c>
       <c r="R172" t="n">
-        <v>6276668</v>
+        <v>6276656</v>
       </c>
       <c r="S172" t="n">
         <v>25</v>
@@ -20764,12 +20761,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20778,19 +20775,23 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>igenlagt sandtag</t>
+        </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -20800,51 +20801,51 @@
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72345748</t>
+          <t>https://artportalen.se/Sighting/60656163</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>86801227</v>
+        <v>5144080</v>
       </c>
       <c r="B173" t="n">
-        <v>99097</v>
+        <v>100797</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>223609</v>
+        <v>222617</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr"/>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Dörbytallskog, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>601308</v>
+        <v>601216</v>
       </c>
       <c r="R173" t="n">
-        <v>6276656</v>
+        <v>6276667</v>
       </c>
       <c r="S173" t="n">
         <v>25</v>
@@ -20871,12 +20872,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20885,24 +20886,23 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>gles tallskog</t>
+          <t>sandtag</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -20912,62 +20912,58 @@
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86801227</t>
+          <t>https://artportalen.se/Sighting/5144080</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127081837</v>
+        <v>72345748</v>
       </c>
       <c r="B174" t="n">
-        <v>99097</v>
+        <v>100797</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>223609</v>
+        <v>222617</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Gårdby tallskog tornet, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>601308</v>
+        <v>601132</v>
       </c>
       <c r="R174" t="n">
-        <v>6276635</v>
+        <v>6276668</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -20991,22 +20987,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -21022,68 +21008,69 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Rolf Kläppe</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Rolf Kläppe</t>
-        </is>
-      </c>
-      <c r="AY174" t="inlineStr"/>
+          <t>Ingela Carlström, Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127081837</t>
+          <t>https://artportalen.se/Sighting/72345748</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>16071746</v>
+        <v>135288104</v>
       </c>
       <c r="B175" t="n">
-        <v>106230</v>
+        <v>100955</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>224098</v>
+        <v>222617</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>601278</v>
+        <v>601301</v>
       </c>
       <c r="R175" t="n">
-        <v>6276674</v>
+        <v>6276866</v>
       </c>
       <c r="S175" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -21107,12 +21094,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -21123,40 +21110,35 @@
       </c>
       <c r="AG175" t="b">
         <v>0</v>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16071746</t>
+          <t>https://artportalen.se/Sighting/135288104</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>60656204</v>
+        <v>86801227</v>
       </c>
       <c r="B176" t="n">
-        <v>106230</v>
+        <v>99097</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21164,37 +21146,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>224098</v>
+        <v>223609</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Wallr.</t>
-        </is>
-      </c>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbytallskog, Öl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>601309</v>
+        <v>601308</v>
       </c>
       <c r="R176" t="n">
-        <v>6276659</v>
+        <v>6276656</v>
       </c>
       <c r="S176" t="n">
         <v>25</v>
@@ -21221,12 +21200,12 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -21235,12 +21214,13 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>skogsväg</t>
+          <t>gles tallskog</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
@@ -21251,7 +21231,7 @@
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -21261,16 +21241,16 @@
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60656204</t>
+          <t>https://artportalen.se/Sighting/86801227</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>66674736</v>
+        <v>127081837</v>
       </c>
       <c r="B177" t="n">
-        <v>106230</v>
+        <v>99097</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21278,44 +21258,45 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>224098</v>
+        <v>223609</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Wallr.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Dörby tallskog, N1, Öl</t>
+          <t>Gårdby tallskog tornet, Öl</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>601316</v>
+        <v>601308</v>
       </c>
       <c r="R177" t="n">
-        <v>6276639</v>
+        <v>6276635</v>
       </c>
       <c r="S177" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -21339,12 +21320,22 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -21353,73 +21344,72 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Rolf Kläppe</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Ingela Carlström</t>
-        </is>
-      </c>
-      <c r="AY177" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Rolf Kläppe</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66674736</t>
+          <t>https://artportalen.se/Sighting/127081837</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>6187223</v>
+        <v>16071746</v>
       </c>
       <c r="B178" t="n">
-        <v>107062</v>
+        <v>106230</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>224354</v>
+        <v>224098</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vanlig axveronika</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Veronica spicata subsp. spicata</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr"/>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
       <c r="I178" t="inlineStr"/>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>601335</v>
+        <v>601278</v>
       </c>
       <c r="R178" t="n">
-        <v>6276698</v>
+        <v>6276674</v>
       </c>
       <c r="S178" t="n">
         <v>25</v>
@@ -21446,12 +21436,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21465,18 +21455,18 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -21486,57 +21476,57 @@
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6187223</t>
+          <t>https://artportalen.se/Sighting/16071746</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>66677098</v>
+        <v>60656204</v>
       </c>
       <c r="B179" t="n">
-        <v>107062</v>
+        <v>106230</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>224354</v>
+        <v>224098</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vanlig axveronika</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Veronica spicata subsp. spicata</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr"/>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Dörby tallskog, infart, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>601217</v>
+        <v>601309</v>
       </c>
       <c r="R179" t="n">
-        <v>6276653</v>
+        <v>6276659</v>
       </c>
       <c r="S179" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -21560,12 +21550,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -21576,16 +21566,21 @@
       </c>
       <c r="AG179" t="b">
         <v>0</v>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>skogsväg</t>
+        </is>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -21595,16 +21590,16 @@
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66677098</t>
+          <t>https://artportalen.se/Sighting/60656204</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>54511699</v>
+        <v>66674736</v>
       </c>
       <c r="B180" t="n">
-        <v>97985</v>
+        <v>106230</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21612,33 +21607,41 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>224363</v>
+        <v>224098</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr"/>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, N1, Öl</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>601285</v>
+        <v>601316</v>
       </c>
       <c r="R180" t="n">
-        <v>6276569</v>
+        <v>6276639</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>
@@ -21665,12 +21668,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21681,21 +21684,16 @@
       </c>
       <c r="AG180" t="b">
         <v>0</v>
-      </c>
-      <c r="AI180" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Tommy Carlström, Ingela Carlström</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
@@ -21705,50 +21703,52 @@
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54511699</t>
+          <t>https://artportalen.se/Sighting/66674736</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>54511702</v>
+        <v>6187223</v>
       </c>
       <c r="B181" t="n">
-        <v>97985</v>
+        <v>107062</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>224363</v>
+        <v>224354</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig axveronika</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Veronica spicata subsp. spicata</t>
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>601304</v>
+        <v>601335</v>
       </c>
       <c r="R181" t="n">
-        <v>6276567</v>
+        <v>6276698</v>
       </c>
       <c r="S181" t="n">
         <v>25</v>
@@ -21775,12 +21775,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21815,16 +21815,16 @@
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54511702</t>
+          <t>https://artportalen.se/Sighting/6187223</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>6247724</v>
+        <v>66677098</v>
       </c>
       <c r="B182" t="n">
-        <v>104640</v>
+        <v>107062</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21832,33 +21832,40 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>224416</v>
+        <v>224354</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Vanlig axveronika</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
+          <t>Veronica spicata subsp. spicata</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, infart, Öl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>601216</v>
+        <v>601217</v>
       </c>
       <c r="R182" t="n">
-        <v>6276667</v>
+        <v>6276653</v>
       </c>
       <c r="S182" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21882,12 +21889,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21898,21 +21905,16 @@
       </c>
       <c r="AG182" t="b">
         <v>0</v>
-      </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>sandtag</t>
-        </is>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -21922,33 +21924,33 @@
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6247724</t>
+          <t>https://artportalen.se/Sighting/66677098</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>16065671</v>
+        <v>54511699</v>
       </c>
       <c r="B183" t="n">
-        <v>104640</v>
+        <v>97985</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>224416</v>
+        <v>224363</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
@@ -21962,10 +21964,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>601212</v>
+        <v>601285</v>
       </c>
       <c r="R183" t="n">
-        <v>6276638</v>
+        <v>6276569</v>
       </c>
       <c r="S183" t="n">
         <v>25</v>
@@ -21992,12 +21994,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -22011,26 +22013,353 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>SANDTAG</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54511699</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>54511702</v>
+      </c>
+      <c r="B184" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Dörby tallskog, Öl</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>601304</v>
+      </c>
+      <c r="R184" t="n">
+        <v>6276567</v>
+      </c>
+      <c r="S184" t="n">
+        <v>25</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2015-07-20</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2015-07-20</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>tallskog på sand</t>
+        </is>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54511702</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>6247724</v>
+      </c>
+      <c r="B185" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Dörby tallskog, Öl</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>601216</v>
+      </c>
+      <c r="R185" t="n">
+        <v>6276667</v>
+      </c>
+      <c r="S185" t="n">
+        <v>25</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2009-06-03</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2009-06-03</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>sandtag</t>
+        </is>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6247724</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>16065671</v>
+      </c>
+      <c r="B186" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Dörby tallskog, Öl</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>601212</v>
+      </c>
+      <c r="R186" t="n">
+        <v>6276638</v>
+      </c>
+      <c r="S186" t="n">
+        <v>25</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2014-07-07</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2014-07-07</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>SANDTAG</t>
+        </is>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
           <t>Ulla-Britt Andersson</t>
         </is>
       </c>
-      <c r="AX183" t="inlineStr">
+      <c r="AX186" t="inlineStr">
         <is>
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY183" t="inlineStr">
+      <c r="AY186" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
-      <c r="AZ183" t="inlineStr">
+      <c r="AZ186" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/16065671</t>
         </is>
@@ -22220,6 +22549,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ186"/>
+  <dimension ref="A1:AZ187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9190,7 +9190,7 @@
         <v>135447260</v>
       </c>
       <c r="B73" t="n">
-        <v>104846</v>
+        <v>104848</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -13494,10 +13494,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>72345745</v>
+        <v>135914235</v>
       </c>
       <c r="B110" t="n">
-        <v>99142</v>
+        <v>99254</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13505,41 +13505,46 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>601132</v>
+        <v>601302</v>
       </c>
       <c r="R110" t="n">
-        <v>6276668</v>
+        <v>6276648</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13563,12 +13568,22 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13577,38 +13592,33 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Erik F Nordberg</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Erik F Nordberg, Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72345745</t>
+          <t>https://artportalen.se/Sighting/135914235</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>78964858</v>
+        <v>72345745</v>
       </c>
       <c r="B111" t="n">
-        <v>99156</v>
+        <v>99142</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13616,49 +13626,41 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219875</v>
+        <v>219847</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Dörrby, Tallskog, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>601274</v>
+        <v>601132</v>
       </c>
       <c r="R111" t="n">
-        <v>6276714</v>
+        <v>6276668</v>
       </c>
       <c r="S111" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13682,12 +13684,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13703,12 +13705,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Joakim Johansson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Joakim Johansson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -13718,13 +13720,13 @@
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78964858</t>
+          <t>https://artportalen.se/Sighting/72345745</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>94471286</v>
+        <v>78964858</v>
       </c>
       <c r="B112" t="n">
         <v>99156</v>
@@ -13752,7 +13754,12 @@
           <t>(Custer) Rchb.</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -13762,17 +13769,17 @@
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Vägkant norr om Gårdby sanshed, Öl</t>
+          <t>Dörrby, Tallskog, Öl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>601203</v>
+        <v>601274</v>
       </c>
       <c r="R112" t="n">
-        <v>6276671</v>
+        <v>6276714</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13796,22 +13803,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13827,62 +13824,73 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Joakim Johansson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr"/>
+          <t>Joakim Johansson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94471286</t>
+          <t>https://artportalen.se/Sighting/78964858</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2674129</v>
+        <v>94471286</v>
       </c>
       <c r="B113" t="n">
-        <v>109814</v>
+        <v>99156</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220204</v>
+        <v>219875</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Vägkant norr om Gårdby sanshed, Öl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>601222</v>
+        <v>601203</v>
       </c>
       <c r="R113" t="n">
-        <v>6276683</v>
+        <v>6276671</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -13909,12 +13917,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2021-06-25</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2021-06-25</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13923,39 +13941,31 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>sandtag</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2674129</t>
+          <t>https://artportalen.se/Sighting/94471286</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>16071705</v>
+        <v>2674129</v>
       </c>
       <c r="B114" t="n">
         <v>109814</v>
@@ -13984,19 +13994,16 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>601272</v>
+        <v>601222</v>
       </c>
       <c r="R114" t="n">
-        <v>6276673</v>
+        <v>6276683</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14023,12 +14030,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14042,18 +14049,18 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>sandtag</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -14063,16 +14070,16 @@
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16071705</t>
+          <t>https://artportalen.se/Sighting/2674129</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135288243</v>
+        <v>16071705</v>
       </c>
       <c r="B115" t="n">
-        <v>109984</v>
+        <v>109814</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14098,19 +14105,22 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Vägområde, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>601301</v>
+        <v>601272</v>
       </c>
       <c r="R115" t="n">
-        <v>6276866</v>
+        <v>6276673</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14134,17 +14144,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>3 plantor i blom på släntkrön 2m från beläggningen(+6plantor utanför vägområdet)</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14155,75 +14160,75 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Edvin Åhman</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Edvin Åhman, Christine Sandberg</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135288243</t>
+          <t>https://artportalen.se/Sighting/16071705</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>3025627</v>
+        <v>135288243</v>
       </c>
       <c r="B116" t="n">
-        <v>99118</v>
+        <v>109986</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>220204</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Gårdby N., Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>601256</v>
+        <v>601301</v>
       </c>
       <c r="R116" t="n">
-        <v>6276584</v>
+        <v>6276866</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14250,17 +14255,17 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2007-08-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2007-08-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Delvis överblommad</t>
+          <t>3 plantor i blom på släntkrön 2m från beläggningen(+6plantor utanför vägområdet)</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14271,37 +14276,32 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3025627</t>
+          <t>https://artportalen.se/Sighting/135288243</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>3026664</v>
+        <v>3025627</v>
       </c>
       <c r="B117" t="n">
         <v>99118</v>
@@ -14330,19 +14330,24 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Övre Ålebäck N, Öl</t>
+          <t>Gårdby N., Öl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>601247</v>
+        <v>601256</v>
       </c>
       <c r="R117" t="n">
-        <v>6276600</v>
+        <v>6276584</v>
       </c>
       <c r="S117" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14366,12 +14371,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2007-08-10</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2007-08-10</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Delvis överblommad</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14391,12 +14401,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -14406,13 +14416,13 @@
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3026664</t>
+          <t>https://artportalen.se/Sighting/3025627</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>3029119</v>
+        <v>3026664</v>
       </c>
       <c r="B118" t="n">
         <v>99118</v>
@@ -14443,14 +14453,14 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Dörby S, Öl</t>
+          <t>Övre Ålebäck N, Öl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>601245</v>
+        <v>601247</v>
       </c>
       <c r="R118" t="n">
-        <v>6276602</v>
+        <v>6276600</v>
       </c>
       <c r="S118" t="n">
         <v>50</v>
@@ -14477,12 +14487,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2009-05-05</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2009-05-05</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14517,13 +14527,13 @@
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3029119</t>
+          <t>https://artportalen.se/Sighting/3026664</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>3029132</v>
+        <v>3029119</v>
       </c>
       <c r="B119" t="n">
         <v>99118</v>
@@ -14552,24 +14562,19 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby S, Öl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>601226</v>
+        <v>601245</v>
       </c>
       <c r="R119" t="n">
-        <v>6276599</v>
+        <v>6276602</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14593,12 +14598,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2009-05-05</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2009-05-05</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14612,18 +14617,18 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>gles tallskog med enstaka lövträd</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -14633,13 +14638,13 @@
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3029132</t>
+          <t>https://artportalen.se/Sighting/3029119</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>3029133</v>
+        <v>3029132</v>
       </c>
       <c r="B120" t="n">
         <v>99118</v>
@@ -14668,16 +14673,21 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>601222</v>
+        <v>601226</v>
       </c>
       <c r="R120" t="n">
-        <v>6276594</v>
+        <v>6276599</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -14712,11 +14722,6 @@
           <t>2009-06-03</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>stort bestånd</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -14749,13 +14754,13 @@
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3029133</t>
+          <t>https://artportalen.se/Sighting/3029132</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>3029134</v>
+        <v>3029133</v>
       </c>
       <c r="B121" t="n">
         <v>99118</v>
@@ -14790,10 +14795,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>601306</v>
+        <v>601222</v>
       </c>
       <c r="R121" t="n">
-        <v>6276718</v>
+        <v>6276594</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -14828,6 +14833,11 @@
           <t>2009-06-03</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>stort bestånd</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -14860,13 +14870,13 @@
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3029134</t>
+          <t>https://artportalen.se/Sighting/3029133</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>3029135</v>
+        <v>3029134</v>
       </c>
       <c r="B122" t="n">
         <v>99118</v>
@@ -14901,10 +14911,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>601299</v>
+        <v>601306</v>
       </c>
       <c r="R122" t="n">
-        <v>6276716</v>
+        <v>6276718</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14971,13 +14981,13 @@
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3029135</t>
+          <t>https://artportalen.se/Sighting/3029134</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>3035150</v>
+        <v>3029135</v>
       </c>
       <c r="B123" t="n">
         <v>99118</v>
@@ -15005,31 +15015,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>tallskog syd Dörby, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>601317</v>
+        <v>601299</v>
       </c>
       <c r="R123" t="n">
-        <v>6276750</v>
+        <v>6276716</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -15056,17 +15052,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>hotas av avverkning</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15080,7 +15071,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>gles tallskog med enstaka lövträd</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -15101,13 +15092,13 @@
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3035150</t>
+          <t>https://artportalen.se/Sighting/3029135</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>3035151</v>
+        <v>3035150</v>
       </c>
       <c r="B124" t="n">
         <v>99118</v>
@@ -15135,10 +15126,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -15147,10 +15147,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>601326</v>
+        <v>601317</v>
       </c>
       <c r="R124" t="n">
-        <v>6276771</v>
+        <v>6276750</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -15222,13 +15222,13 @@
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3035151</t>
+          <t>https://artportalen.se/Sighting/3035150</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>3035398</v>
+        <v>3035151</v>
       </c>
       <c r="B125" t="n">
         <v>99118</v>
@@ -15264,14 +15264,14 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>tallskog mellan Dörby-Gårdby, Öl</t>
+          <t>tallskog syd Dörby, Öl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>601300</v>
+        <v>601326</v>
       </c>
       <c r="R125" t="n">
-        <v>6276710</v>
+        <v>6276771</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -15298,17 +15298,17 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>ej blommande</t>
+          <t>hotas av avverkning</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -15343,13 +15343,13 @@
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3035398</t>
+          <t>https://artportalen.se/Sighting/3035151</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>3035399</v>
+        <v>3035398</v>
       </c>
       <c r="B126" t="n">
         <v>99118</v>
@@ -15389,10 +15389,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>601211</v>
+        <v>601300</v>
       </c>
       <c r="R126" t="n">
-        <v>6276590</v>
+        <v>6276710</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -15429,7 +15429,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>täckt av ris för avverkning</t>
+          <t>ej blommande</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15464,13 +15464,13 @@
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3035399</t>
+          <t>https://artportalen.se/Sighting/3035398</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>3042763</v>
+        <v>3035399</v>
       </c>
       <c r="B127" t="n">
         <v>99118</v>
@@ -15498,31 +15498,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Öl</t>
+          <t>tallskog mellan Dörby-Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>601285</v>
+        <v>601211</v>
       </c>
       <c r="R127" t="n">
-        <v>6276690</v>
+        <v>6276590</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -15549,17 +15540,17 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>5 blommande, 50 bladrosetter</t>
+          <t>täckt av ris för avverkning</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15594,13 +15585,13 @@
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3042763</t>
+          <t>https://artportalen.se/Sighting/3035399</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>3042764</v>
+        <v>3042763</v>
       </c>
       <c r="B128" t="n">
         <v>99118</v>
@@ -15630,7 +15621,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -15649,10 +15640,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>601259</v>
+        <v>601285</v>
       </c>
       <c r="R128" t="n">
-        <v>6276711</v>
+        <v>6276690</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -15689,7 +15680,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>1 blommande, 2 bestånd, 14 bladrosetter</t>
+          <t>5 blommande, 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15724,13 +15715,13 @@
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3042764</t>
+          <t>https://artportalen.se/Sighting/3042763</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>3042765</v>
+        <v>3042764</v>
       </c>
       <c r="B129" t="n">
         <v>99118</v>
@@ -15760,7 +15751,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -15779,10 +15770,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>601330</v>
+        <v>601259</v>
       </c>
       <c r="R129" t="n">
-        <v>6276690</v>
+        <v>6276711</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -15819,7 +15810,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>4blommande, 55 bladrosetter, 2 bestånd</t>
+          <t>1 blommande, 2 bestånd, 14 bladrosetter</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15854,13 +15845,13 @@
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3042765</t>
+          <t>https://artportalen.se/Sighting/3042764</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>3042766</v>
+        <v>3042765</v>
       </c>
       <c r="B130" t="n">
         <v>99118</v>
@@ -15890,12 +15881,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -15909,10 +15900,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>601317</v>
+        <v>601330</v>
       </c>
       <c r="R130" t="n">
-        <v>6276649</v>
+        <v>6276690</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -15949,7 +15940,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>9 blommande, 50 bladrosetter</t>
+          <t>4blommande, 55 bladrosetter, 2 bestånd</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15984,13 +15975,13 @@
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3042766</t>
+          <t>https://artportalen.se/Sighting/3042765</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>3052277</v>
+        <v>3042766</v>
       </c>
       <c r="B131" t="n">
         <v>99118</v>
@@ -16020,29 +16011,29 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Dörby, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>601279</v>
+        <v>601317</v>
       </c>
       <c r="R131" t="n">
-        <v>6276712</v>
+        <v>6276649</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -16069,12 +16060,17 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2011-08-31</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2011-08-31</t>
+          <t>2011-07-17</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>9 blommande, 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16088,18 +16084,18 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>Sandtallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Veronika Johansson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Veronika Johansson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -16109,13 +16105,13 @@
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3052277</t>
+          <t>https://artportalen.se/Sighting/3042766</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>79945652</v>
+        <v>3052277</v>
       </c>
       <c r="B132" t="n">
         <v>99118</v>
@@ -16143,28 +16139,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Dörby, Öl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>601267</v>
+        <v>601279</v>
       </c>
       <c r="R132" t="n">
-        <v>6276623</v>
+        <v>6276712</v>
       </c>
       <c r="S132" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16188,12 +16190,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2010-08-07</t>
+          <t>2011-08-31</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2010-08-07</t>
+          <t>2011-08-31</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16202,19 +16204,23 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>Veronika Johansson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>Veronika Johansson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -16224,16 +16230,16 @@
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79945652</t>
+          <t>https://artportalen.se/Sighting/3052277</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>134863685</v>
+        <v>79945652</v>
       </c>
       <c r="B133" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16258,29 +16264,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Mörbylånga, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>601249</v>
+        <v>601267</v>
       </c>
       <c r="R133" t="n">
-        <v>6276655</v>
+        <v>6276623</v>
       </c>
       <c r="S133" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16304,22 +16309,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>07:53</t>
+          <t>2010-08-07</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>07:53</t>
+          <t>2010-08-07</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16328,76 +16323,85 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Kjell Stålberg</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Kjell Stålberg, Carolina Stålberg</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr"/>
+          <t>Christer Klingstedt</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134863685</t>
+          <t>https://artportalen.se/Sighting/79945652</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>3421658</v>
+        <v>134863685</v>
       </c>
       <c r="B134" t="n">
-        <v>106243</v>
+        <v>99276</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Övre Ålebäck N, Öl</t>
+          <t>Mörbylånga, Öl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>601247</v>
+        <v>601249</v>
       </c>
       <c r="R134" t="n">
-        <v>6276600</v>
+        <v>6276655</v>
       </c>
       <c r="S134" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16421,12 +16425,22 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16437,37 +16451,28 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Kjell Stålberg</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Kjell Stålberg, Carolina Stålberg</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3421658</t>
+          <t>https://artportalen.se/Sighting/134863685</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>3424445</v>
+        <v>3421658</v>
       </c>
       <c r="B135" t="n">
         <v>106243</v>
@@ -16498,22 +16503,22 @@
       <c r="I135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>tallskog syd Dörby, Öl</t>
+          <t>Övre Ålebäck N, Öl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>601286</v>
+        <v>601247</v>
       </c>
       <c r="R135" t="n">
-        <v>6276626</v>
+        <v>6276600</v>
       </c>
       <c r="S135" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16537,12 +16542,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16556,18 +16561,18 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -16577,13 +16582,13 @@
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3424445</t>
+          <t>https://artportalen.se/Sighting/3421658</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>3424446</v>
+        <v>3424445</v>
       </c>
       <c r="B136" t="n">
         <v>106243</v>
@@ -16623,10 +16628,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>601257</v>
+        <v>601286</v>
       </c>
       <c r="R136" t="n">
-        <v>6276610</v>
+        <v>6276626</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -16693,13 +16698,13 @@
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3424446</t>
+          <t>https://artportalen.se/Sighting/3424445</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>3424453</v>
+        <v>3424446</v>
       </c>
       <c r="B137" t="n">
         <v>106243</v>
@@ -16730,19 +16735,19 @@
       <c r="I137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>tallskog mellan Dörby-Gårdby, Öl</t>
+          <t>tallskog syd Dörby, Öl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>601243</v>
+        <v>601257</v>
       </c>
       <c r="R137" t="n">
-        <v>6276628</v>
+        <v>6276610</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -16769,12 +16774,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16788,7 +16793,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -16809,13 +16814,13 @@
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3424453</t>
+          <t>https://artportalen.se/Sighting/3424446</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>3425394</v>
+        <v>3424453</v>
       </c>
       <c r="B138" t="n">
         <v>106243</v>
@@ -16851,14 +16856,14 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Öl</t>
+          <t>tallskog mellan Dörby-Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>601237</v>
+        <v>601243</v>
       </c>
       <c r="R138" t="n">
-        <v>6276677</v>
+        <v>6276628</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -16885,12 +16890,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16925,13 +16930,13 @@
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3425394</t>
+          <t>https://artportalen.se/Sighting/3424453</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>7176385</v>
+        <v>3425394</v>
       </c>
       <c r="B139" t="n">
         <v>106243</v>
@@ -16960,19 +16965,21 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>601266</v>
+        <v>601237</v>
       </c>
       <c r="R139" t="n">
-        <v>6276652</v>
+        <v>6276677</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -16999,12 +17006,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17015,16 +17022,21 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>tallskog på sand</t>
+        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -17034,13 +17046,13 @@
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7176385</t>
+          <t>https://artportalen.se/Sighting/3425394</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>16038157</v>
+        <v>7176385</v>
       </c>
       <c r="B140" t="n">
         <v>106243</v>
@@ -17074,14 +17086,14 @@
       <c r="L140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>601227</v>
+        <v>601266</v>
       </c>
       <c r="R140" t="n">
-        <v>6276593</v>
+        <v>6276652</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -17108,12 +17120,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17124,11 +17136,6 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
@@ -17138,7 +17145,7 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -17148,13 +17155,13 @@
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038157</t>
+          <t>https://artportalen.se/Sighting/7176385</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>16038171</v>
+        <v>16038157</v>
       </c>
       <c r="B141" t="n">
         <v>106243</v>
@@ -17184,11 +17191,7 @@
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -17196,10 +17199,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>601245</v>
+        <v>601227</v>
       </c>
       <c r="R141" t="n">
-        <v>6276638</v>
+        <v>6276593</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -17266,13 +17269,13 @@
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038171</t>
+          <t>https://artportalen.se/Sighting/16038157</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>16038187</v>
+        <v>16038171</v>
       </c>
       <c r="B142" t="n">
         <v>106243</v>
@@ -17302,7 +17305,11 @@
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -17310,10 +17317,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>601269</v>
+        <v>601245</v>
       </c>
       <c r="R142" t="n">
-        <v>6276641</v>
+        <v>6276638</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -17380,13 +17387,13 @@
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038187</t>
+          <t>https://artportalen.se/Sighting/16038171</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>16038207</v>
+        <v>16038187</v>
       </c>
       <c r="B143" t="n">
         <v>106243</v>
@@ -17424,10 +17431,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>601489</v>
+        <v>601269</v>
       </c>
       <c r="R143" t="n">
-        <v>6276715</v>
+        <v>6276641</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -17494,13 +17501,13 @@
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038207</t>
+          <t>https://artportalen.se/Sighting/16038187</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>16038421</v>
+        <v>16038207</v>
       </c>
       <c r="B144" t="n">
         <v>106243</v>
@@ -17538,10 +17545,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>601286</v>
+        <v>601489</v>
       </c>
       <c r="R144" t="n">
-        <v>6276666</v>
+        <v>6276715</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -17608,13 +17615,13 @@
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038421</t>
+          <t>https://artportalen.se/Sighting/16038207</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>16065773</v>
+        <v>16038421</v>
       </c>
       <c r="B145" t="n">
         <v>106243</v>
@@ -17652,10 +17659,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>601303</v>
+        <v>601286</v>
       </c>
       <c r="R145" t="n">
-        <v>6276692</v>
+        <v>6276666</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -17682,12 +17689,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17701,7 +17708,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -17712,7 +17719,7 @@
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -17722,13 +17729,13 @@
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16065773</t>
+          <t>https://artportalen.se/Sighting/16038421</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>17204730</v>
+        <v>16065773</v>
       </c>
       <c r="B146" t="n">
         <v>106243</v>
@@ -17758,22 +17765,18 @@
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>601400</v>
+        <v>601303</v>
       </c>
       <c r="R146" t="n">
-        <v>6276601</v>
+        <v>6276692</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -17800,12 +17803,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2015-03-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2015-03-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17819,7 +17822,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -17840,13 +17843,13 @@
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17204730</t>
+          <t>https://artportalen.se/Sighting/16065773</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>54444054</v>
+        <v>17204730</v>
       </c>
       <c r="B147" t="n">
         <v>106243</v>
@@ -17876,18 +17879,22 @@
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>601271</v>
+        <v>601400</v>
       </c>
       <c r="R147" t="n">
-        <v>6276655</v>
+        <v>6276601</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -17914,12 +17921,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17933,7 +17940,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -17954,13 +17961,13 @@
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54444054</t>
+          <t>https://artportalen.se/Sighting/17204730</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>54444133</v>
+        <v>54444054</v>
       </c>
       <c r="B148" t="n">
         <v>106243</v>
@@ -17998,10 +18005,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>601309</v>
+        <v>601271</v>
       </c>
       <c r="R148" t="n">
-        <v>6276695</v>
+        <v>6276655</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -18068,13 +18075,13 @@
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54444133</t>
+          <t>https://artportalen.se/Sighting/54444054</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>54444175</v>
+        <v>54444133</v>
       </c>
       <c r="B149" t="n">
         <v>106243</v>
@@ -18112,10 +18119,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>601351</v>
+        <v>601309</v>
       </c>
       <c r="R149" t="n">
-        <v>6276607</v>
+        <v>6276695</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -18182,13 +18189,13 @@
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54444175</t>
+          <t>https://artportalen.se/Sighting/54444133</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>54511650</v>
+        <v>54444175</v>
       </c>
       <c r="B150" t="n">
         <v>106243</v>
@@ -18226,10 +18233,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>601215</v>
+        <v>601351</v>
       </c>
       <c r="R150" t="n">
-        <v>6276591</v>
+        <v>6276607</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -18256,12 +18263,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18275,18 +18282,18 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -18296,13 +18303,13 @@
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54511650</t>
+          <t>https://artportalen.se/Sighting/54444175</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>54524712</v>
+        <v>54511650</v>
       </c>
       <c r="B151" t="n">
         <v>106243</v>
@@ -18336,17 +18343,17 @@
       <c r="L151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>NO Gårdby sandhed, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>601271</v>
+        <v>601215</v>
       </c>
       <c r="R151" t="n">
-        <v>6276640</v>
+        <v>6276591</v>
       </c>
       <c r="S151" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -18370,12 +18377,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2015-07-21</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2015-07-21</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18386,16 +18393,21 @@
       </c>
       <c r="AG151" t="b">
         <v>0</v>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>tallskog på sand</t>
+        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -18405,13 +18417,13 @@
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54524712</t>
+          <t>https://artportalen.se/Sighting/54511650</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>58885018</v>
+        <v>54524712</v>
       </c>
       <c r="B152" t="n">
         <v>106243</v>
@@ -18445,14 +18457,14 @@
       <c r="L152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>NO Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>601246</v>
+        <v>601271</v>
       </c>
       <c r="R152" t="n">
-        <v>6276674</v>
+        <v>6276640</v>
       </c>
       <c r="S152" t="n">
         <v>50</v>
@@ -18479,12 +18491,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2015-07-21</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2015-07-21</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18499,12 +18511,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -18514,13 +18526,13 @@
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/58885018</t>
+          <t>https://artportalen.se/Sighting/54524712</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>66113422</v>
+        <v>58885018</v>
       </c>
       <c r="B153" t="n">
         <v>106243</v>
@@ -18550,11 +18562,7 @@
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
@@ -18562,10 +18570,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>601321</v>
+        <v>601246</v>
       </c>
       <c r="R153" t="n">
-        <v>6276619</v>
+        <v>6276674</v>
       </c>
       <c r="S153" t="n">
         <v>50</v>
@@ -18592,12 +18600,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18612,12 +18620,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Hans Lindfors</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Hans Lindfors</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -18627,13 +18635,13 @@
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66113422</t>
+          <t>https://artportalen.se/Sighting/58885018</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>66676941</v>
+        <v>66113422</v>
       </c>
       <c r="B154" t="n">
         <v>106243</v>
@@ -18663,21 +18671,25 @@
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Dörby tallskog, N2, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>601276</v>
+        <v>601321</v>
       </c>
       <c r="R154" t="n">
-        <v>6276684</v>
+        <v>6276619</v>
       </c>
       <c r="S154" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -18701,12 +18713,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2017-06-04</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2017-06-04</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18721,12 +18733,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Hans Lindfors</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Hans Lindfors</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -18736,13 +18748,13 @@
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66676941</t>
+          <t>https://artportalen.se/Sighting/66113422</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>72346187</v>
+        <v>66676941</v>
       </c>
       <c r="B155" t="n">
         <v>106243</v>
@@ -18772,23 +18784,18 @@
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, N2, Öl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>601215</v>
+        <v>601276</v>
       </c>
       <c r="R155" t="n">
-        <v>6276612</v>
+        <v>6276684</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -18815,12 +18822,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18829,7 +18836,6 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -18851,13 +18857,13 @@
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72346187</t>
+          <t>https://artportalen.se/Sighting/66676941</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>86801212</v>
+        <v>72346187</v>
       </c>
       <c r="B156" t="n">
         <v>106243</v>
@@ -18889,21 +18895,21 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Dörbytallskog, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>601246</v>
+        <v>601215</v>
       </c>
       <c r="R156" t="n">
-        <v>6276644</v>
+        <v>6276612</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -18930,12 +18936,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18948,20 +18954,15 @@
       <c r="AG156" t="b">
         <v>0</v>
       </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
-      </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -18971,16 +18972,16 @@
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86801212</t>
+          <t>https://artportalen.se/Sighting/72346187</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>94467626</v>
+        <v>86801212</v>
       </c>
       <c r="B157" t="n">
-        <v>106244</v>
+        <v>106243</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19006,19 +19007,24 @@
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Dörby tallskog, norr sandheden, Öl</t>
+          <t>Dörbytallskog, Öl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>601269</v>
+        <v>601246</v>
       </c>
       <c r="R157" t="n">
-        <v>6276632</v>
+        <v>6276644</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -19045,12 +19051,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -19063,27 +19069,36 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>gles tallskog</t>
+        </is>
+      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
-        </is>
-      </c>
-      <c r="AY157" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94467626</t>
+          <t>https://artportalen.se/Sighting/86801212</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>99255605</v>
+        <v>94467626</v>
       </c>
       <c r="B158" t="n">
         <v>106244</v>
@@ -19111,29 +19126,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Gårdby-Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, norr sandheden, Öl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>601203</v>
+        <v>601269</v>
       </c>
       <c r="R158" t="n">
-        <v>6276606</v>
+        <v>6276632</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -19160,12 +19166,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19178,32 +19184,27 @@
       <c r="AG158" t="b">
         <v>0</v>
       </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99255605</t>
+          <t>https://artportalen.se/Sighting/94467626</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>99255615</v>
+        <v>99255605</v>
       </c>
       <c r="B159" t="n">
         <v>106244</v>
@@ -19231,8 +19232,16 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
@@ -19242,10 +19251,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>601209</v>
+        <v>601203</v>
       </c>
       <c r="R159" t="n">
-        <v>6276612</v>
+        <v>6276606</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -19309,13 +19318,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99255615</t>
+          <t>https://artportalen.se/Sighting/99255605</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>99255628</v>
+        <v>99255615</v>
       </c>
       <c r="B160" t="n">
         <v>106244</v>
@@ -19343,16 +19352,8 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
@@ -19362,10 +19363,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>601239</v>
+        <v>601209</v>
       </c>
       <c r="R160" t="n">
-        <v>6276653</v>
+        <v>6276612</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -19429,13 +19430,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99255628</t>
+          <t>https://artportalen.se/Sighting/99255615</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>99255660</v>
+        <v>99255628</v>
       </c>
       <c r="B161" t="n">
         <v>106244</v>
@@ -19465,7 +19466,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -19482,10 +19483,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>601321</v>
+        <v>601239</v>
       </c>
       <c r="R161" t="n">
-        <v>6276611</v>
+        <v>6276653</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -19549,13 +19550,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99255660</t>
+          <t>https://artportalen.se/Sighting/99255628</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>101612360</v>
+        <v>99255660</v>
       </c>
       <c r="B162" t="n">
         <v>106244</v>
@@ -19583,28 +19584,32 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Gårdby-Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>601240</v>
+        <v>601321</v>
       </c>
       <c r="R162" t="n">
-        <v>6276652</v>
+        <v>6276611</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -19628,12 +19633,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19646,27 +19651,32 @@
       <c r="AG162" t="b">
         <v>0</v>
       </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
+      </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Erik F Nordberg</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Erik F Nordberg, Karin Andersson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101612360</t>
+          <t>https://artportalen.se/Sighting/99255660</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126780833</v>
+        <v>101612360</v>
       </c>
       <c r="B163" t="n">
         <v>106244</v>
@@ -19696,22 +19706,26 @@
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>601288</v>
+        <v>601240</v>
       </c>
       <c r="R163" t="n">
-        <v>6276671</v>
+        <v>6276652</v>
       </c>
       <c r="S163" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -19735,12 +19749,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19753,85 +19767,69 @@
       <c r="AG163" t="b">
         <v>0</v>
       </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>gallrad tallskog</t>
-        </is>
-      </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Erik F Nordberg</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Erik F Nordberg, Karin Andersson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126780833</t>
+          <t>https://artportalen.se/Sighting/101612360</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>60656115</v>
+        <v>126780833</v>
       </c>
       <c r="B164" t="n">
-        <v>107294</v>
+        <v>106244</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221647</v>
+        <v>221144</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Galeopsis ladanum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>601212</v>
+        <v>601288</v>
       </c>
       <c r="R164" t="n">
-        <v>6276638</v>
+        <v>6276671</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -19858,12 +19856,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19872,12 +19870,13 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>igenlagt sandtag</t>
+          <t>gallrad tallskog</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -19891,23 +19890,19 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY164" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+      <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60656115</t>
+          <t>https://artportalen.se/Sighting/126780833</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>16065673</v>
+        <v>60656115</v>
       </c>
       <c r="B165" t="n">
-        <v>107516</v>
+        <v>107294</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19915,16 +19910,16 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>221849</v>
+        <v>221647</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Galeopsis ladanum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -19932,9 +19927,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
@@ -19972,12 +19979,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19991,7 +19998,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>SANDTAG</t>
+          <t>igenlagt sandtag</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -20012,13 +20019,13 @@
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16065673</t>
+          <t>https://artportalen.se/Sighting/60656115</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>54591844</v>
+        <v>16065673</v>
       </c>
       <c r="B166" t="n">
         <v>107516</v>
@@ -20056,10 +20063,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>601143</v>
+        <v>601212</v>
       </c>
       <c r="R166" t="n">
-        <v>6276662</v>
+        <v>6276638</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -20086,12 +20093,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20105,18 +20112,18 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>fd banvall, sandig</t>
+          <t>SANDTAG</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -20126,13 +20133,13 @@
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54591844</t>
+          <t>https://artportalen.se/Sighting/16065673</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>72696139</v>
+        <v>54591844</v>
       </c>
       <c r="B167" t="n">
         <v>107516</v>
@@ -20164,17 +20171,16 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>601166</v>
+        <v>601143</v>
       </c>
       <c r="R167" t="n">
-        <v>6276823</v>
+        <v>6276662</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -20201,12 +20207,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20215,24 +20221,23 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>sandig gammal banvall</t>
+          <t>fd banvall, sandig</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -20242,33 +20247,33 @@
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72696139</t>
+          <t>https://artportalen.se/Sighting/54591844</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>4220789</v>
+        <v>72696139</v>
       </c>
       <c r="B168" t="n">
-        <v>97983</v>
+        <v>107516</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>221945</v>
+        <v>221849</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -20277,16 +20282,20 @@
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Dörby tallskog, öster vägen, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>601369</v>
+        <v>601166</v>
       </c>
       <c r="R168" t="n">
-        <v>6276502</v>
+        <v>6276823</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -20313,12 +20322,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2008-01-27</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2008-01-27</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20327,23 +20336,24 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>sandig tallskog med enstaka hassel/ek</t>
+          <t>sandig gammal banvall</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -20353,13 +20363,13 @@
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4220789</t>
+          <t>https://artportalen.se/Sighting/72696139</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>4220790</v>
+        <v>4220789</v>
       </c>
       <c r="B169" t="n">
         <v>97983</v>
@@ -20394,10 +20404,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>601392</v>
+        <v>601369</v>
       </c>
       <c r="R169" t="n">
-        <v>6276503</v>
+        <v>6276502</v>
       </c>
       <c r="S169" t="n">
         <v>25</v>
@@ -20464,13 +20474,13 @@
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4220790</t>
+          <t>https://artportalen.se/Sighting/4220789</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>7176403</v>
+        <v>4220790</v>
       </c>
       <c r="B170" t="n">
         <v>97983</v>
@@ -20499,19 +20509,16 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, öster vägen, Öl</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>601303</v>
+        <v>601392</v>
       </c>
       <c r="R170" t="n">
-        <v>6276564</v>
+        <v>6276503</v>
       </c>
       <c r="S170" t="n">
         <v>25</v>
@@ -20538,12 +20545,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2008-01-27</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2008-01-27</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20554,16 +20561,21 @@
       </c>
       <c r="AG170" t="b">
         <v>0</v>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>sandig tallskog med enstaka hassel/ek</t>
+        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
@@ -20573,13 +20585,13 @@
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7176403</t>
+          <t>https://artportalen.se/Sighting/4220790</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>16065769</v>
+        <v>7176403</v>
       </c>
       <c r="B171" t="n">
         <v>97983</v>
@@ -20613,14 +20625,14 @@
       <c r="L171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>601312</v>
+        <v>601303</v>
       </c>
       <c r="R171" t="n">
-        <v>6276555</v>
+        <v>6276564</v>
       </c>
       <c r="S171" t="n">
         <v>25</v>
@@ -20647,12 +20659,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20663,11 +20675,6 @@
       </c>
       <c r="AG171" t="b">
         <v>0</v>
-      </c>
-      <c r="AI171" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
@@ -20687,38 +20694,38 @@
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16065769</t>
+          <t>https://artportalen.se/Sighting/7176403</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>60656163</v>
+        <v>16065769</v>
       </c>
       <c r="B172" t="n">
-        <v>100292</v>
+        <v>97983</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>222223</v>
+        <v>221945</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Apera spica-venti</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) P. Beauv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -20731,10 +20738,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>601222</v>
+        <v>601312</v>
       </c>
       <c r="R172" t="n">
-        <v>6276656</v>
+        <v>6276555</v>
       </c>
       <c r="S172" t="n">
         <v>25</v>
@@ -20761,12 +20768,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20780,7 +20787,7 @@
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>igenlagt sandtag</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
@@ -20801,16 +20808,16 @@
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60656163</t>
+          <t>https://artportalen.se/Sighting/16065769</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>5144080</v>
+        <v>60656163</v>
       </c>
       <c r="B173" t="n">
-        <v>100797</v>
+        <v>100292</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20818,34 +20825,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>222617</v>
+        <v>222223</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Apera spica-venti</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>(L.) P. Beauv.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>601216</v>
+        <v>601222</v>
       </c>
       <c r="R173" t="n">
-        <v>6276667</v>
+        <v>6276656</v>
       </c>
       <c r="S173" t="n">
         <v>25</v>
@@ -20872,12 +20882,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20891,18 +20901,18 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>sandtag</t>
+          <t>igenlagt sandtag</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -20912,13 +20922,13 @@
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5144080</t>
+          <t>https://artportalen.se/Sighting/60656163</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>72345748</v>
+        <v>5144080</v>
       </c>
       <c r="B174" t="n">
         <v>100797</v>
@@ -20947,20 +20957,16 @@
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>601132</v>
+        <v>601216</v>
       </c>
       <c r="R174" t="n">
-        <v>6276668</v>
+        <v>6276667</v>
       </c>
       <c r="S174" t="n">
         <v>25</v>
@@ -20987,12 +20993,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -21001,19 +21007,23 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>sandtag</t>
+        </is>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
@@ -21023,16 +21033,16 @@
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72345748</t>
+          <t>https://artportalen.se/Sighting/5144080</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>135288104</v>
+        <v>72345748</v>
       </c>
       <c r="B175" t="n">
-        <v>100955</v>
+        <v>100797</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21058,19 +21068,23 @@
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Vägområde, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>601301</v>
+        <v>601132</v>
       </c>
       <c r="R175" t="n">
-        <v>6276866</v>
+        <v>6276668</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -21094,12 +21108,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -21108,75 +21122,76 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
+      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Edvin Åhman</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Edvin Åhman, Christine Sandberg</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135288104</t>
+          <t>https://artportalen.se/Sighting/72345748</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>86801227</v>
+        <v>135288104</v>
       </c>
       <c r="B176" t="n">
-        <v>99097</v>
+        <v>100957</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>223609</v>
+        <v>222617</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr"/>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Dörbytallskog, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>601308</v>
+        <v>601301</v>
       </c>
       <c r="R176" t="n">
-        <v>6276656</v>
+        <v>6276866</v>
       </c>
       <c r="S176" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -21200,12 +21215,12 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -21214,40 +21229,34 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86801227</t>
+          <t>https://artportalen.se/Sighting/135288104</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127081837</v>
+        <v>86801227</v>
       </c>
       <c r="B177" t="n">
         <v>99097</v>
@@ -21271,32 +21280,24 @@
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Gårdby tallskog tornet, Öl</t>
+          <t>Dörbytallskog, Öl</t>
         </is>
       </c>
       <c r="Q177" t="n">
         <v>601308</v>
       </c>
       <c r="R177" t="n">
-        <v>6276635</v>
+        <v>6276656</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -21320,22 +21321,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -21348,30 +21339,39 @@
       <c r="AG177" t="b">
         <v>0</v>
       </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>gles tallskog</t>
+        </is>
+      </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Rolf Kläppe</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Rolf Kläppe</t>
-        </is>
-      </c>
-      <c r="AY177" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127081837</t>
+          <t>https://artportalen.se/Sighting/86801227</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>16071746</v>
+        <v>127081837</v>
       </c>
       <c r="B178" t="n">
-        <v>106230</v>
+        <v>99097</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21379,40 +21379,45 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>224098</v>
+        <v>223609</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Wallr.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Gårdby tallskog tornet, Öl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>601278</v>
+        <v>601308</v>
       </c>
       <c r="R178" t="n">
-        <v>6276674</v>
+        <v>6276635</v>
       </c>
       <c r="S178" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -21436,12 +21441,22 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21450,39 +21465,31 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Rolf Kläppe</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY178" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Rolf Kläppe</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16071746</t>
+          <t>https://artportalen.se/Sighting/127081837</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>60656204</v>
+        <v>16071746</v>
       </c>
       <c r="B179" t="n">
         <v>106230</v>
@@ -21520,10 +21527,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>601309</v>
+        <v>601278</v>
       </c>
       <c r="R179" t="n">
-        <v>6276659</v>
+        <v>6276674</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>
@@ -21550,12 +21557,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -21569,7 +21576,7 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>skogsväg</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr"/>
@@ -21590,13 +21597,13 @@
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60656204</t>
+          <t>https://artportalen.se/Sighting/16071746</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>66674736</v>
+        <v>60656204</v>
       </c>
       <c r="B180" t="n">
         <v>106230</v>
@@ -21626,22 +21633,18 @@
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Dörby tallskog, N1, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>601316</v>
+        <v>601309</v>
       </c>
       <c r="R180" t="n">
-        <v>6276639</v>
+        <v>6276659</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>
@@ -21668,12 +21671,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21684,16 +21687,21 @@
       </c>
       <c r="AG180" t="b">
         <v>0</v>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>skogsväg</t>
+        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Ingela Carlström</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
@@ -21703,52 +21711,58 @@
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66674736</t>
+          <t>https://artportalen.se/Sighting/60656204</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>6187223</v>
+        <v>66674736</v>
       </c>
       <c r="B181" t="n">
-        <v>107062</v>
+        <v>106230</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>224354</v>
+        <v>224098</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vanlig axveronika</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Veronica spicata subsp. spicata</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr"/>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
       <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Öl</t>
+          <t>Dörby tallskog, N1, Öl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>601335</v>
+        <v>601316</v>
       </c>
       <c r="R181" t="n">
-        <v>6276698</v>
+        <v>6276639</v>
       </c>
       <c r="S181" t="n">
         <v>25</v>
@@ -21775,12 +21789,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21791,21 +21805,16 @@
       </c>
       <c r="AG181" t="b">
         <v>0</v>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Tommy Carlström, Ingela Carlström</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
@@ -21815,13 +21824,13 @@
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6187223</t>
+          <t>https://artportalen.se/Sighting/66674736</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>66677098</v>
+        <v>6187223</v>
       </c>
       <c r="B182" t="n">
         <v>107062</v>
@@ -21846,26 +21855,24 @@
       </c>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Dörby tallskog, infart, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>601217</v>
+        <v>601335</v>
       </c>
       <c r="R182" t="n">
-        <v>6276653</v>
+        <v>6276698</v>
       </c>
       <c r="S182" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21889,12 +21896,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21905,16 +21912,21 @@
       </c>
       <c r="AG182" t="b">
         <v>0</v>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>tallskog på sand</t>
+        </is>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -21924,53 +21936,57 @@
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66677098</t>
+          <t>https://artportalen.se/Sighting/6187223</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>54511699</v>
+        <v>66677098</v>
       </c>
       <c r="B183" t="n">
-        <v>97985</v>
+        <v>107062</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>224363</v>
+        <v>224354</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig axveronika</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Veronica spicata subsp. spicata</t>
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, infart, Öl</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>601285</v>
+        <v>601217</v>
       </c>
       <c r="R183" t="n">
-        <v>6276569</v>
+        <v>6276653</v>
       </c>
       <c r="S183" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21994,12 +22010,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -22010,21 +22026,16 @@
       </c>
       <c r="AG183" t="b">
         <v>0</v>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
@@ -22034,13 +22045,13 @@
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54511699</t>
+          <t>https://artportalen.se/Sighting/66677098</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>54511702</v>
+        <v>54511699</v>
       </c>
       <c r="B184" t="n">
         <v>97985</v>
@@ -22074,10 +22085,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>601304</v>
+        <v>601285</v>
       </c>
       <c r="R184" t="n">
-        <v>6276567</v>
+        <v>6276569</v>
       </c>
       <c r="S184" t="n">
         <v>25</v>
@@ -22144,47 +22155,50 @@
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54511702</t>
+          <t>https://artportalen.se/Sighting/54511699</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>6247724</v>
+        <v>54511702</v>
       </c>
       <c r="B185" t="n">
-        <v>104640</v>
+        <v>97985</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>224416</v>
+        <v>224363</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>601216</v>
+        <v>601304</v>
       </c>
       <c r="R185" t="n">
-        <v>6276667</v>
+        <v>6276567</v>
       </c>
       <c r="S185" t="n">
         <v>25</v>
@@ -22211,12 +22225,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -22230,7 +22244,7 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>sandtag</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>
@@ -22251,13 +22265,13 @@
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6247724</t>
+          <t>https://artportalen.se/Sighting/54511702</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>16065671</v>
+        <v>6247724</v>
       </c>
       <c r="B186" t="n">
         <v>104640</v>
@@ -22282,19 +22296,16 @@
       </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>601212</v>
+        <v>601216</v>
       </c>
       <c r="R186" t="n">
-        <v>6276638</v>
+        <v>6276667</v>
       </c>
       <c r="S186" t="n">
         <v>25</v>
@@ -22321,12 +22332,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -22340,26 +22351,136 @@
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>SANDTAG</t>
+          <t>sandtag</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6247724</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>16065671</v>
+      </c>
+      <c r="B187" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Dörby tallskog, Öl</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>601212</v>
+      </c>
+      <c r="R187" t="n">
+        <v>6276638</v>
+      </c>
+      <c r="S187" t="n">
+        <v>25</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2014-07-07</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2014-07-07</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>SANDTAG</t>
+        </is>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
           <t>Ulla-Britt Andersson</t>
         </is>
       </c>
-      <c r="AX186" t="inlineStr">
+      <c r="AX187" t="inlineStr">
         <is>
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY186" t="inlineStr">
+      <c r="AY187" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
-      <c r="AZ186" t="inlineStr">
+      <c r="AZ187" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/16065671</t>
         </is>
@@ -22552,6 +22673,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -9190,7 +9190,7 @@
         <v>135447260</v>
       </c>
       <c r="B73" t="n">
-        <v>104848</v>
+        <v>104868</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>135914235</v>
       </c>
       <c r="B110" t="n">
-        <v>99254</v>
+        <v>99271</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>134863685</v>
       </c>
       <c r="B134" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -13497,7 +13497,7 @@
         <v>135914235</v>
       </c>
       <c r="B110" t="n">
-        <v>99271</v>
+        <v>99272</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>134863685</v>
       </c>
       <c r="B134" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -13497,7 +13497,7 @@
         <v>135914235</v>
       </c>
       <c r="B110" t="n">
-        <v>99272</v>
+        <v>99273</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>134863685</v>
       </c>
       <c r="B134" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -13497,7 +13497,7 @@
         <v>135914235</v>
       </c>
       <c r="B110" t="n">
-        <v>99273</v>
+        <v>99274</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>134863685</v>
       </c>
       <c r="B134" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -13497,7 +13497,7 @@
         <v>135914235</v>
       </c>
       <c r="B110" t="n">
-        <v>99274</v>
+        <v>99280</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>134863685</v>
       </c>
       <c r="B134" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -13497,7 +13497,7 @@
         <v>135914235</v>
       </c>
       <c r="B110" t="n">
-        <v>99280</v>
+        <v>99281</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>134863685</v>
       </c>
       <c r="B134" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -13497,7 +13497,7 @@
         <v>135914235</v>
       </c>
       <c r="B110" t="n">
-        <v>99281</v>
+        <v>99292</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>134863685</v>
       </c>
       <c r="B134" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -13497,7 +13497,7 @@
         <v>135914235</v>
       </c>
       <c r="B110" t="n">
-        <v>99292</v>
+        <v>99305</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>134863685</v>
       </c>
       <c r="B134" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -13497,7 +13497,7 @@
         <v>135914235</v>
       </c>
       <c r="B110" t="n">
-        <v>99305</v>
+        <v>99306</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>134863685</v>
       </c>
       <c r="B134" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -13497,7 +13497,7 @@
         <v>135914235</v>
       </c>
       <c r="B110" t="n">
-        <v>99306</v>
+        <v>99319</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>134863685</v>
       </c>
       <c r="B134" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -13497,7 +13497,7 @@
         <v>135914235</v>
       </c>
       <c r="B110" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>134863685</v>
       </c>
       <c r="B134" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
